--- a/tratando_tabelas/objetiva/entradas_objetiva.xlsx
+++ b/tratando_tabelas/objetiva/entradas_objetiva.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6600" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6600" uniqueCount="739">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.8 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 07/08/2026 08:36:19</t>
+    <t xml:space="preserve">Emitido em: 07/08/2026 08:49:28</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -1204,81 +1204,72 @@
     <t xml:space="preserve">35260797837181005963550010000535601632997923</t>
   </si>
   <si>
+    <t xml:space="preserve">7.661 - SEGURIMAX COM. AT. EQUIP. SEG. IMP. EXP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.932,47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.164 - TRANSPORTES MARLIM LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251,21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260717011376000102550010001869601236288220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260758158372000120570010000474621000475103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.593 - ROCA SANITARIO BRASIL LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.339,21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260775801902002501550000008319501460419692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934.638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.441,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260788674080000101550010009346381580496417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">934.636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.367,90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260788674080000101550010009346361580496390</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.927 - TIGRE MATERIAIS E SOLUCOES PARA CONSTRUCAO LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">2.072.039</t>
+    <t xml:space="preserve">2.071.823</t>
   </si>
   <si>
     <t xml:space="preserve">15/08/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">61.391,40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260708862530001122550010020720391122868296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.661 - SEGURIMAX COM. AT. EQUIP. SEG. IMP. EXP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.932,47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.164 - TRANSPORTES MARLIM LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251,21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260717011376000102550010001869601236288220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260758158372000120570010000474621000475103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.593 - ROCA SANITARIO BRASIL LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.339,21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31260775801902002501550000008319501460419692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">934.638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.441,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260788674080000101550010009346381580496417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">934.636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.367,90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260788674080000101550010009346361580496390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.071.823</t>
-  </si>
-  <si>
     <t xml:space="preserve">51.407,80</t>
   </si>
   <si>
@@ -2165,6 +2156,21 @@
   </si>
   <si>
     <t xml:space="preserve">35260752618139002817550030008828921900329299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">756 - SFERA COMERCIAL IMPORTADORA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.438,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260772741051000185550550003094831436500188</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -34678,7 +34684,7 @@
     </row>
     <row r="80" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
-        <v>312052</v>
+        <v>312064</v>
       </c>
       <c r="B80" s="9" t="s">
         <v>394</v>
@@ -34693,61 +34699,61 @@
         <v>91</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>291</v>
+        <v>214</v>
       </c>
       <c r="I80" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>396</v>
+        <v>166</v>
       </c>
       <c r="K80" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>61391.4</v>
+        <v>3932.47</v>
       </c>
       <c r="M80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O80" s="12" t="n">
-        <v>61391.4</v>
+        <v>3843</v>
       </c>
       <c r="P80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="13" t="n">
-        <v>62.6283</v>
+        <v>0.047532</v>
       </c>
       <c r="R80" s="12" t="n">
-        <v>4723.74</v>
+        <v>75.92</v>
       </c>
       <c r="S80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T80" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="U80" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V80" s="12" t="n">
-        <v>51812.8</v>
+        <v>3348.02</v>
       </c>
       <c r="W80" s="12" t="n">
-        <v>51.81</v>
+        <v>3.34</v>
       </c>
       <c r="X80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y80" s="12" t="n">
-        <v>466.31</v>
+        <v>30.14</v>
       </c>
       <c r="Z80" s="12" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="AA80" s="9" t="s">
         <v>77</v>
@@ -34756,13 +34762,13 @@
         <v>303</v>
       </c>
       <c r="AC80" s="12" t="n">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="AD80" s="12" t="n">
-        <v>61391.4</v>
+        <v>3843</v>
       </c>
       <c r="AE80" s="12" t="n">
-        <v>4297.4</v>
+        <v>153.72</v>
       </c>
       <c r="AF80" s="12" t="n">
         <v>0</v>
@@ -34771,7 +34777,7 @@
         <v>0</v>
       </c>
       <c r="AH80" s="12" t="n">
-        <v>0</v>
+        <v>251.21</v>
       </c>
       <c r="AI80" s="12" t="n">
         <v>0</v>
@@ -34852,25 +34858,25 @@
         <v>79</v>
       </c>
       <c r="BI80" s="14" t="s">
-        <v>79</v>
+        <v>397</v>
       </c>
       <c r="BJ80" s="9" t="s">
-        <v>79</v>
+        <v>398</v>
       </c>
       <c r="BK80" s="9" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="BL80" s="14" t="s">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="BM80" s="9" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="BN80" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="BO80" s="9" t="s">
-        <v>79</v>
+        <v>401</v>
       </c>
       <c r="BP80" s="9" t="s">
         <v>79</v>
@@ -34881,34 +34887,34 @@
     </row>
     <row r="81" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
-        <v>312064</v>
+        <v>312073</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
       <c r="F81" s="9" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>91</v>
+        <v>242</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>214</v>
+        <v>291</v>
       </c>
       <c r="I81" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>166</v>
+        <v>267</v>
       </c>
       <c r="K81" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>3932.47</v>
+        <v>37339.21</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
@@ -34917,40 +34923,40 @@
         <v>3</v>
       </c>
       <c r="O81" s="12" t="n">
-        <v>3843</v>
+        <v>37339.21</v>
       </c>
       <c r="P81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q81" s="13" t="n">
-        <v>0.047532</v>
+        <v>9.262</v>
       </c>
       <c r="R81" s="12" t="n">
-        <v>75.92</v>
+        <v>1413.53</v>
       </c>
       <c r="S81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T81" s="14" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="U81" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V81" s="12" t="n">
-        <v>3348.02</v>
+        <v>31513.35</v>
       </c>
       <c r="W81" s="12" t="n">
-        <v>3.34</v>
+        <v>31.53</v>
       </c>
       <c r="X81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y81" s="12" t="n">
-        <v>30.14</v>
+        <v>283.62</v>
       </c>
       <c r="Z81" s="12" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="AA81" s="9" t="s">
         <v>77</v>
@@ -34959,13 +34965,13 @@
         <v>303</v>
       </c>
       <c r="AC81" s="12" t="n">
-        <v>89.47</v>
+        <v>0</v>
       </c>
       <c r="AD81" s="12" t="n">
-        <v>3843</v>
+        <v>37339.21</v>
       </c>
       <c r="AE81" s="12" t="n">
-        <v>153.72</v>
+        <v>2613.74</v>
       </c>
       <c r="AF81" s="12" t="n">
         <v>0</v>
@@ -34974,7 +34980,7 @@
         <v>0</v>
       </c>
       <c r="AH81" s="12" t="n">
-        <v>251.21</v>
+        <v>0</v>
       </c>
       <c r="AI81" s="12" t="n">
         <v>0</v>
@@ -35055,25 +35061,25 @@
         <v>79</v>
       </c>
       <c r="BI81" s="14" t="s">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="BJ81" s="9" t="s">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="BK81" s="9" t="s">
-        <v>214</v>
+        <v>73</v>
       </c>
       <c r="BL81" s="14" t="s">
-        <v>404</v>
+        <v>79</v>
       </c>
       <c r="BM81" s="9" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="BN81" s="9" t="s">
         <v>405</v>
       </c>
       <c r="BO81" s="9" t="s">
-        <v>406</v>
+        <v>79</v>
       </c>
       <c r="BP81" s="9" t="s">
         <v>79</v>
@@ -35084,19 +35090,19 @@
     </row>
     <row r="82" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
-        <v>312073</v>
+        <v>312076</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>407</v>
+        <v>265</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
       <c r="F82" s="9" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="H82" s="9" t="s">
         <v>291</v>
@@ -35105,55 +35111,55 @@
         <v>303</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>267</v>
+        <v>407</v>
       </c>
       <c r="K82" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>37339.21</v>
+        <v>1441.87</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N82" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O82" s="12" t="n">
-        <v>37339.21</v>
+        <v>1396.48</v>
       </c>
       <c r="P82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="13" t="n">
-        <v>9.262</v>
+        <v>0.00588</v>
       </c>
       <c r="R82" s="12" t="n">
-        <v>1413.53</v>
+        <v>3.5</v>
       </c>
       <c r="S82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T82" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="U82" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V82" s="12" t="n">
-        <v>31513.35</v>
+        <v>1178.6</v>
       </c>
       <c r="W82" s="12" t="n">
-        <v>31.53</v>
+        <v>1.18</v>
       </c>
       <c r="X82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y82" s="12" t="n">
-        <v>283.62</v>
+        <v>10.61</v>
       </c>
       <c r="Z82" s="12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="AA82" s="9" t="s">
         <v>77</v>
@@ -35162,13 +35168,13 @@
         <v>303</v>
       </c>
       <c r="AC82" s="12" t="n">
-        <v>0</v>
+        <v>45.39</v>
       </c>
       <c r="AD82" s="12" t="n">
-        <v>37339.21</v>
+        <v>1396.48</v>
       </c>
       <c r="AE82" s="12" t="n">
-        <v>2613.74</v>
+        <v>97.75</v>
       </c>
       <c r="AF82" s="12" t="n">
         <v>0</v>
@@ -35273,7 +35279,7 @@
         <v>73</v>
       </c>
       <c r="BN82" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="BO82" s="9" t="s">
         <v>79</v>
@@ -35287,7 +35293,7 @@
     </row>
     <row r="83" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="n">
-        <v>312076</v>
+        <v>312077</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>265</v>
@@ -35296,7 +35302,7 @@
       <c r="D83" s="9"/>
       <c r="E83" s="9"/>
       <c r="F83" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>91</v>
@@ -35308,52 +35314,52 @@
         <v>303</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="K83" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>1441.87</v>
+        <v>2367.9</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O83" s="12" t="n">
-        <v>1396.48</v>
+        <v>2285</v>
       </c>
       <c r="P83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="13" t="n">
-        <v>0.00588</v>
+        <v>0.01512</v>
       </c>
       <c r="R83" s="12" t="n">
-        <v>3.5</v>
+        <v>6.16</v>
       </c>
       <c r="S83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T83" s="14" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="U83" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V83" s="12" t="n">
-        <v>1178.6</v>
+        <v>1928.48</v>
       </c>
       <c r="W83" s="12" t="n">
-        <v>1.18</v>
+        <v>1.93</v>
       </c>
       <c r="X83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y83" s="12" t="n">
-        <v>10.61</v>
+        <v>17.36</v>
       </c>
       <c r="Z83" s="12" t="n">
         <v>35</v>
@@ -35365,13 +35371,13 @@
         <v>303</v>
       </c>
       <c r="AC83" s="12" t="n">
-        <v>45.39</v>
+        <v>82.9</v>
       </c>
       <c r="AD83" s="12" t="n">
-        <v>1396.48</v>
+        <v>2285</v>
       </c>
       <c r="AE83" s="12" t="n">
-        <v>97.75</v>
+        <v>159.95</v>
       </c>
       <c r="AF83" s="12" t="n">
         <v>0</v>
@@ -35476,7 +35482,7 @@
         <v>73</v>
       </c>
       <c r="BN83" s="9" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="BO83" s="9" t="s">
         <v>79</v>
@@ -35490,16 +35496,16 @@
     </row>
     <row r="84" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="n">
-        <v>312077</v>
+        <v>312082</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>265</v>
+        <v>413</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
       <c r="E84" s="9"/>
       <c r="F84" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>91</v>
@@ -35511,31 +35517,31 @@
         <v>303</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K84" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>2367.9</v>
+        <v>51407.8</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N84" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O84" s="12" t="n">
-        <v>2285</v>
+        <v>51407.8</v>
       </c>
       <c r="P84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q84" s="13" t="n">
-        <v>0.01512</v>
+        <v>61.1256</v>
       </c>
       <c r="R84" s="12" t="n">
-        <v>6.16</v>
+        <v>4506.94</v>
       </c>
       <c r="S84" s="12" t="n">
         <v>0</v>
@@ -35547,19 +35553,19 @@
         <v>76</v>
       </c>
       <c r="V84" s="12" t="n">
-        <v>1928.48</v>
+        <v>43386.9</v>
       </c>
       <c r="W84" s="12" t="n">
-        <v>1.93</v>
+        <v>43.38</v>
       </c>
       <c r="X84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y84" s="12" t="n">
-        <v>17.36</v>
+        <v>390.47</v>
       </c>
       <c r="Z84" s="12" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AA84" s="9" t="s">
         <v>77</v>
@@ -35568,13 +35574,13 @@
         <v>303</v>
       </c>
       <c r="AC84" s="12" t="n">
-        <v>82.9</v>
+        <v>0</v>
       </c>
       <c r="AD84" s="12" t="n">
-        <v>2285</v>
+        <v>51407.8</v>
       </c>
       <c r="AE84" s="12" t="n">
-        <v>159.95</v>
+        <v>3598.55</v>
       </c>
       <c r="AF84" s="12" t="n">
         <v>0</v>
@@ -35693,10 +35699,10 @@
     </row>
     <row r="85" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="n">
-        <v>312082</v>
+        <v>312083</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>394</v>
+        <v>281</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="9"/>
@@ -35714,31 +35720,31 @@
         <v>303</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>396</v>
+        <v>166</v>
       </c>
       <c r="K85" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>51407.8</v>
+        <v>64964.98</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O85" s="12" t="n">
-        <v>51407.8</v>
+        <v>62920.08</v>
       </c>
       <c r="P85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q85" s="13" t="n">
-        <v>61.1256</v>
+        <v>17.9004</v>
       </c>
       <c r="R85" s="12" t="n">
-        <v>4506.94</v>
+        <v>2204.5</v>
       </c>
       <c r="S85" s="12" t="n">
         <v>0</v>
@@ -35750,19 +35756,19 @@
         <v>76</v>
       </c>
       <c r="V85" s="12" t="n">
-        <v>43386.9</v>
+        <v>53102.97</v>
       </c>
       <c r="W85" s="12" t="n">
-        <v>43.38</v>
+        <v>53.1</v>
       </c>
       <c r="X85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y85" s="12" t="n">
-        <v>390.47</v>
+        <v>477.92</v>
       </c>
       <c r="Z85" s="12" t="n">
-        <v>15</v>
+        <v>55.12</v>
       </c>
       <c r="AA85" s="9" t="s">
         <v>77</v>
@@ -35771,13 +35777,13 @@
         <v>303</v>
       </c>
       <c r="AC85" s="12" t="n">
-        <v>0</v>
+        <v>2044.9</v>
       </c>
       <c r="AD85" s="12" t="n">
-        <v>51407.8</v>
+        <v>62920.08</v>
       </c>
       <c r="AE85" s="12" t="n">
-        <v>3598.55</v>
+        <v>4404.41</v>
       </c>
       <c r="AF85" s="12" t="n">
         <v>0</v>
@@ -35896,16 +35902,16 @@
     </row>
     <row r="86" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="n">
-        <v>312083</v>
+        <v>312084</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>281</v>
+        <v>421</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="9"/>
       <c r="E86" s="9"/>
       <c r="F86" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>91</v>
@@ -35923,49 +35929,49 @@
         <v>74</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>64964.98</v>
+        <v>10869.42</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O86" s="12" t="n">
-        <v>62920.08</v>
+        <v>9799.29</v>
       </c>
       <c r="P86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="13" t="n">
-        <v>17.9004</v>
+        <v>8.45448</v>
       </c>
       <c r="R86" s="12" t="n">
-        <v>2204.5</v>
+        <v>218.15</v>
       </c>
       <c r="S86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T86" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="U86" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V86" s="12" t="n">
-        <v>53102.97</v>
+        <v>8270.37</v>
       </c>
       <c r="W86" s="12" t="n">
-        <v>53.1</v>
+        <v>8.28</v>
       </c>
       <c r="X86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y86" s="12" t="n">
-        <v>477.92</v>
+        <v>74.44</v>
       </c>
       <c r="Z86" s="12" t="n">
-        <v>55.12</v>
+        <v>42</v>
       </c>
       <c r="AA86" s="9" t="s">
         <v>77</v>
@@ -35974,13 +35980,13 @@
         <v>303</v>
       </c>
       <c r="AC86" s="12" t="n">
-        <v>2044.9</v>
+        <v>0</v>
       </c>
       <c r="AD86" s="12" t="n">
-        <v>62920.08</v>
+        <v>9799.29</v>
       </c>
       <c r="AE86" s="12" t="n">
-        <v>4404.41</v>
+        <v>685.94</v>
       </c>
       <c r="AF86" s="12" t="n">
         <v>0</v>
@@ -35995,10 +36001,10 @@
         <v>0</v>
       </c>
       <c r="AJ86" s="12" t="n">
-        <v>0</v>
+        <v>6963.3</v>
       </c>
       <c r="AK86" s="12" t="n">
-        <v>0</v>
+        <v>1070.13</v>
       </c>
       <c r="AL86" s="14" t="s">
         <v>78</v>
@@ -36049,7 +36055,7 @@
         <v>78</v>
       </c>
       <c r="BB86" s="10" t="s">
-        <v>95</v>
+        <v>424</v>
       </c>
       <c r="BC86" s="14" t="s">
         <v>79</v>
@@ -36085,7 +36091,7 @@
         <v>73</v>
       </c>
       <c r="BN86" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="BO86" s="9" t="s">
         <v>79</v>
@@ -36099,16 +36105,16 @@
     </row>
     <row r="87" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="n">
-        <v>312084</v>
+        <v>312085</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9"/>
       <c r="E87" s="9"/>
       <c r="F87" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>91</v>
@@ -36126,46 +36132,46 @@
         <v>74</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>10869.42</v>
+        <v>35042.51</v>
       </c>
       <c r="M87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N87" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O87" s="12" t="n">
-        <v>9799.29</v>
+        <v>29786.32</v>
       </c>
       <c r="P87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="13" t="n">
-        <v>8.45448</v>
+        <v>61.214148</v>
       </c>
       <c r="R87" s="12" t="n">
-        <v>218.15</v>
+        <v>889.16</v>
       </c>
       <c r="S87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T87" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="U87" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V87" s="12" t="n">
-        <v>8270.37</v>
+        <v>25138.93</v>
       </c>
       <c r="W87" s="12" t="n">
-        <v>8.28</v>
+        <v>25.14</v>
       </c>
       <c r="X87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y87" s="12" t="n">
-        <v>74.44</v>
+        <v>226.25</v>
       </c>
       <c r="Z87" s="12" t="n">
         <v>42</v>
@@ -36180,10 +36186,10 @@
         <v>0</v>
       </c>
       <c r="AD87" s="12" t="n">
-        <v>9799.29</v>
+        <v>29786.32</v>
       </c>
       <c r="AE87" s="12" t="n">
-        <v>685.94</v>
+        <v>2085.04</v>
       </c>
       <c r="AF87" s="12" t="n">
         <v>0</v>
@@ -36198,10 +36204,10 @@
         <v>0</v>
       </c>
       <c r="AJ87" s="12" t="n">
-        <v>6963.3</v>
+        <v>34201.66</v>
       </c>
       <c r="AK87" s="12" t="n">
-        <v>1070.13</v>
+        <v>5256.19</v>
       </c>
       <c r="AL87" s="14" t="s">
         <v>78</v>
@@ -36252,7 +36258,7 @@
         <v>78</v>
       </c>
       <c r="BB87" s="10" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BC87" s="14" t="s">
         <v>79</v>
@@ -36302,10 +36308,10 @@
     </row>
     <row r="88" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="n">
-        <v>312085</v>
+        <v>312087</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>424</v>
+        <v>281</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -36329,25 +36335,25 @@
         <v>74</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>35042.51</v>
+        <v>252020.26</v>
       </c>
       <c r="M88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O88" s="12" t="n">
-        <v>29786.32</v>
+        <v>244087.41</v>
       </c>
       <c r="P88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q88" s="13" t="n">
-        <v>61.214148</v>
+        <v>52.271424</v>
       </c>
       <c r="R88" s="12" t="n">
-        <v>889.16</v>
+        <v>5617.51</v>
       </c>
       <c r="S88" s="12" t="n">
         <v>0</v>
@@ -36359,19 +36365,19 @@
         <v>76</v>
       </c>
       <c r="V88" s="12" t="n">
-        <v>25138.93</v>
+        <v>206003.7</v>
       </c>
       <c r="W88" s="12" t="n">
-        <v>25.14</v>
+        <v>206.02</v>
       </c>
       <c r="X88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y88" s="12" t="n">
-        <v>226.25</v>
+        <v>1854.03</v>
       </c>
       <c r="Z88" s="12" t="n">
-        <v>42</v>
+        <v>55.12</v>
       </c>
       <c r="AA88" s="9" t="s">
         <v>77</v>
@@ -36380,13 +36386,13 @@
         <v>303</v>
       </c>
       <c r="AC88" s="12" t="n">
-        <v>0</v>
+        <v>7932.85</v>
       </c>
       <c r="AD88" s="12" t="n">
-        <v>29786.32</v>
+        <v>244087.41</v>
       </c>
       <c r="AE88" s="12" t="n">
-        <v>2085.04</v>
+        <v>17086.12</v>
       </c>
       <c r="AF88" s="12" t="n">
         <v>0</v>
@@ -36401,10 +36407,10 @@
         <v>0</v>
       </c>
       <c r="AJ88" s="12" t="n">
-        <v>34201.66</v>
+        <v>0</v>
       </c>
       <c r="AK88" s="12" t="n">
-        <v>5256.19</v>
+        <v>0</v>
       </c>
       <c r="AL88" s="14" t="s">
         <v>78</v>
@@ -36455,7 +36461,7 @@
         <v>78</v>
       </c>
       <c r="BB88" s="10" t="s">
-        <v>427</v>
+        <v>95</v>
       </c>
       <c r="BC88" s="14" t="s">
         <v>79</v>
@@ -36505,10 +36511,10 @@
     </row>
     <row r="89" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="n">
-        <v>312087</v>
+        <v>312088</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>281</v>
+        <v>421</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="9"/>
@@ -36532,25 +36538,25 @@
         <v>74</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>252020.26</v>
+        <v>29227.24</v>
       </c>
       <c r="M89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N89" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O89" s="12" t="n">
-        <v>244087.41</v>
+        <v>28394.25</v>
       </c>
       <c r="P89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q89" s="13" t="n">
-        <v>52.271424</v>
+        <v>11.282565</v>
       </c>
       <c r="R89" s="12" t="n">
-        <v>5617.51</v>
+        <v>131.37</v>
       </c>
       <c r="S89" s="12" t="n">
         <v>0</v>
@@ -36562,19 +36568,19 @@
         <v>76</v>
       </c>
       <c r="V89" s="12" t="n">
-        <v>206003.7</v>
+        <v>23964.03</v>
       </c>
       <c r="W89" s="12" t="n">
-        <v>206.02</v>
+        <v>23.97</v>
       </c>
       <c r="X89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y89" s="12" t="n">
-        <v>1854.03</v>
+        <v>215.67</v>
       </c>
       <c r="Z89" s="12" t="n">
-        <v>55.12</v>
+        <v>42</v>
       </c>
       <c r="AA89" s="9" t="s">
         <v>77</v>
@@ -36583,13 +36589,13 @@
         <v>303</v>
       </c>
       <c r="AC89" s="12" t="n">
-        <v>7932.85</v>
+        <v>0</v>
       </c>
       <c r="AD89" s="12" t="n">
-        <v>244087.41</v>
+        <v>28394.25</v>
       </c>
       <c r="AE89" s="12" t="n">
-        <v>17086.12</v>
+        <v>1987.6</v>
       </c>
       <c r="AF89" s="12" t="n">
         <v>0</v>
@@ -36604,10 +36610,10 @@
         <v>0</v>
       </c>
       <c r="AJ89" s="12" t="n">
-        <v>0</v>
+        <v>5420.2</v>
       </c>
       <c r="AK89" s="12" t="n">
-        <v>0</v>
+        <v>832.99</v>
       </c>
       <c r="AL89" s="14" t="s">
         <v>78</v>
@@ -36708,10 +36714,10 @@
     </row>
     <row r="90" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="n">
-        <v>312088</v>
+        <v>312089</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="9"/>
@@ -36729,13 +36735,13 @@
         <v>303</v>
       </c>
       <c r="J90" s="9" t="s">
-        <v>166</v>
+        <v>415</v>
       </c>
       <c r="K90" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>29227.24</v>
+        <v>56914</v>
       </c>
       <c r="M90" s="12" t="n">
         <v>0</v>
@@ -36744,16 +36750,16 @@
         <v>2</v>
       </c>
       <c r="O90" s="12" t="n">
-        <v>28394.25</v>
+        <v>56914</v>
       </c>
       <c r="P90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="13" t="n">
-        <v>11.282565</v>
+        <v>72.73668</v>
       </c>
       <c r="R90" s="12" t="n">
-        <v>131.37</v>
+        <v>5030.72</v>
       </c>
       <c r="S90" s="12" t="n">
         <v>0</v>
@@ -36765,19 +36771,19 @@
         <v>76</v>
       </c>
       <c r="V90" s="12" t="n">
-        <v>23964.03</v>
+        <v>48033.99</v>
       </c>
       <c r="W90" s="12" t="n">
-        <v>23.97</v>
+        <v>48.03</v>
       </c>
       <c r="X90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y90" s="12" t="n">
-        <v>215.67</v>
+        <v>432.3</v>
       </c>
       <c r="Z90" s="12" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="AA90" s="9" t="s">
         <v>77</v>
@@ -36789,10 +36795,10 @@
         <v>0</v>
       </c>
       <c r="AD90" s="12" t="n">
-        <v>28394.25</v>
+        <v>56914</v>
       </c>
       <c r="AE90" s="12" t="n">
-        <v>1987.6</v>
+        <v>3983.98</v>
       </c>
       <c r="AF90" s="12" t="n">
         <v>0</v>
@@ -36807,10 +36813,10 @@
         <v>0</v>
       </c>
       <c r="AJ90" s="12" t="n">
-        <v>5420.2</v>
+        <v>0</v>
       </c>
       <c r="AK90" s="12" t="n">
-        <v>832.99</v>
+        <v>0</v>
       </c>
       <c r="AL90" s="14" t="s">
         <v>78</v>
@@ -36911,10 +36917,10 @@
     </row>
     <row r="91" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="n">
-        <v>312089</v>
+        <v>312090</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="9"/>
@@ -36932,31 +36938,31 @@
         <v>303</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>396</v>
+        <v>166</v>
       </c>
       <c r="K91" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>56914</v>
+        <v>10444.5</v>
       </c>
       <c r="M91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N91" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O91" s="12" t="n">
-        <v>56914</v>
+        <v>10444.5</v>
       </c>
       <c r="P91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q91" s="13" t="n">
-        <v>72.73668</v>
+        <v>13.69989</v>
       </c>
       <c r="R91" s="12" t="n">
-        <v>5030.72</v>
+        <v>341.74</v>
       </c>
       <c r="S91" s="12" t="n">
         <v>0</v>
@@ -36968,19 +36974,19 @@
         <v>76</v>
       </c>
       <c r="V91" s="12" t="n">
-        <v>48033.99</v>
+        <v>8814.89</v>
       </c>
       <c r="W91" s="12" t="n">
-        <v>48.03</v>
+        <v>8.81</v>
       </c>
       <c r="X91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y91" s="12" t="n">
-        <v>432.3</v>
+        <v>79.33</v>
       </c>
       <c r="Z91" s="12" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AA91" s="9" t="s">
         <v>77</v>
@@ -36992,10 +36998,10 @@
         <v>0</v>
       </c>
       <c r="AD91" s="12" t="n">
-        <v>56914</v>
+        <v>10444.5</v>
       </c>
       <c r="AE91" s="12" t="n">
-        <v>3983.98</v>
+        <v>731.12</v>
       </c>
       <c r="AF91" s="12" t="n">
         <v>0</v>
@@ -37114,10 +37120,10 @@
     </row>
     <row r="92" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="n">
-        <v>312090</v>
+        <v>312091</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="9"/>
@@ -37141,7 +37147,7 @@
         <v>74</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>10444.5</v>
+        <v>3309.3</v>
       </c>
       <c r="M92" s="12" t="n">
         <v>0</v>
@@ -37150,16 +37156,16 @@
         <v>1</v>
       </c>
       <c r="O92" s="12" t="n">
-        <v>10444.5</v>
+        <v>2685.55</v>
       </c>
       <c r="P92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q92" s="13" t="n">
-        <v>13.69989</v>
+        <v>8.18892</v>
       </c>
       <c r="R92" s="12" t="n">
-        <v>341.74</v>
+        <v>94.34</v>
       </c>
       <c r="S92" s="12" t="n">
         <v>0</v>
@@ -37171,16 +37177,16 @@
         <v>76</v>
       </c>
       <c r="V92" s="12" t="n">
-        <v>8814.89</v>
+        <v>2266.54</v>
       </c>
       <c r="W92" s="12" t="n">
-        <v>8.81</v>
+        <v>2.27</v>
       </c>
       <c r="X92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y92" s="12" t="n">
-        <v>79.33</v>
+        <v>20.4</v>
       </c>
       <c r="Z92" s="12" t="n">
         <v>42</v>
@@ -37195,10 +37201,10 @@
         <v>0</v>
       </c>
       <c r="AD92" s="12" t="n">
-        <v>10444.5</v>
+        <v>2685.55</v>
       </c>
       <c r="AE92" s="12" t="n">
-        <v>731.12</v>
+        <v>187.99</v>
       </c>
       <c r="AF92" s="12" t="n">
         <v>0</v>
@@ -37213,10 +37219,10 @@
         <v>0</v>
       </c>
       <c r="AJ92" s="12" t="n">
-        <v>0</v>
+        <v>4058.67</v>
       </c>
       <c r="AK92" s="12" t="n">
-        <v>0</v>
+        <v>623.75</v>
       </c>
       <c r="AL92" s="14" t="s">
         <v>78</v>
@@ -37267,7 +37273,7 @@
         <v>78</v>
       </c>
       <c r="BB92" s="10" t="s">
-        <v>95</v>
+        <v>424</v>
       </c>
       <c r="BC92" s="14" t="s">
         <v>79</v>
@@ -37317,10 +37323,10 @@
     </row>
     <row r="93" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="n">
-        <v>312091</v>
+        <v>312092</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>424</v>
+        <v>306</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="9"/>
@@ -37344,7 +37350,7 @@
         <v>74</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>3309.3</v>
+        <v>4100.89</v>
       </c>
       <c r="M93" s="12" t="n">
         <v>0</v>
@@ -37353,16 +37359,16 @@
         <v>1</v>
       </c>
       <c r="O93" s="12" t="n">
-        <v>2685.55</v>
+        <v>3850.6</v>
       </c>
       <c r="P93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q93" s="13" t="n">
-        <v>8.18892</v>
+        <v>0.04222</v>
       </c>
       <c r="R93" s="12" t="n">
-        <v>94.34</v>
+        <v>13.9</v>
       </c>
       <c r="S93" s="12" t="n">
         <v>0</v>
@@ -37374,19 +37380,19 @@
         <v>76</v>
       </c>
       <c r="V93" s="12" t="n">
-        <v>2266.54</v>
+        <v>3354.65</v>
       </c>
       <c r="W93" s="12" t="n">
-        <v>2.27</v>
+        <v>3.35</v>
       </c>
       <c r="X93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y93" s="12" t="n">
-        <v>20.4</v>
+        <v>30.19</v>
       </c>
       <c r="Z93" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AA93" s="9" t="s">
         <v>77</v>
@@ -37395,13 +37401,13 @@
         <v>303</v>
       </c>
       <c r="AC93" s="12" t="n">
-        <v>0</v>
+        <v>250.29</v>
       </c>
       <c r="AD93" s="12" t="n">
-        <v>2685.55</v>
+        <v>3850.6</v>
       </c>
       <c r="AE93" s="12" t="n">
-        <v>187.99</v>
+        <v>154.02</v>
       </c>
       <c r="AF93" s="12" t="n">
         <v>0</v>
@@ -37416,10 +37422,10 @@
         <v>0</v>
       </c>
       <c r="AJ93" s="12" t="n">
-        <v>4058.67</v>
+        <v>0</v>
       </c>
       <c r="AK93" s="12" t="n">
-        <v>623.75</v>
+        <v>0</v>
       </c>
       <c r="AL93" s="14" t="s">
         <v>78</v>
@@ -37470,7 +37476,7 @@
         <v>78</v>
       </c>
       <c r="BB93" s="10" t="s">
-        <v>427</v>
+        <v>95</v>
       </c>
       <c r="BC93" s="14" t="s">
         <v>79</v>
@@ -37520,10 +37526,10 @@
     </row>
     <row r="94" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="n">
-        <v>312092</v>
+        <v>312093</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>306</v>
+        <v>421</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="9"/>
@@ -37547,7 +37553,7 @@
         <v>74</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>4100.89</v>
+        <v>6877.54</v>
       </c>
       <c r="M94" s="12" t="n">
         <v>0</v>
@@ -37556,16 +37562,16 @@
         <v>1</v>
       </c>
       <c r="O94" s="12" t="n">
-        <v>3850.6</v>
+        <v>5581.24</v>
       </c>
       <c r="P94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="13" t="n">
-        <v>0.04222</v>
+        <v>21.586392</v>
       </c>
       <c r="R94" s="12" t="n">
-        <v>13.9</v>
+        <v>229.23</v>
       </c>
       <c r="S94" s="12" t="n">
         <v>0</v>
@@ -37577,19 +37583,19 @@
         <v>76</v>
       </c>
       <c r="V94" s="12" t="n">
-        <v>3354.65</v>
+        <v>4710.43</v>
       </c>
       <c r="W94" s="12" t="n">
-        <v>3.35</v>
+        <v>4.71</v>
       </c>
       <c r="X94" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y94" s="12" t="n">
-        <v>30.19</v>
+        <v>42.39</v>
       </c>
       <c r="Z94" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AA94" s="9" t="s">
         <v>77</v>
@@ -37598,13 +37604,13 @@
         <v>303</v>
       </c>
       <c r="AC94" s="12" t="n">
-        <v>250.29</v>
+        <v>0</v>
       </c>
       <c r="AD94" s="12" t="n">
-        <v>3850.6</v>
+        <v>5581.24</v>
       </c>
       <c r="AE94" s="12" t="n">
-        <v>154.02</v>
+        <v>390.69</v>
       </c>
       <c r="AF94" s="12" t="n">
         <v>0</v>
@@ -37619,10 +37625,10 @@
         <v>0</v>
       </c>
       <c r="AJ94" s="12" t="n">
-        <v>0</v>
+        <v>8434.93</v>
       </c>
       <c r="AK94" s="12" t="n">
-        <v>0</v>
+        <v>1296.3</v>
       </c>
       <c r="AL94" s="14" t="s">
         <v>78</v>
@@ -37673,7 +37679,7 @@
         <v>78</v>
       </c>
       <c r="BB94" s="10" t="s">
-        <v>95</v>
+        <v>424</v>
       </c>
       <c r="BC94" s="14" t="s">
         <v>79</v>
@@ -37723,10 +37729,10 @@
     </row>
     <row r="95" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="n">
-        <v>312093</v>
+        <v>312094</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
@@ -37750,25 +37756,25 @@
         <v>74</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>6877.54</v>
+        <v>22657.14</v>
       </c>
       <c r="M95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N95" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O95" s="12" t="n">
-        <v>5581.24</v>
+        <v>18386.65</v>
       </c>
       <c r="P95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q95" s="13" t="n">
-        <v>21.586392</v>
+        <v>56.35191</v>
       </c>
       <c r="R95" s="12" t="n">
-        <v>229.23</v>
+        <v>624.76</v>
       </c>
       <c r="S95" s="12" t="n">
         <v>0</v>
@@ -37780,16 +37786,16 @@
         <v>76</v>
       </c>
       <c r="V95" s="12" t="n">
-        <v>4710.43</v>
+        <v>15517.88</v>
       </c>
       <c r="W95" s="12" t="n">
-        <v>4.71</v>
+        <v>15.52</v>
       </c>
       <c r="X95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y95" s="12" t="n">
-        <v>42.39</v>
+        <v>139.67</v>
       </c>
       <c r="Z95" s="12" t="n">
         <v>42</v>
@@ -37804,10 +37810,10 @@
         <v>0</v>
       </c>
       <c r="AD95" s="12" t="n">
-        <v>5581.24</v>
+        <v>18386.65</v>
       </c>
       <c r="AE95" s="12" t="n">
-        <v>390.69</v>
+        <v>1287.06</v>
       </c>
       <c r="AF95" s="12" t="n">
         <v>0</v>
@@ -37822,10 +37828,10 @@
         <v>0</v>
       </c>
       <c r="AJ95" s="12" t="n">
-        <v>8434.93</v>
+        <v>27787.75</v>
       </c>
       <c r="AK95" s="12" t="n">
-        <v>1296.3</v>
+        <v>4270.49</v>
       </c>
       <c r="AL95" s="14" t="s">
         <v>78</v>
@@ -37876,7 +37882,7 @@
         <v>78</v>
       </c>
       <c r="BB95" s="10" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="BC95" s="14" t="s">
         <v>79</v>
@@ -37926,10 +37932,10 @@
     </row>
     <row r="96" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="n">
-        <v>312094</v>
+        <v>312095</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>424</v>
+        <v>306</v>
       </c>
       <c r="C96" s="9"/>
       <c r="D96" s="9"/>
@@ -37953,25 +37959,25 @@
         <v>74</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>22657.14</v>
+        <v>308625.52</v>
       </c>
       <c r="M96" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N96" s="12" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="O96" s="12" t="n">
-        <v>18386.65</v>
+        <v>307025.88</v>
       </c>
       <c r="P96" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q96" s="13" t="n">
-        <v>56.35191</v>
+        <v>6.620778</v>
       </c>
       <c r="R96" s="12" t="n">
-        <v>624.76</v>
+        <v>1053.44</v>
       </c>
       <c r="S96" s="12" t="n">
         <v>0</v>
@@ -37983,19 +37989,19 @@
         <v>76</v>
       </c>
       <c r="V96" s="12" t="n">
-        <v>15517.88</v>
+        <v>259891.09</v>
       </c>
       <c r="W96" s="12" t="n">
-        <v>15.52</v>
+        <v>259.89</v>
       </c>
       <c r="X96" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y96" s="12" t="n">
-        <v>139.67</v>
+        <v>2339.05</v>
       </c>
       <c r="Z96" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AA96" s="9" t="s">
         <v>77</v>
@@ -38004,13 +38010,13 @@
         <v>303</v>
       </c>
       <c r="AC96" s="12" t="n">
-        <v>0</v>
+        <v>1599.64</v>
       </c>
       <c r="AD96" s="12" t="n">
-        <v>18386.65</v>
+        <v>302933.08</v>
       </c>
       <c r="AE96" s="12" t="n">
-        <v>1287.06</v>
+        <v>20644.58</v>
       </c>
       <c r="AF96" s="12" t="n">
         <v>0</v>
@@ -38025,10 +38031,10 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="12" t="n">
-        <v>27787.75</v>
+        <v>0</v>
       </c>
       <c r="AK96" s="12" t="n">
-        <v>4270.49</v>
+        <v>0</v>
       </c>
       <c r="AL96" s="14" t="s">
         <v>78</v>
@@ -38079,7 +38085,7 @@
         <v>78</v>
       </c>
       <c r="BB96" s="10" t="s">
-        <v>427</v>
+        <v>95</v>
       </c>
       <c r="BC96" s="14" t="s">
         <v>79</v>
@@ -38129,7 +38135,7 @@
     </row>
     <row r="97" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="n">
-        <v>312095</v>
+        <v>312096</v>
       </c>
       <c r="B97" s="9" t="s">
         <v>306</v>
@@ -38150,55 +38156,55 @@
         <v>303</v>
       </c>
       <c r="J97" s="9" t="s">
-        <v>166</v>
+        <v>457</v>
       </c>
       <c r="K97" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>308625.52</v>
+        <v>1688.37</v>
       </c>
       <c r="M97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N97" s="12" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="O97" s="12" t="n">
-        <v>307025.88</v>
+        <v>1585.32</v>
       </c>
       <c r="P97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q97" s="13" t="n">
-        <v>6.620778</v>
+        <v>0.184548</v>
       </c>
       <c r="R97" s="12" t="n">
-        <v>1053.44</v>
+        <v>6.73</v>
       </c>
       <c r="S97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T97" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="U97" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V97" s="12" t="n">
-        <v>259891.09</v>
+        <v>1381.14</v>
       </c>
       <c r="W97" s="12" t="n">
-        <v>259.89</v>
+        <v>1.38</v>
       </c>
       <c r="X97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y97" s="12" t="n">
-        <v>2339.05</v>
+        <v>12.43</v>
       </c>
       <c r="Z97" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="AA97" s="9" t="s">
         <v>77</v>
@@ -38207,13 +38213,13 @@
         <v>303</v>
       </c>
       <c r="AC97" s="12" t="n">
-        <v>1599.64</v>
+        <v>103.05</v>
       </c>
       <c r="AD97" s="12" t="n">
-        <v>302933.08</v>
+        <v>1585.32</v>
       </c>
       <c r="AE97" s="12" t="n">
-        <v>20644.58</v>
+        <v>63.41</v>
       </c>
       <c r="AF97" s="12" t="n">
         <v>0</v>
@@ -38318,7 +38324,7 @@
         <v>73</v>
       </c>
       <c r="BN97" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="BO97" s="9" t="s">
         <v>79</v>
@@ -38332,7 +38338,7 @@
     </row>
     <row r="98" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="n">
-        <v>312096</v>
+        <v>312097</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>306</v>
@@ -38341,7 +38347,7 @@
       <c r="D98" s="9"/>
       <c r="E98" s="9"/>
       <c r="F98" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>91</v>
@@ -38353,13 +38359,13 @@
         <v>303</v>
       </c>
       <c r="J98" s="9" t="s">
-        <v>460</v>
+        <v>166</v>
       </c>
       <c r="K98" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>1688.37</v>
+        <v>4350.48</v>
       </c>
       <c r="M98" s="12" t="n">
         <v>0</v>
@@ -38368,16 +38374,16 @@
         <v>1</v>
       </c>
       <c r="O98" s="12" t="n">
-        <v>1585.32</v>
+        <v>4350.48</v>
       </c>
       <c r="P98" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q98" s="13" t="n">
-        <v>0.184548</v>
+        <v>0.005328</v>
       </c>
       <c r="R98" s="12" t="n">
-        <v>6.73</v>
+        <v>10.13</v>
       </c>
       <c r="S98" s="12" t="n">
         <v>0</v>
@@ -38389,19 +38395,19 @@
         <v>76</v>
       </c>
       <c r="V98" s="12" t="n">
-        <v>1381.14</v>
+        <v>3671.7</v>
       </c>
       <c r="W98" s="12" t="n">
-        <v>1.38</v>
+        <v>3.67</v>
       </c>
       <c r="X98" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y98" s="12" t="n">
-        <v>12.43</v>
+        <v>33.05</v>
       </c>
       <c r="Z98" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="AA98" s="9" t="s">
         <v>77</v>
@@ -38410,13 +38416,13 @@
         <v>303</v>
       </c>
       <c r="AC98" s="12" t="n">
-        <v>103.05</v>
+        <v>0</v>
       </c>
       <c r="AD98" s="12" t="n">
-        <v>1585.32</v>
+        <v>4350.48</v>
       </c>
       <c r="AE98" s="12" t="n">
-        <v>63.41</v>
+        <v>304.53</v>
       </c>
       <c r="AF98" s="12" t="n">
         <v>0</v>
@@ -38535,7 +38541,7 @@
     </row>
     <row r="99" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="n">
-        <v>312097</v>
+        <v>312098</v>
       </c>
       <c r="B99" s="9" t="s">
         <v>306</v>
@@ -38562,7 +38568,7 @@
         <v>74</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>4350.48</v>
+        <v>2724.78</v>
       </c>
       <c r="M99" s="12" t="n">
         <v>0</v>
@@ -38571,16 +38577,16 @@
         <v>1</v>
       </c>
       <c r="O99" s="12" t="n">
-        <v>4350.48</v>
+        <v>2558.48</v>
       </c>
       <c r="P99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q99" s="13" t="n">
-        <v>0.005328</v>
+        <v>0.002296</v>
       </c>
       <c r="R99" s="12" t="n">
-        <v>10.13</v>
+        <v>1.58</v>
       </c>
       <c r="S99" s="12" t="n">
         <v>0</v>
@@ -38592,16 +38598,16 @@
         <v>76</v>
       </c>
       <c r="V99" s="12" t="n">
-        <v>3671.7</v>
+        <v>2159.3</v>
       </c>
       <c r="W99" s="12" t="n">
-        <v>3.67</v>
+        <v>2.16</v>
       </c>
       <c r="X99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y99" s="12" t="n">
-        <v>33.05</v>
+        <v>19.43</v>
       </c>
       <c r="Z99" s="12" t="n">
         <v>28</v>
@@ -38613,13 +38619,13 @@
         <v>303</v>
       </c>
       <c r="AC99" s="12" t="n">
-        <v>0</v>
+        <v>166.3</v>
       </c>
       <c r="AD99" s="12" t="n">
-        <v>4350.48</v>
+        <v>2558.48</v>
       </c>
       <c r="AE99" s="12" t="n">
-        <v>304.53</v>
+        <v>179.09</v>
       </c>
       <c r="AF99" s="12" t="n">
         <v>0</v>
@@ -38738,7 +38744,7 @@
     </row>
     <row r="100" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="n">
-        <v>312098</v>
+        <v>312099</v>
       </c>
       <c r="B100" s="9" t="s">
         <v>306</v>
@@ -38765,7 +38771,7 @@
         <v>74</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>2724.78</v>
+        <v>34038</v>
       </c>
       <c r="M100" s="12" t="n">
         <v>0</v>
@@ -38774,16 +38780,16 @@
         <v>1</v>
       </c>
       <c r="O100" s="12" t="n">
-        <v>2558.48</v>
+        <v>34038</v>
       </c>
       <c r="P100" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q100" s="13" t="n">
-        <v>0.002296</v>
+        <v>225</v>
       </c>
       <c r="R100" s="12" t="n">
-        <v>1.58</v>
+        <v>270</v>
       </c>
       <c r="S100" s="12" t="n">
         <v>0</v>
@@ -38795,16 +38801,16 @@
         <v>76</v>
       </c>
       <c r="V100" s="12" t="n">
-        <v>2159.3</v>
+        <v>29301.73</v>
       </c>
       <c r="W100" s="12" t="n">
-        <v>2.16</v>
+        <v>29.3</v>
       </c>
       <c r="X100" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y100" s="12" t="n">
-        <v>19.43</v>
+        <v>263.72</v>
       </c>
       <c r="Z100" s="12" t="n">
         <v>28</v>
@@ -38816,13 +38822,13 @@
         <v>303</v>
       </c>
       <c r="AC100" s="12" t="n">
-        <v>166.3</v>
+        <v>0</v>
       </c>
       <c r="AD100" s="12" t="n">
-        <v>2558.48</v>
+        <v>24994.1</v>
       </c>
       <c r="AE100" s="12" t="n">
-        <v>179.09</v>
+        <v>1749.59</v>
       </c>
       <c r="AF100" s="12" t="n">
         <v>0</v>
@@ -38941,7 +38947,7 @@
     </row>
     <row r="101" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="n">
-        <v>312099</v>
+        <v>312100</v>
       </c>
       <c r="B101" s="9" t="s">
         <v>306</v>
@@ -38968,7 +38974,7 @@
         <v>74</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>34038</v>
+        <v>2537.78</v>
       </c>
       <c r="M101" s="12" t="n">
         <v>0</v>
@@ -38977,16 +38983,16 @@
         <v>1</v>
       </c>
       <c r="O101" s="12" t="n">
-        <v>34038</v>
+        <v>2537.78</v>
       </c>
       <c r="P101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q101" s="13" t="n">
-        <v>225</v>
+        <v>0.003108</v>
       </c>
       <c r="R101" s="12" t="n">
-        <v>270</v>
+        <v>5.91</v>
       </c>
       <c r="S101" s="12" t="n">
         <v>0</v>
@@ -38998,16 +39004,16 @@
         <v>76</v>
       </c>
       <c r="V101" s="12" t="n">
-        <v>29301.73</v>
+        <v>2141.83</v>
       </c>
       <c r="W101" s="12" t="n">
-        <v>29.3</v>
+        <v>2.14</v>
       </c>
       <c r="X101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y101" s="12" t="n">
-        <v>263.72</v>
+        <v>19.28</v>
       </c>
       <c r="Z101" s="12" t="n">
         <v>28</v>
@@ -39022,10 +39028,10 @@
         <v>0</v>
       </c>
       <c r="AD101" s="12" t="n">
-        <v>24994.1</v>
+        <v>2537.78</v>
       </c>
       <c r="AE101" s="12" t="n">
-        <v>1749.59</v>
+        <v>177.64</v>
       </c>
       <c r="AF101" s="12" t="n">
         <v>0</v>
@@ -39144,7 +39150,7 @@
     </row>
     <row r="102" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="n">
-        <v>312100</v>
+        <v>312101</v>
       </c>
       <c r="B102" s="9" t="s">
         <v>306</v>
@@ -39165,13 +39171,13 @@
         <v>303</v>
       </c>
       <c r="J102" s="9" t="s">
-        <v>166</v>
+        <v>473</v>
       </c>
       <c r="K102" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>2537.78</v>
+        <v>15588.72</v>
       </c>
       <c r="M102" s="12" t="n">
         <v>0</v>
@@ -39180,40 +39186,40 @@
         <v>1</v>
       </c>
       <c r="O102" s="12" t="n">
-        <v>2537.78</v>
+        <v>15588.72</v>
       </c>
       <c r="P102" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q102" s="13" t="n">
-        <v>0.003108</v>
+        <v>0.173054</v>
       </c>
       <c r="R102" s="12" t="n">
-        <v>5.91</v>
+        <v>41.61</v>
       </c>
       <c r="S102" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T102" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="U102" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V102" s="12" t="n">
-        <v>2141.83</v>
+        <v>13156.49</v>
       </c>
       <c r="W102" s="12" t="n">
-        <v>2.14</v>
+        <v>13.16</v>
       </c>
       <c r="X102" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y102" s="12" t="n">
-        <v>19.28</v>
+        <v>118.41</v>
       </c>
       <c r="Z102" s="12" t="n">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="AA102" s="9" t="s">
         <v>77</v>
@@ -39225,10 +39231,10 @@
         <v>0</v>
       </c>
       <c r="AD102" s="12" t="n">
-        <v>2537.78</v>
+        <v>15588.72</v>
       </c>
       <c r="AE102" s="12" t="n">
-        <v>177.64</v>
+        <v>1091.21</v>
       </c>
       <c r="AF102" s="12" t="n">
         <v>0</v>
@@ -39333,7 +39339,7 @@
         <v>73</v>
       </c>
       <c r="BN102" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="BO102" s="9" t="s">
         <v>79</v>
@@ -39347,7 +39353,7 @@
     </row>
     <row r="103" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="n">
-        <v>312101</v>
+        <v>312102</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>306</v>
@@ -39356,7 +39362,7 @@
       <c r="D103" s="9"/>
       <c r="E103" s="9"/>
       <c r="F103" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G103" s="10" t="s">
         <v>91</v>
@@ -39368,13 +39374,13 @@
         <v>303</v>
       </c>
       <c r="J103" s="9" t="s">
-        <v>476</v>
+        <v>166</v>
       </c>
       <c r="K103" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>15588.72</v>
+        <v>1087.62</v>
       </c>
       <c r="M103" s="12" t="n">
         <v>0</v>
@@ -39383,16 +39389,16 @@
         <v>1</v>
       </c>
       <c r="O103" s="12" t="n">
-        <v>15588.72</v>
+        <v>1087.62</v>
       </c>
       <c r="P103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q103" s="13" t="n">
-        <v>0.173054</v>
+        <v>0.001332</v>
       </c>
       <c r="R103" s="12" t="n">
-        <v>41.61</v>
+        <v>2.53</v>
       </c>
       <c r="S103" s="12" t="n">
         <v>0</v>
@@ -39404,19 +39410,19 @@
         <v>76</v>
       </c>
       <c r="V103" s="12" t="n">
-        <v>13156.49</v>
+        <v>917.93</v>
       </c>
       <c r="W103" s="12" t="n">
-        <v>13.16</v>
+        <v>0.92</v>
       </c>
       <c r="X103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y103" s="12" t="n">
-        <v>118.41</v>
+        <v>8.26</v>
       </c>
       <c r="Z103" s="12" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="AA103" s="9" t="s">
         <v>77</v>
@@ -39428,10 +39434,10 @@
         <v>0</v>
       </c>
       <c r="AD103" s="12" t="n">
-        <v>15588.72</v>
+        <v>1087.62</v>
       </c>
       <c r="AE103" s="12" t="n">
-        <v>1091.21</v>
+        <v>76.13</v>
       </c>
       <c r="AF103" s="12" t="n">
         <v>0</v>
@@ -39550,7 +39556,7 @@
     </row>
     <row r="104" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="n">
-        <v>312102</v>
+        <v>312103</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>306</v>
@@ -39577,25 +39583,25 @@
         <v>74</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>1087.62</v>
+        <v>42627.7</v>
       </c>
       <c r="M104" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N104" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O104" s="12" t="n">
-        <v>1087.62</v>
+        <v>42627.7</v>
       </c>
       <c r="P104" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q104" s="13" t="n">
-        <v>0.001332</v>
+        <v>0.046062</v>
       </c>
       <c r="R104" s="12" t="n">
-        <v>2.53</v>
+        <v>120.93</v>
       </c>
       <c r="S104" s="12" t="n">
         <v>0</v>
@@ -39607,16 +39613,16 @@
         <v>76</v>
       </c>
       <c r="V104" s="12" t="n">
-        <v>917.93</v>
+        <v>36954.92</v>
       </c>
       <c r="W104" s="12" t="n">
-        <v>0.92</v>
+        <v>36.96</v>
       </c>
       <c r="X104" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y104" s="12" t="n">
-        <v>8.26</v>
+        <v>332.59</v>
       </c>
       <c r="Z104" s="12" t="n">
         <v>28</v>
@@ -39631,10 +39637,10 @@
         <v>0</v>
       </c>
       <c r="AD104" s="12" t="n">
-        <v>1087.62</v>
+        <v>42627.7</v>
       </c>
       <c r="AE104" s="12" t="n">
-        <v>76.13</v>
+        <v>1906.04</v>
       </c>
       <c r="AF104" s="12" t="n">
         <v>0</v>
@@ -39753,10 +39759,10 @@
     </row>
     <row r="105" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="n">
-        <v>312103</v>
+        <v>312105</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="9"/>
@@ -39774,55 +39780,55 @@
         <v>303</v>
       </c>
       <c r="J105" s="9" t="s">
-        <v>166</v>
+        <v>483</v>
       </c>
       <c r="K105" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>42627.7</v>
+        <v>6406.01</v>
       </c>
       <c r="M105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N105" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O105" s="12" t="n">
-        <v>42627.7</v>
+        <v>6126.22</v>
       </c>
       <c r="P105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q105" s="13" t="n">
-        <v>0.046062</v>
+        <v>0.07496</v>
       </c>
       <c r="R105" s="12" t="n">
-        <v>120.93</v>
+        <v>270.7</v>
       </c>
       <c r="S105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T105" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="U105" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V105" s="12" t="n">
-        <v>36954.92</v>
+        <v>5204.16</v>
       </c>
       <c r="W105" s="12" t="n">
-        <v>36.96</v>
+        <v>5.2</v>
       </c>
       <c r="X105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y105" s="12" t="n">
-        <v>332.59</v>
+        <v>46.84</v>
       </c>
       <c r="Z105" s="12" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="AA105" s="9" t="s">
         <v>77</v>
@@ -39831,13 +39837,13 @@
         <v>303</v>
       </c>
       <c r="AC105" s="12" t="n">
-        <v>0</v>
+        <v>279.79</v>
       </c>
       <c r="AD105" s="12" t="n">
-        <v>42627.7</v>
+        <v>6126.22</v>
       </c>
       <c r="AE105" s="12" t="n">
-        <v>1906.04</v>
+        <v>391.6</v>
       </c>
       <c r="AF105" s="12" t="n">
         <v>0</v>
@@ -39942,7 +39948,7 @@
         <v>73</v>
       </c>
       <c r="BN105" s="9" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="BO105" s="9" t="s">
         <v>79</v>
@@ -39956,19 +39962,19 @@
     </row>
     <row r="106" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="n">
-        <v>312105</v>
+        <v>312108</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>265</v>
+        <v>126</v>
       </c>
       <c r="C106" s="9"/>
       <c r="D106" s="9"/>
       <c r="E106" s="9"/>
       <c r="F106" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>291</v>
@@ -39977,31 +39983,31 @@
         <v>303</v>
       </c>
       <c r="J106" s="9" t="s">
-        <v>486</v>
+        <v>166</v>
       </c>
       <c r="K106" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>6406.01</v>
+        <v>18494.18</v>
       </c>
       <c r="M106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N106" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O106" s="12" t="n">
-        <v>6126.22</v>
+        <v>17605.3</v>
       </c>
       <c r="P106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q106" s="13" t="n">
-        <v>0.07496</v>
+        <v>0.19307</v>
       </c>
       <c r="R106" s="12" t="n">
-        <v>270.7</v>
+        <v>764.34</v>
       </c>
       <c r="S106" s="12" t="n">
         <v>0</v>
@@ -40013,19 +40019,19 @@
         <v>76</v>
       </c>
       <c r="V106" s="12" t="n">
-        <v>5204.16</v>
+        <v>14858.1</v>
       </c>
       <c r="W106" s="12" t="n">
-        <v>5.2</v>
+        <v>14.86</v>
       </c>
       <c r="X106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y106" s="12" t="n">
-        <v>46.84</v>
+        <v>133.72</v>
       </c>
       <c r="Z106" s="12" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="AA106" s="9" t="s">
         <v>77</v>
@@ -40034,13 +40040,13 @@
         <v>303</v>
       </c>
       <c r="AC106" s="12" t="n">
-        <v>279.79</v>
+        <v>888.88</v>
       </c>
       <c r="AD106" s="12" t="n">
-        <v>6126.22</v>
+        <v>17605.3</v>
       </c>
       <c r="AE106" s="12" t="n">
-        <v>391.6</v>
+        <v>1232.37</v>
       </c>
       <c r="AF106" s="12" t="n">
         <v>0</v>
@@ -40159,19 +40165,19 @@
     </row>
     <row r="107" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="n">
-        <v>312108</v>
+        <v>312112</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>126</v>
+        <v>489</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="9"/>
       <c r="E107" s="9"/>
       <c r="F107" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>128</v>
+        <v>491</v>
       </c>
       <c r="H107" s="9" t="s">
         <v>291</v>
@@ -40186,49 +40192,49 @@
         <v>74</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>18494.18</v>
+        <v>830.49</v>
       </c>
       <c r="M107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N107" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O107" s="12" t="n">
-        <v>17605.3</v>
+        <v>756.71</v>
       </c>
       <c r="P107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q107" s="13" t="n">
-        <v>0.19307</v>
+        <v>0.068075</v>
       </c>
       <c r="R107" s="12" t="n">
-        <v>764.34</v>
+        <v>2.5</v>
       </c>
       <c r="S107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T107" s="14" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="U107" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V107" s="12" t="n">
-        <v>14858.1</v>
+        <v>659.24</v>
       </c>
       <c r="W107" s="12" t="n">
-        <v>14.86</v>
+        <v>0.66</v>
       </c>
       <c r="X107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y107" s="12" t="n">
-        <v>133.72</v>
+        <v>5.93</v>
       </c>
       <c r="Z107" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="AA107" s="9" t="s">
         <v>77</v>
@@ -40237,13 +40243,13 @@
         <v>303</v>
       </c>
       <c r="AC107" s="12" t="n">
-        <v>888.88</v>
+        <v>73.78</v>
       </c>
       <c r="AD107" s="12" t="n">
-        <v>17605.3</v>
+        <v>756.71</v>
       </c>
       <c r="AE107" s="12" t="n">
-        <v>1232.37</v>
+        <v>30.27</v>
       </c>
       <c r="AF107" s="12" t="n">
         <v>0</v>
@@ -40348,7 +40354,7 @@
         <v>73</v>
       </c>
       <c r="BN107" s="9" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="BO107" s="9" t="s">
         <v>79</v>
@@ -40362,19 +40368,19 @@
     </row>
     <row r="108" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="n">
-        <v>312112</v>
+        <v>312113</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>492</v>
+        <v>281</v>
       </c>
       <c r="C108" s="9"/>
       <c r="D108" s="9"/>
       <c r="E108" s="9"/>
       <c r="F108" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>494</v>
+        <v>91</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>291</v>
@@ -40389,25 +40395,25 @@
         <v>74</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>830.49</v>
+        <v>60246.61</v>
       </c>
       <c r="M108" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N108" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O108" s="12" t="n">
-        <v>756.71</v>
+        <v>58350.22</v>
       </c>
       <c r="P108" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="13" t="n">
-        <v>0.068075</v>
+        <v>5.2822</v>
       </c>
       <c r="R108" s="12" t="n">
-        <v>2.5</v>
+        <v>878.99</v>
       </c>
       <c r="S108" s="12" t="n">
         <v>0</v>
@@ -40419,19 +40425,19 @@
         <v>76</v>
       </c>
       <c r="V108" s="12" t="n">
-        <v>659.24</v>
+        <v>49246.12</v>
       </c>
       <c r="W108" s="12" t="n">
-        <v>0.66</v>
+        <v>49.25</v>
       </c>
       <c r="X108" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y108" s="12" t="n">
-        <v>5.93</v>
+        <v>443.22</v>
       </c>
       <c r="Z108" s="12" t="n">
-        <v>56</v>
+        <v>55.12</v>
       </c>
       <c r="AA108" s="9" t="s">
         <v>77</v>
@@ -40440,13 +40446,13 @@
         <v>303</v>
       </c>
       <c r="AC108" s="12" t="n">
-        <v>73.78</v>
+        <v>1896.39</v>
       </c>
       <c r="AD108" s="12" t="n">
-        <v>756.71</v>
+        <v>58350.22</v>
       </c>
       <c r="AE108" s="12" t="n">
-        <v>30.27</v>
+        <v>4084.52</v>
       </c>
       <c r="AF108" s="12" t="n">
         <v>0</v>
@@ -40565,19 +40571,19 @@
     </row>
     <row r="109" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="n">
-        <v>312113</v>
+        <v>312114</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>281</v>
+        <v>497</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="9"/>
       <c r="E109" s="9"/>
       <c r="F109" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>91</v>
+        <v>200</v>
       </c>
       <c r="H109" s="9" t="s">
         <v>291</v>
@@ -40592,49 +40598,49 @@
         <v>74</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>60246.61</v>
+        <v>236735.23</v>
       </c>
       <c r="M109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N109" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O109" s="12" t="n">
-        <v>58350.22</v>
+        <v>229224.24</v>
       </c>
       <c r="P109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q109" s="13" t="n">
-        <v>5.2822</v>
+        <v>28.948</v>
       </c>
       <c r="R109" s="12" t="n">
-        <v>878.99</v>
+        <v>13671.46</v>
       </c>
       <c r="S109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T109" s="14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="U109" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V109" s="12" t="n">
-        <v>49246.12</v>
+        <v>193473.72</v>
       </c>
       <c r="W109" s="12" t="n">
-        <v>49.25</v>
+        <v>193.45</v>
       </c>
       <c r="X109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y109" s="12" t="n">
-        <v>443.22</v>
+        <v>1741.26</v>
       </c>
       <c r="Z109" s="12" t="n">
-        <v>55.12</v>
+        <v>28</v>
       </c>
       <c r="AA109" s="9" t="s">
         <v>77</v>
@@ -40643,13 +40649,13 @@
         <v>303</v>
       </c>
       <c r="AC109" s="12" t="n">
-        <v>1896.39</v>
+        <v>7510.99</v>
       </c>
       <c r="AD109" s="12" t="n">
-        <v>58350.22</v>
+        <v>229224.24</v>
       </c>
       <c r="AE109" s="12" t="n">
-        <v>4084.52</v>
+        <v>16030.07</v>
       </c>
       <c r="AF109" s="12" t="n">
         <v>0</v>
@@ -40754,7 +40760,7 @@
         <v>73</v>
       </c>
       <c r="BN109" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="BO109" s="9" t="s">
         <v>79</v>
@@ -40768,76 +40774,76 @@
     </row>
     <row r="110" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="n">
-        <v>312114</v>
+        <v>312115</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="9"/>
       <c r="E110" s="9"/>
       <c r="F110" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>200</v>
+        <v>91</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>291</v>
+        <v>503</v>
       </c>
       <c r="I110" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J110" s="9" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="K110" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>236735.23</v>
+        <v>28542</v>
       </c>
       <c r="M110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N110" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O110" s="12" t="n">
-        <v>229224.24</v>
+        <v>26800</v>
       </c>
       <c r="P110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q110" s="13" t="n">
-        <v>28.948</v>
+        <v>1.3156</v>
       </c>
       <c r="R110" s="12" t="n">
-        <v>13671.46</v>
+        <v>1000</v>
       </c>
       <c r="S110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T110" s="14" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="U110" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V110" s="12" t="n">
-        <v>193473.72</v>
+        <v>24014.28</v>
       </c>
       <c r="W110" s="12" t="n">
-        <v>193.45</v>
+        <v>24.01</v>
       </c>
       <c r="X110" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y110" s="12" t="n">
-        <v>1741.26</v>
+        <v>216.13</v>
       </c>
       <c r="Z110" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AA110" s="9" t="s">
         <v>77</v>
@@ -40846,13 +40852,13 @@
         <v>303</v>
       </c>
       <c r="AC110" s="12" t="n">
-        <v>7510.99</v>
+        <v>1742</v>
       </c>
       <c r="AD110" s="12" t="n">
-        <v>229224.24</v>
+        <v>26800</v>
       </c>
       <c r="AE110" s="12" t="n">
-        <v>16030.07</v>
+        <v>1876</v>
       </c>
       <c r="AF110" s="12" t="n">
         <v>0</v>
@@ -40957,7 +40963,7 @@
         <v>73</v>
       </c>
       <c r="BN110" s="9" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="BO110" s="9" t="s">
         <v>79</v>
@@ -40971,22 +40977,22 @@
     </row>
     <row r="111" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="n">
-        <v>312115</v>
+        <v>312116</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="9"/>
       <c r="E111" s="9"/>
       <c r="F111" s="9" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G111" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="I111" s="9" t="s">
         <v>303</v>
@@ -40998,46 +41004,46 @@
         <v>74</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>28542</v>
+        <v>4117.89</v>
       </c>
       <c r="M111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O111" s="12" t="n">
-        <v>26800</v>
+        <v>3956.86</v>
       </c>
       <c r="P111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q111" s="13" t="n">
-        <v>1.3156</v>
+        <v>0.297542</v>
       </c>
       <c r="R111" s="12" t="n">
-        <v>1000</v>
+        <v>93.58</v>
       </c>
       <c r="S111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T111" s="14" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="U111" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V111" s="12" t="n">
-        <v>24014.28</v>
+        <v>3956.86</v>
       </c>
       <c r="W111" s="12" t="n">
-        <v>24.01</v>
+        <v>3.96</v>
       </c>
       <c r="X111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y111" s="12" t="n">
-        <v>216.13</v>
+        <v>35.6</v>
       </c>
       <c r="Z111" s="12" t="n">
         <v>35</v>
@@ -41049,13 +41055,13 @@
         <v>303</v>
       </c>
       <c r="AC111" s="12" t="n">
-        <v>1742</v>
+        <v>161.03</v>
       </c>
       <c r="AD111" s="12" t="n">
-        <v>26800</v>
+        <v>3956.86</v>
       </c>
       <c r="AE111" s="12" t="n">
-        <v>1876</v>
+        <v>198.32</v>
       </c>
       <c r="AF111" s="12" t="n">
         <v>0</v>
@@ -41160,7 +41166,7 @@
         <v>73</v>
       </c>
       <c r="BN111" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="BO111" s="9" t="s">
         <v>79</v>
@@ -41174,10 +41180,10 @@
     </row>
     <row r="112" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="8" t="n">
-        <v>312116</v>
+        <v>312120</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>509</v>
+        <v>265</v>
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="9"/>
@@ -41189,61 +41195,61 @@
         <v>91</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>506</v>
+        <v>291</v>
       </c>
       <c r="I112" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J112" s="9" t="s">
-        <v>123</v>
+        <v>511</v>
       </c>
       <c r="K112" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>4117.89</v>
+        <v>20180.35</v>
       </c>
       <c r="M112" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N112" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O112" s="12" t="n">
-        <v>3956.86</v>
+        <v>18387.56</v>
       </c>
       <c r="P112" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="13" t="n">
-        <v>0.297542</v>
+        <v>0.907296</v>
       </c>
       <c r="R112" s="12" t="n">
-        <v>93.58</v>
+        <v>107.28</v>
       </c>
       <c r="S112" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T112" s="14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="U112" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V112" s="12" t="n">
-        <v>3956.86</v>
+        <v>15518.64</v>
       </c>
       <c r="W112" s="12" t="n">
-        <v>3.96</v>
+        <v>15.52</v>
       </c>
       <c r="X112" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y112" s="12" t="n">
-        <v>35.6</v>
+        <v>139.67</v>
       </c>
       <c r="Z112" s="12" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="AA112" s="9" t="s">
         <v>77</v>
@@ -41252,13 +41258,13 @@
         <v>303</v>
       </c>
       <c r="AC112" s="12" t="n">
-        <v>161.03</v>
+        <v>1792.79</v>
       </c>
       <c r="AD112" s="12" t="n">
-        <v>3956.86</v>
+        <v>18387.56</v>
       </c>
       <c r="AE112" s="12" t="n">
-        <v>198.32</v>
+        <v>1287.14</v>
       </c>
       <c r="AF112" s="12" t="n">
         <v>0</v>
@@ -41363,7 +41369,7 @@
         <v>73</v>
       </c>
       <c r="BN112" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="BO112" s="9" t="s">
         <v>79</v>
@@ -41377,52 +41383,52 @@
     </row>
     <row r="113" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="n">
-        <v>312120</v>
+        <v>312123</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="9"/>
       <c r="E113" s="9"/>
       <c r="F113" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>91</v>
+        <v>242</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>291</v>
+        <v>503</v>
       </c>
       <c r="I113" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J113" s="9" t="s">
-        <v>514</v>
+        <v>259</v>
       </c>
       <c r="K113" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>20180.35</v>
+        <v>383.64</v>
       </c>
       <c r="M113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N113" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O113" s="12" t="n">
-        <v>18387.56</v>
+        <v>383.64</v>
       </c>
       <c r="P113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q113" s="13" t="n">
-        <v>0.907296</v>
+        <v>0.017556</v>
       </c>
       <c r="R113" s="12" t="n">
-        <v>107.28</v>
+        <v>2.38</v>
       </c>
       <c r="S113" s="12" t="n">
         <v>0</v>
@@ -41434,19 +41440,19 @@
         <v>76</v>
       </c>
       <c r="V113" s="12" t="n">
-        <v>15518.64</v>
+        <v>323.78</v>
       </c>
       <c r="W113" s="12" t="n">
-        <v>15.52</v>
+        <v>0.32</v>
       </c>
       <c r="X113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y113" s="12" t="n">
-        <v>139.67</v>
+        <v>2.91</v>
       </c>
       <c r="Z113" s="12" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AA113" s="9" t="s">
         <v>77</v>
@@ -41455,13 +41461,13 @@
         <v>303</v>
       </c>
       <c r="AC113" s="12" t="n">
-        <v>1792.79</v>
+        <v>0</v>
       </c>
       <c r="AD113" s="12" t="n">
-        <v>18387.56</v>
+        <v>383.64</v>
       </c>
       <c r="AE113" s="12" t="n">
-        <v>1287.14</v>
+        <v>26.85</v>
       </c>
       <c r="AF113" s="12" t="n">
         <v>0</v>
@@ -41580,76 +41586,76 @@
     </row>
     <row r="114" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="n">
-        <v>312123</v>
+        <v>312124</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>240</v>
+        <v>517</v>
       </c>
       <c r="C114" s="9"/>
       <c r="D114" s="9"/>
       <c r="E114" s="9"/>
       <c r="F114" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="I114" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J114" s="9" t="s">
-        <v>259</v>
+        <v>519</v>
       </c>
       <c r="K114" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>383.64</v>
+        <v>50309.12</v>
       </c>
       <c r="M114" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N114" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O114" s="12" t="n">
-        <v>383.64</v>
+        <v>50309.12</v>
       </c>
       <c r="P114" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q114" s="13" t="n">
-        <v>0.017556</v>
+        <v>11.517776</v>
       </c>
       <c r="R114" s="12" t="n">
-        <v>2.38</v>
+        <v>12384</v>
       </c>
       <c r="S114" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T114" s="14" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="U114" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V114" s="12" t="n">
-        <v>323.78</v>
+        <v>42459.63</v>
       </c>
       <c r="W114" s="12" t="n">
-        <v>0.32</v>
+        <v>42.46</v>
       </c>
       <c r="X114" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y114" s="12" t="n">
-        <v>2.91</v>
+        <v>382.14</v>
       </c>
       <c r="Z114" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA114" s="9" t="s">
         <v>77</v>
@@ -41661,10 +41667,10 @@
         <v>0</v>
       </c>
       <c r="AD114" s="12" t="n">
-        <v>383.64</v>
+        <v>50309.12</v>
       </c>
       <c r="AE114" s="12" t="n">
-        <v>26.85</v>
+        <v>3521.64</v>
       </c>
       <c r="AF114" s="12" t="n">
         <v>0</v>
@@ -41769,7 +41775,7 @@
         <v>73</v>
       </c>
       <c r="BN114" s="9" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="BO114" s="9" t="s">
         <v>79</v>
@@ -41783,52 +41789,52 @@
     </row>
     <row r="115" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="n">
-        <v>312124</v>
+        <v>312125</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="9"/>
       <c r="E115" s="9"/>
       <c r="F115" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G115" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="I115" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J115" s="9" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="K115" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>50309.12</v>
+        <v>79548.35</v>
       </c>
       <c r="M115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N115" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="O115" s="12" t="n">
-        <v>50309.12</v>
+        <v>79008.54</v>
       </c>
       <c r="P115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="13" t="n">
-        <v>11.517776</v>
+        <v>14.374222</v>
       </c>
       <c r="R115" s="12" t="n">
-        <v>12384</v>
+        <v>14081.8</v>
       </c>
       <c r="S115" s="12" t="n">
         <v>0</v>
@@ -41840,16 +41846,16 @@
         <v>76</v>
       </c>
       <c r="V115" s="12" t="n">
-        <v>42459.63</v>
+        <v>66681.19</v>
       </c>
       <c r="W115" s="12" t="n">
-        <v>42.46</v>
+        <v>66.68</v>
       </c>
       <c r="X115" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y115" s="12" t="n">
-        <v>382.14</v>
+        <v>600.14</v>
       </c>
       <c r="Z115" s="12" t="n">
         <v>28</v>
@@ -41861,13 +41867,13 @@
         <v>303</v>
       </c>
       <c r="AC115" s="12" t="n">
-        <v>0</v>
+        <v>539.81</v>
       </c>
       <c r="AD115" s="12" t="n">
-        <v>50309.12</v>
+        <v>79008.54</v>
       </c>
       <c r="AE115" s="12" t="n">
-        <v>3521.64</v>
+        <v>5530.62</v>
       </c>
       <c r="AF115" s="12" t="n">
         <v>0</v>
@@ -41986,10 +41992,10 @@
     </row>
     <row r="116" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="n">
-        <v>312125</v>
+        <v>312127</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>520</v>
+        <v>104</v>
       </c>
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
@@ -42001,37 +42007,37 @@
         <v>91</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>506</v>
+        <v>214</v>
       </c>
       <c r="I116" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J116" s="9" t="s">
-        <v>522</v>
+        <v>73</v>
       </c>
       <c r="K116" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>79548.35</v>
+        <v>3128.4</v>
       </c>
       <c r="M116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N116" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O116" s="12" t="n">
-        <v>79008.54</v>
+        <v>3128.4</v>
       </c>
       <c r="P116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q116" s="13" t="n">
-        <v>14.374222</v>
+        <v>0.218592</v>
       </c>
       <c r="R116" s="12" t="n">
-        <v>14081.8</v>
+        <v>126.72</v>
       </c>
       <c r="S116" s="12" t="n">
         <v>0</v>
@@ -42043,19 +42049,19 @@
         <v>76</v>
       </c>
       <c r="V116" s="12" t="n">
-        <v>66681.19</v>
+        <v>3003.26</v>
       </c>
       <c r="W116" s="12" t="n">
-        <v>66.68</v>
+        <v>3</v>
       </c>
       <c r="X116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y116" s="12" t="n">
-        <v>600.14</v>
+        <v>27.03</v>
       </c>
       <c r="Z116" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA116" s="9" t="s">
         <v>77</v>
@@ -42064,13 +42070,13 @@
         <v>303</v>
       </c>
       <c r="AC116" s="12" t="n">
-        <v>539.81</v>
+        <v>0</v>
       </c>
       <c r="AD116" s="12" t="n">
-        <v>79008.54</v>
+        <v>3128.4</v>
       </c>
       <c r="AE116" s="12" t="n">
-        <v>5530.62</v>
+        <v>125.14</v>
       </c>
       <c r="AF116" s="12" t="n">
         <v>0</v>
@@ -42079,7 +42085,7 @@
         <v>0</v>
       </c>
       <c r="AH116" s="12" t="n">
-        <v>0</v>
+        <v>86.82</v>
       </c>
       <c r="AI116" s="12" t="n">
         <v>0</v>
@@ -42139,7 +42145,7 @@
         <v>78</v>
       </c>
       <c r="BB116" s="10" t="s">
-        <v>95</v>
+        <v>527</v>
       </c>
       <c r="BC116" s="14" t="s">
         <v>79</v>
@@ -42160,25 +42166,25 @@
         <v>79</v>
       </c>
       <c r="BI116" s="14" t="s">
-        <v>79</v>
+        <v>528</v>
       </c>
       <c r="BJ116" s="9" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="BK116" s="9" t="s">
-        <v>73</v>
+        <v>291</v>
       </c>
       <c r="BL116" s="14" t="s">
-        <v>79</v>
+        <v>529</v>
       </c>
       <c r="BM116" s="9" t="s">
-        <v>73</v>
+        <v>503</v>
       </c>
       <c r="BN116" s="9" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="BO116" s="9" t="s">
-        <v>79</v>
+        <v>531</v>
       </c>
       <c r="BP116" s="9" t="s">
         <v>79</v>
@@ -42189,16 +42195,16 @@
     </row>
     <row r="117" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="8" t="n">
-        <v>312127</v>
+        <v>312128</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>104</v>
+        <v>320</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
       <c r="F117" s="9" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="G117" s="10" t="s">
         <v>91</v>
@@ -42210,13 +42216,13 @@
         <v>303</v>
       </c>
       <c r="J117" s="9" t="s">
-        <v>73</v>
+        <v>308</v>
       </c>
       <c r="K117" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>3128.4</v>
+        <v>227.78</v>
       </c>
       <c r="M117" s="12" t="n">
         <v>0</v>
@@ -42225,40 +42231,40 @@
         <v>1</v>
       </c>
       <c r="O117" s="12" t="n">
-        <v>3128.4</v>
+        <v>213.88</v>
       </c>
       <c r="P117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q117" s="13" t="n">
-        <v>0.218592</v>
+        <v>0.0026</v>
       </c>
       <c r="R117" s="12" t="n">
-        <v>126.72</v>
+        <v>0.92</v>
       </c>
       <c r="S117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T117" s="14" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="U117" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V117" s="12" t="n">
-        <v>3003.26</v>
+        <v>186.33</v>
       </c>
       <c r="W117" s="12" t="n">
-        <v>3</v>
+        <v>0.19</v>
       </c>
       <c r="X117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y117" s="12" t="n">
-        <v>27.03</v>
+        <v>1.68</v>
       </c>
       <c r="Z117" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA117" s="9" t="s">
         <v>77</v>
@@ -42267,13 +42273,13 @@
         <v>303</v>
       </c>
       <c r="AC117" s="12" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="AD117" s="12" t="n">
-        <v>3128.4</v>
+        <v>213.88</v>
       </c>
       <c r="AE117" s="12" t="n">
-        <v>125.14</v>
+        <v>8.56</v>
       </c>
       <c r="AF117" s="12" t="n">
         <v>0</v>
@@ -42282,7 +42288,7 @@
         <v>0</v>
       </c>
       <c r="AH117" s="12" t="n">
-        <v>86.82</v>
+        <v>0</v>
       </c>
       <c r="AI117" s="12" t="n">
         <v>0</v>
@@ -42342,7 +42348,7 @@
         <v>78</v>
       </c>
       <c r="BB117" s="10" t="s">
-        <v>530</v>
+        <v>95</v>
       </c>
       <c r="BC117" s="14" t="s">
         <v>79</v>
@@ -42363,25 +42369,25 @@
         <v>79</v>
       </c>
       <c r="BI117" s="14" t="s">
-        <v>531</v>
+        <v>79</v>
       </c>
       <c r="BJ117" s="9" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="BK117" s="9" t="s">
-        <v>291</v>
+        <v>73</v>
       </c>
       <c r="BL117" s="14" t="s">
-        <v>532</v>
+        <v>79</v>
       </c>
       <c r="BM117" s="9" t="s">
-        <v>506</v>
+        <v>73</v>
       </c>
       <c r="BN117" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="BO117" s="9" t="s">
-        <v>534</v>
+        <v>79</v>
       </c>
       <c r="BP117" s="9" t="s">
         <v>79</v>
@@ -42392,7 +42398,7 @@
     </row>
     <row r="118" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="8" t="n">
-        <v>312128</v>
+        <v>312129</v>
       </c>
       <c r="B118" s="9" t="s">
         <v>320</v>
@@ -42419,25 +42425,25 @@
         <v>74</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>227.78</v>
+        <v>6043.66</v>
       </c>
       <c r="M118" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N118" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O118" s="12" t="n">
-        <v>213.88</v>
+        <v>5932.44</v>
       </c>
       <c r="P118" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q118" s="13" t="n">
-        <v>0.0026</v>
+        <v>0.020826</v>
       </c>
       <c r="R118" s="12" t="n">
-        <v>0.92</v>
+        <v>7.97</v>
       </c>
       <c r="S118" s="12" t="n">
         <v>0</v>
@@ -42449,16 +42455,16 @@
         <v>76</v>
       </c>
       <c r="V118" s="12" t="n">
-        <v>186.33</v>
+        <v>5168.34</v>
       </c>
       <c r="W118" s="12" t="n">
-        <v>0.19</v>
+        <v>5.17</v>
       </c>
       <c r="X118" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y118" s="12" t="n">
-        <v>1.68</v>
+        <v>46.52</v>
       </c>
       <c r="Z118" s="12" t="n">
         <v>28</v>
@@ -42470,13 +42476,13 @@
         <v>303</v>
       </c>
       <c r="AC118" s="12" t="n">
-        <v>13.9</v>
+        <v>111.22</v>
       </c>
       <c r="AD118" s="12" t="n">
-        <v>213.88</v>
+        <v>5932.44</v>
       </c>
       <c r="AE118" s="12" t="n">
-        <v>8.56</v>
+        <v>237.3</v>
       </c>
       <c r="AF118" s="12" t="n">
         <v>0</v>
@@ -42595,16 +42601,16 @@
     </row>
     <row r="119" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="8" t="n">
-        <v>312129</v>
+        <v>312130</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>320</v>
+        <v>538</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
       <c r="F119" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G119" s="10" t="s">
         <v>91</v>
@@ -42622,49 +42628,49 @@
         <v>74</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>6043.66</v>
+        <v>4647.45</v>
       </c>
       <c r="M119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N119" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O119" s="12" t="n">
-        <v>5932.44</v>
+        <v>4647.45</v>
       </c>
       <c r="P119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q119" s="13" t="n">
-        <v>0.020826</v>
+        <v>5.077058</v>
       </c>
       <c r="R119" s="12" t="n">
-        <v>7.97</v>
+        <v>21.79</v>
       </c>
       <c r="S119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T119" s="14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="U119" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V119" s="12" t="n">
-        <v>5168.34</v>
+        <v>4152.5</v>
       </c>
       <c r="W119" s="12" t="n">
-        <v>5.17</v>
+        <v>4.14</v>
       </c>
       <c r="X119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y119" s="12" t="n">
-        <v>46.52</v>
+        <v>37.35</v>
       </c>
       <c r="Z119" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AA119" s="9" t="s">
         <v>77</v>
@@ -42673,13 +42679,13 @@
         <v>303</v>
       </c>
       <c r="AC119" s="12" t="n">
-        <v>111.22</v>
+        <v>0</v>
       </c>
       <c r="AD119" s="12" t="n">
-        <v>5932.44</v>
+        <v>4647.45</v>
       </c>
       <c r="AE119" s="12" t="n">
-        <v>237.3</v>
+        <v>325.32</v>
       </c>
       <c r="AF119" s="12" t="n">
         <v>0</v>
@@ -42688,7 +42694,7 @@
         <v>0</v>
       </c>
       <c r="AH119" s="12" t="n">
-        <v>0</v>
+        <v>107.43</v>
       </c>
       <c r="AI119" s="12" t="n">
         <v>0</v>
@@ -42769,25 +42775,25 @@
         <v>79</v>
       </c>
       <c r="BI119" s="14" t="s">
-        <v>79</v>
+        <v>541</v>
       </c>
       <c r="BJ119" s="9" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="BK119" s="9" t="s">
-        <v>73</v>
+        <v>291</v>
       </c>
       <c r="BL119" s="14" t="s">
-        <v>79</v>
+        <v>542</v>
       </c>
       <c r="BM119" s="9" t="s">
-        <v>73</v>
+        <v>503</v>
       </c>
       <c r="BN119" s="9" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="BO119" s="9" t="s">
-        <v>79</v>
+        <v>544</v>
       </c>
       <c r="BP119" s="9" t="s">
         <v>79</v>
@@ -42798,76 +42804,76 @@
     </row>
     <row r="120" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="n">
-        <v>312130</v>
+        <v>312135</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
       <c r="F120" s="9" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="G120" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>214</v>
+        <v>291</v>
       </c>
       <c r="I120" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J120" s="9" t="s">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="K120" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>4647.45</v>
+        <v>89906.9</v>
       </c>
       <c r="M120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N120" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O120" s="12" t="n">
-        <v>4647.45</v>
+        <v>87076.9</v>
       </c>
       <c r="P120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q120" s="13" t="n">
-        <v>5.077058</v>
+        <v>4.1126</v>
       </c>
       <c r="R120" s="12" t="n">
-        <v>21.79</v>
+        <v>407.5</v>
       </c>
       <c r="S120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T120" s="14" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="U120" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V120" s="12" t="n">
-        <v>4152.5</v>
+        <v>75539.22</v>
       </c>
       <c r="W120" s="12" t="n">
-        <v>4.14</v>
+        <v>75.54</v>
       </c>
       <c r="X120" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y120" s="12" t="n">
-        <v>37.35</v>
+        <v>679.86</v>
       </c>
       <c r="Z120" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="AA120" s="9" t="s">
         <v>77</v>
@@ -42876,13 +42882,13 @@
         <v>303</v>
       </c>
       <c r="AC120" s="12" t="n">
-        <v>0</v>
+        <v>2830</v>
       </c>
       <c r="AD120" s="12" t="n">
-        <v>4647.45</v>
+        <v>87076.9</v>
       </c>
       <c r="AE120" s="12" t="n">
-        <v>325.32</v>
+        <v>3483.07</v>
       </c>
       <c r="AF120" s="12" t="n">
         <v>0</v>
@@ -42891,7 +42897,7 @@
         <v>0</v>
       </c>
       <c r="AH120" s="12" t="n">
-        <v>107.43</v>
+        <v>0</v>
       </c>
       <c r="AI120" s="12" t="n">
         <v>0</v>
@@ -42972,25 +42978,25 @@
         <v>79</v>
       </c>
       <c r="BI120" s="14" t="s">
-        <v>544</v>
+        <v>79</v>
       </c>
       <c r="BJ120" s="9" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="BK120" s="9" t="s">
-        <v>291</v>
+        <v>73</v>
       </c>
       <c r="BL120" s="14" t="s">
-        <v>545</v>
+        <v>79</v>
       </c>
       <c r="BM120" s="9" t="s">
-        <v>506</v>
+        <v>73</v>
       </c>
       <c r="BN120" s="9" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="BO120" s="9" t="s">
-        <v>547</v>
+        <v>79</v>
       </c>
       <c r="BP120" s="9" t="s">
         <v>79</v>
@@ -43001,10 +43007,10 @@
     </row>
     <row r="121" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="n">
-        <v>312135</v>
+        <v>312139</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>548</v>
+        <v>306</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
@@ -43028,25 +43034,25 @@
         <v>74</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>89906.9</v>
+        <v>4453.92</v>
       </c>
       <c r="M121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N121" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O121" s="12" t="n">
-        <v>87076.9</v>
+        <v>4453.92</v>
       </c>
       <c r="P121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="13" t="n">
-        <v>4.1126</v>
+        <v>0.049444</v>
       </c>
       <c r="R121" s="12" t="n">
-        <v>407.5</v>
+        <v>11.89</v>
       </c>
       <c r="S121" s="12" t="n">
         <v>0</v>
@@ -43058,16 +43064,16 @@
         <v>76</v>
       </c>
       <c r="V121" s="12" t="n">
-        <v>75539.22</v>
+        <v>3759</v>
       </c>
       <c r="W121" s="12" t="n">
-        <v>75.54</v>
+        <v>3.76</v>
       </c>
       <c r="X121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y121" s="12" t="n">
-        <v>679.86</v>
+        <v>33.83</v>
       </c>
       <c r="Z121" s="12" t="n">
         <v>28</v>
@@ -43079,13 +43085,13 @@
         <v>303</v>
       </c>
       <c r="AC121" s="12" t="n">
-        <v>2830</v>
+        <v>0</v>
       </c>
       <c r="AD121" s="12" t="n">
-        <v>87076.9</v>
+        <v>4453.92</v>
       </c>
       <c r="AE121" s="12" t="n">
-        <v>3483.07</v>
+        <v>311.77</v>
       </c>
       <c r="AF121" s="12" t="n">
         <v>0</v>
@@ -43204,16 +43210,16 @@
     </row>
     <row r="122" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="8" t="n">
-        <v>312139</v>
+        <v>312140</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>306</v>
+        <v>552</v>
       </c>
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
       <c r="F122" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G122" s="10" t="s">
         <v>91</v>
@@ -43225,55 +43231,55 @@
         <v>303</v>
       </c>
       <c r="J122" s="9" t="s">
-        <v>166</v>
+        <v>407</v>
       </c>
       <c r="K122" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>4453.92</v>
+        <v>8169.6</v>
       </c>
       <c r="M122" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N122" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O122" s="12" t="n">
-        <v>4453.92</v>
+        <v>8169.6</v>
       </c>
       <c r="P122" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q122" s="13" t="n">
-        <v>0.049444</v>
+        <v>1.71218</v>
       </c>
       <c r="R122" s="12" t="n">
-        <v>11.89</v>
+        <v>96.28</v>
       </c>
       <c r="S122" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T122" s="14" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="U122" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V122" s="12" t="n">
-        <v>3759</v>
+        <v>6894.95</v>
       </c>
       <c r="W122" s="12" t="n">
-        <v>3.76</v>
+        <v>6.9</v>
       </c>
       <c r="X122" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y122" s="12" t="n">
-        <v>33.83</v>
+        <v>62.06</v>
       </c>
       <c r="Z122" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="AA122" s="9" t="s">
         <v>77</v>
@@ -43285,10 +43291,10 @@
         <v>0</v>
       </c>
       <c r="AD122" s="12" t="n">
-        <v>4453.92</v>
+        <v>8169.6</v>
       </c>
       <c r="AE122" s="12" t="n">
-        <v>311.77</v>
+        <v>571.87</v>
       </c>
       <c r="AF122" s="12" t="n">
         <v>0</v>
@@ -43393,7 +43399,7 @@
         <v>73</v>
       </c>
       <c r="BN122" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="BO122" s="9" t="s">
         <v>79</v>
@@ -43407,16 +43413,16 @@
     </row>
     <row r="123" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="8" t="n">
-        <v>312140</v>
+        <v>312141</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
       <c r="F123" s="9" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G123" s="10" t="s">
         <v>91</v>
@@ -43428,55 +43434,55 @@
         <v>303</v>
       </c>
       <c r="J123" s="9" t="s">
-        <v>412</v>
+        <v>101</v>
       </c>
       <c r="K123" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>8169.6</v>
+        <v>18429.45</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0</v>
+        <v>1948.05</v>
       </c>
       <c r="N123" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O123" s="12" t="n">
-        <v>8169.6</v>
+        <v>19797.4</v>
       </c>
       <c r="P123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q123" s="13" t="n">
-        <v>1.71218</v>
+        <v>8.90125</v>
       </c>
       <c r="R123" s="12" t="n">
-        <v>96.28</v>
+        <v>438</v>
       </c>
       <c r="S123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T123" s="14" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="U123" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V123" s="12" t="n">
-        <v>6894.95</v>
+        <v>15064.41</v>
       </c>
       <c r="W123" s="12" t="n">
-        <v>6.9</v>
+        <v>15.08</v>
       </c>
       <c r="X123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y123" s="12" t="n">
-        <v>62.06</v>
+        <v>135.58</v>
       </c>
       <c r="Z123" s="12" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="AA123" s="9" t="s">
         <v>77</v>
@@ -43485,13 +43491,13 @@
         <v>303</v>
       </c>
       <c r="AC123" s="12" t="n">
-        <v>0</v>
+        <v>580.1</v>
       </c>
       <c r="AD123" s="12" t="n">
-        <v>8169.6</v>
+        <v>17849.35</v>
       </c>
       <c r="AE123" s="12" t="n">
-        <v>571.87</v>
+        <v>1249.46</v>
       </c>
       <c r="AF123" s="12" t="n">
         <v>0</v>
@@ -43596,7 +43602,7 @@
         <v>73</v>
       </c>
       <c r="BN123" s="9" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="BO123" s="9" t="s">
         <v>79</v>
@@ -43610,16 +43616,16 @@
     </row>
     <row r="124" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="8" t="n">
-        <v>312141</v>
+        <v>312142</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
       <c r="F124" s="9" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G124" s="10" t="s">
         <v>91</v>
@@ -43637,46 +43643,46 @@
         <v>74</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>18429.45</v>
+        <v>8102.99</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>1948.05</v>
+        <v>0</v>
       </c>
       <c r="N124" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O124" s="12" t="n">
-        <v>19797.4</v>
+        <v>8102.99</v>
       </c>
       <c r="P124" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q124" s="13" t="n">
-        <v>8.90125</v>
+        <v>0.209151</v>
       </c>
       <c r="R124" s="12" t="n">
-        <v>438</v>
+        <v>66</v>
       </c>
       <c r="S124" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T124" s="14" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="U124" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V124" s="12" t="n">
-        <v>15064.41</v>
+        <v>7059.31</v>
       </c>
       <c r="W124" s="12" t="n">
-        <v>15.08</v>
+        <v>7.06</v>
       </c>
       <c r="X124" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y124" s="12" t="n">
-        <v>135.58</v>
+        <v>63.54</v>
       </c>
       <c r="Z124" s="12" t="n">
         <v>14</v>
@@ -43688,13 +43694,13 @@
         <v>303</v>
       </c>
       <c r="AC124" s="12" t="n">
-        <v>580.1</v>
+        <v>0</v>
       </c>
       <c r="AD124" s="12" t="n">
-        <v>17849.35</v>
+        <v>8102.99</v>
       </c>
       <c r="AE124" s="12" t="n">
-        <v>1249.46</v>
+        <v>324.12</v>
       </c>
       <c r="AF124" s="12" t="n">
         <v>0</v>
@@ -43799,7 +43805,7 @@
         <v>73</v>
       </c>
       <c r="BN124" s="9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="BO124" s="9" t="s">
         <v>79</v>
@@ -43813,16 +43819,16 @@
     </row>
     <row r="125" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="8" t="n">
-        <v>312142</v>
+        <v>312143</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
       <c r="F125" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G125" s="10" t="s">
         <v>91</v>
@@ -43834,55 +43840,55 @@
         <v>303</v>
       </c>
       <c r="J125" s="9" t="s">
-        <v>101</v>
+        <v>370</v>
       </c>
       <c r="K125" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>8102.99</v>
+        <v>3856.67</v>
       </c>
       <c r="M125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N125" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O125" s="12" t="n">
-        <v>8102.99</v>
+        <v>3514.05</v>
       </c>
       <c r="P125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q125" s="13" t="n">
-        <v>0.209151</v>
+        <v>0.012045</v>
       </c>
       <c r="R125" s="12" t="n">
-        <v>66</v>
+        <v>10.62</v>
       </c>
       <c r="S125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T125" s="14" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="U125" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V125" s="12" t="n">
-        <v>7059.31</v>
+        <v>3033.24</v>
       </c>
       <c r="W125" s="12" t="n">
-        <v>7.06</v>
+        <v>3.05</v>
       </c>
       <c r="X125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y125" s="12" t="n">
-        <v>63.54</v>
+        <v>27.31</v>
       </c>
       <c r="Z125" s="12" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="AA125" s="9" t="s">
         <v>77</v>
@@ -43891,13 +43897,13 @@
         <v>303</v>
       </c>
       <c r="AC125" s="12" t="n">
-        <v>0</v>
+        <v>342.62</v>
       </c>
       <c r="AD125" s="12" t="n">
-        <v>8102.99</v>
+        <v>3514.05</v>
       </c>
       <c r="AE125" s="12" t="n">
-        <v>324.12</v>
+        <v>171.62</v>
       </c>
       <c r="AF125" s="12" t="n">
         <v>0</v>
@@ -44002,7 +44008,7 @@
         <v>73</v>
       </c>
       <c r="BN125" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="BO125" s="9" t="s">
         <v>79</v>
@@ -44016,16 +44022,16 @@
     </row>
     <row r="126" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="8" t="n">
-        <v>312143</v>
+        <v>312145</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
       <c r="F126" s="9" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G126" s="10" t="s">
         <v>91</v>
@@ -44037,55 +44043,55 @@
         <v>303</v>
       </c>
       <c r="J126" s="9" t="s">
-        <v>370</v>
+        <v>570</v>
       </c>
       <c r="K126" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>3856.67</v>
+        <v>1821.83</v>
       </c>
       <c r="M126" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N126" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O126" s="12" t="n">
-        <v>3514.05</v>
+        <v>1821.83</v>
       </c>
       <c r="P126" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q126" s="13" t="n">
-        <v>0.012045</v>
+        <v>0.150728</v>
       </c>
       <c r="R126" s="12" t="n">
-        <v>10.62</v>
+        <v>62.59</v>
       </c>
       <c r="S126" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T126" s="14" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="U126" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V126" s="12" t="n">
-        <v>3033.24</v>
+        <v>1524.95</v>
       </c>
       <c r="W126" s="12" t="n">
-        <v>3.05</v>
+        <v>1.53</v>
       </c>
       <c r="X126" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y126" s="12" t="n">
-        <v>27.31</v>
+        <v>13.73</v>
       </c>
       <c r="Z126" s="12" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="AA126" s="9" t="s">
         <v>77</v>
@@ -44094,13 +44100,13 @@
         <v>303</v>
       </c>
       <c r="AC126" s="12" t="n">
-        <v>342.62</v>
+        <v>0</v>
       </c>
       <c r="AD126" s="12" t="n">
-        <v>3514.05</v>
+        <v>1821.83</v>
       </c>
       <c r="AE126" s="12" t="n">
-        <v>171.62</v>
+        <v>141.45</v>
       </c>
       <c r="AF126" s="12" t="n">
         <v>0</v>
@@ -44205,7 +44211,7 @@
         <v>73</v>
       </c>
       <c r="BN126" s="9" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="BO126" s="9" t="s">
         <v>79</v>
@@ -44219,16 +44225,16 @@
     </row>
     <row r="127" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="8" t="n">
-        <v>312145</v>
+        <v>312146</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>571</v>
+        <v>320</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
       <c r="F127" s="9" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G127" s="10" t="s">
         <v>91</v>
@@ -44240,31 +44246,31 @@
         <v>303</v>
       </c>
       <c r="J127" s="9" t="s">
-        <v>573</v>
+        <v>166</v>
       </c>
       <c r="K127" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>1821.83</v>
+        <v>11297.74</v>
       </c>
       <c r="M127" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N127" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O127" s="12" t="n">
-        <v>1821.83</v>
+        <v>10608.2</v>
       </c>
       <c r="P127" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q127" s="13" t="n">
-        <v>0.150728</v>
+        <v>1.9608</v>
       </c>
       <c r="R127" s="12" t="n">
-        <v>62.59</v>
+        <v>35.82</v>
       </c>
       <c r="S127" s="12" t="n">
         <v>0</v>
@@ -44276,19 +44282,19 @@
         <v>76</v>
       </c>
       <c r="V127" s="12" t="n">
-        <v>1524.95</v>
+        <v>9241.87</v>
       </c>
       <c r="W127" s="12" t="n">
-        <v>1.53</v>
+        <v>9.24</v>
       </c>
       <c r="X127" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y127" s="12" t="n">
-        <v>13.73</v>
+        <v>83.17</v>
       </c>
       <c r="Z127" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA127" s="9" t="s">
         <v>77</v>
@@ -44297,13 +44303,13 @@
         <v>303</v>
       </c>
       <c r="AC127" s="12" t="n">
-        <v>0</v>
+        <v>689.54</v>
       </c>
       <c r="AD127" s="12" t="n">
-        <v>1821.83</v>
+        <v>10608.2</v>
       </c>
       <c r="AE127" s="12" t="n">
-        <v>141.45</v>
+        <v>424.33</v>
       </c>
       <c r="AF127" s="12" t="n">
         <v>0</v>
@@ -44422,7 +44428,7 @@
     </row>
     <row r="128" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="8" t="n">
-        <v>312146</v>
+        <v>312147</v>
       </c>
       <c r="B128" s="9" t="s">
         <v>320</v>
@@ -44443,55 +44449,55 @@
         <v>303</v>
       </c>
       <c r="J128" s="9" t="s">
-        <v>166</v>
+        <v>577</v>
       </c>
       <c r="K128" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>11297.74</v>
+        <v>7008.55</v>
       </c>
       <c r="M128" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N128" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O128" s="12" t="n">
-        <v>10608.2</v>
+        <v>6580.8</v>
       </c>
       <c r="P128" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q128" s="13" t="n">
-        <v>1.9608</v>
+        <v>0.91728</v>
       </c>
       <c r="R128" s="12" t="n">
-        <v>35.82</v>
+        <v>33.6</v>
       </c>
       <c r="S128" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T128" s="14" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="U128" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V128" s="12" t="n">
-        <v>9241.87</v>
+        <v>5733.19</v>
       </c>
       <c r="W128" s="12" t="n">
-        <v>9.24</v>
+        <v>5.73</v>
       </c>
       <c r="X128" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y128" s="12" t="n">
-        <v>83.17</v>
+        <v>51.6</v>
       </c>
       <c r="Z128" s="12" t="n">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="AA128" s="9" t="s">
         <v>77</v>
@@ -44500,13 +44506,13 @@
         <v>303</v>
       </c>
       <c r="AC128" s="12" t="n">
-        <v>689.54</v>
+        <v>427.75</v>
       </c>
       <c r="AD128" s="12" t="n">
-        <v>10608.2</v>
+        <v>6580.8</v>
       </c>
       <c r="AE128" s="12" t="n">
-        <v>424.33</v>
+        <v>263.23</v>
       </c>
       <c r="AF128" s="12" t="n">
         <v>0</v>
@@ -44611,7 +44617,7 @@
         <v>73</v>
       </c>
       <c r="BN128" s="9" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="BO128" s="9" t="s">
         <v>79</v>
@@ -44625,7 +44631,7 @@
     </row>
     <row r="129" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="8" t="n">
-        <v>312147</v>
+        <v>312148</v>
       </c>
       <c r="B129" s="9" t="s">
         <v>320</v>
@@ -44634,7 +44640,7 @@
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
       <c r="F129" s="9" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G129" s="10" t="s">
         <v>91</v>
@@ -44646,31 +44652,31 @@
         <v>303</v>
       </c>
       <c r="J129" s="9" t="s">
-        <v>580</v>
+        <v>166</v>
       </c>
       <c r="K129" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>7008.55</v>
+        <v>69788.59</v>
       </c>
       <c r="M129" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N129" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O129" s="12" t="n">
-        <v>6580.8</v>
+        <v>67662.66</v>
       </c>
       <c r="P129" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q129" s="13" t="n">
-        <v>0.91728</v>
+        <v>0.861064</v>
       </c>
       <c r="R129" s="12" t="n">
-        <v>33.6</v>
+        <v>246.14</v>
       </c>
       <c r="S129" s="12" t="n">
         <v>0</v>
@@ -44682,19 +44688,19 @@
         <v>76</v>
       </c>
       <c r="V129" s="12" t="n">
-        <v>5733.19</v>
+        <v>58947.68</v>
       </c>
       <c r="W129" s="12" t="n">
-        <v>5.73</v>
+        <v>58.96</v>
       </c>
       <c r="X129" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y129" s="12" t="n">
-        <v>51.6</v>
+        <v>530.54</v>
       </c>
       <c r="Z129" s="12" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="AA129" s="9" t="s">
         <v>77</v>
@@ -44703,13 +44709,13 @@
         <v>303</v>
       </c>
       <c r="AC129" s="12" t="n">
-        <v>427.75</v>
+        <v>2125.93</v>
       </c>
       <c r="AD129" s="12" t="n">
-        <v>6580.8</v>
+        <v>67662.66</v>
       </c>
       <c r="AE129" s="12" t="n">
-        <v>263.23</v>
+        <v>2706.51</v>
       </c>
       <c r="AF129" s="12" t="n">
         <v>0</v>
@@ -44828,7 +44834,7 @@
     </row>
     <row r="130" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="8" t="n">
-        <v>312148</v>
+        <v>312150</v>
       </c>
       <c r="B130" s="9" t="s">
         <v>320</v>
@@ -44849,31 +44855,31 @@
         <v>303</v>
       </c>
       <c r="J130" s="9" t="s">
-        <v>166</v>
+        <v>457</v>
       </c>
       <c r="K130" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L130" s="12" t="n">
-        <v>69788.59</v>
+        <v>33393.41</v>
       </c>
       <c r="M130" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N130" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O130" s="12" t="n">
-        <v>67662.66</v>
+        <v>30426.8</v>
       </c>
       <c r="P130" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q130" s="13" t="n">
-        <v>0.861064</v>
+        <v>0.00052</v>
       </c>
       <c r="R130" s="12" t="n">
-        <v>246.14</v>
+        <v>12.2</v>
       </c>
       <c r="S130" s="12" t="n">
         <v>0</v>
@@ -44885,19 +44891,19 @@
         <v>76</v>
       </c>
       <c r="V130" s="12" t="n">
-        <v>58947.68</v>
+        <v>26507.83</v>
       </c>
       <c r="W130" s="12" t="n">
-        <v>58.96</v>
+        <v>26.51</v>
       </c>
       <c r="X130" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y130" s="12" t="n">
-        <v>530.54</v>
+        <v>238.57</v>
       </c>
       <c r="Z130" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="AA130" s="9" t="s">
         <v>77</v>
@@ -44906,13 +44912,13 @@
         <v>303</v>
       </c>
       <c r="AC130" s="12" t="n">
-        <v>2125.93</v>
+        <v>2966.61</v>
       </c>
       <c r="AD130" s="12" t="n">
-        <v>67662.66</v>
+        <v>30426.8</v>
       </c>
       <c r="AE130" s="12" t="n">
-        <v>2706.51</v>
+        <v>1217.07</v>
       </c>
       <c r="AF130" s="12" t="n">
         <v>0</v>
@@ -45031,7 +45037,7 @@
     </row>
     <row r="131" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="8" t="n">
-        <v>312150</v>
+        <v>312151</v>
       </c>
       <c r="B131" s="9" t="s">
         <v>320</v>
@@ -45052,13 +45058,13 @@
         <v>303</v>
       </c>
       <c r="J131" s="9" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="K131" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L131" s="12" t="n">
-        <v>33393.41</v>
+        <v>10018.02</v>
       </c>
       <c r="M131" s="12" t="n">
         <v>0</v>
@@ -45067,16 +45073,16 @@
         <v>1</v>
       </c>
       <c r="O131" s="12" t="n">
-        <v>30426.8</v>
+        <v>9128.04</v>
       </c>
       <c r="P131" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q131" s="13" t="n">
-        <v>0.00052</v>
+        <v>0.000156</v>
       </c>
       <c r="R131" s="12" t="n">
-        <v>12.2</v>
+        <v>3.66</v>
       </c>
       <c r="S131" s="12" t="n">
         <v>0</v>
@@ -45088,16 +45094,16 @@
         <v>76</v>
       </c>
       <c r="V131" s="12" t="n">
-        <v>26507.83</v>
+        <v>7952.35</v>
       </c>
       <c r="W131" s="12" t="n">
-        <v>26.51</v>
+        <v>7.95</v>
       </c>
       <c r="X131" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y131" s="12" t="n">
-        <v>238.57</v>
+        <v>71.57</v>
       </c>
       <c r="Z131" s="12" t="n">
         <v>56</v>
@@ -45109,13 +45115,13 @@
         <v>303</v>
       </c>
       <c r="AC131" s="12" t="n">
-        <v>2966.61</v>
+        <v>889.98</v>
       </c>
       <c r="AD131" s="12" t="n">
-        <v>30426.8</v>
+        <v>9128.04</v>
       </c>
       <c r="AE131" s="12" t="n">
-        <v>1217.07</v>
+        <v>365.12</v>
       </c>
       <c r="AF131" s="12" t="n">
         <v>0</v>
@@ -45234,7 +45240,7 @@
     </row>
     <row r="132" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="8" t="n">
-        <v>312151</v>
+        <v>312152</v>
       </c>
       <c r="B132" s="9" t="s">
         <v>320</v>
@@ -45255,13 +45261,13 @@
         <v>303</v>
       </c>
       <c r="J132" s="9" t="s">
-        <v>460</v>
+        <v>577</v>
       </c>
       <c r="K132" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L132" s="12" t="n">
-        <v>10018.02</v>
+        <v>8348.35</v>
       </c>
       <c r="M132" s="12" t="n">
         <v>0</v>
@@ -45270,16 +45276,16 @@
         <v>1</v>
       </c>
       <c r="O132" s="12" t="n">
-        <v>9128.04</v>
+        <v>7606.7</v>
       </c>
       <c r="P132" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q132" s="13" t="n">
-        <v>0.000156</v>
+        <v>0.00013</v>
       </c>
       <c r="R132" s="12" t="n">
-        <v>3.66</v>
+        <v>3.05</v>
       </c>
       <c r="S132" s="12" t="n">
         <v>0</v>
@@ -45291,19 +45297,19 @@
         <v>76</v>
       </c>
       <c r="V132" s="12" t="n">
-        <v>7952.35</v>
+        <v>6626.96</v>
       </c>
       <c r="W132" s="12" t="n">
-        <v>7.95</v>
+        <v>6.63</v>
       </c>
       <c r="X132" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y132" s="12" t="n">
-        <v>71.57</v>
+        <v>59.64</v>
       </c>
       <c r="Z132" s="12" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="AA132" s="9" t="s">
         <v>77</v>
@@ -45312,13 +45318,13 @@
         <v>303</v>
       </c>
       <c r="AC132" s="12" t="n">
-        <v>889.98</v>
+        <v>741.65</v>
       </c>
       <c r="AD132" s="12" t="n">
-        <v>9128.04</v>
+        <v>7606.7</v>
       </c>
       <c r="AE132" s="12" t="n">
-        <v>365.12</v>
+        <v>304.27</v>
       </c>
       <c r="AF132" s="12" t="n">
         <v>0</v>
@@ -45437,7 +45443,7 @@
     </row>
     <row r="133" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="8" t="n">
-        <v>312152</v>
+        <v>312153</v>
       </c>
       <c r="B133" s="9" t="s">
         <v>320</v>
@@ -45458,13 +45464,13 @@
         <v>303</v>
       </c>
       <c r="J133" s="9" t="s">
-        <v>580</v>
+        <v>457</v>
       </c>
       <c r="K133" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L133" s="12" t="n">
-        <v>8348.35</v>
+        <v>16696.71</v>
       </c>
       <c r="M133" s="12" t="n">
         <v>0</v>
@@ -45473,16 +45479,16 @@
         <v>1</v>
       </c>
       <c r="O133" s="12" t="n">
-        <v>7606.7</v>
+        <v>15213.4</v>
       </c>
       <c r="P133" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q133" s="13" t="n">
-        <v>0.00013</v>
+        <v>0.00026</v>
       </c>
       <c r="R133" s="12" t="n">
-        <v>3.05</v>
+        <v>6.1</v>
       </c>
       <c r="S133" s="12" t="n">
         <v>0</v>
@@ -45494,19 +45500,19 @@
         <v>76</v>
       </c>
       <c r="V133" s="12" t="n">
-        <v>6626.96</v>
+        <v>13253.91</v>
       </c>
       <c r="W133" s="12" t="n">
-        <v>6.63</v>
+        <v>13.25</v>
       </c>
       <c r="X133" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y133" s="12" t="n">
-        <v>59.64</v>
+        <v>119.29</v>
       </c>
       <c r="Z133" s="12" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="AA133" s="9" t="s">
         <v>77</v>
@@ -45515,13 +45521,13 @@
         <v>303</v>
       </c>
       <c r="AC133" s="12" t="n">
-        <v>741.65</v>
+        <v>1483.31</v>
       </c>
       <c r="AD133" s="12" t="n">
-        <v>7606.7</v>
+        <v>15213.4</v>
       </c>
       <c r="AE133" s="12" t="n">
-        <v>304.27</v>
+        <v>608.54</v>
       </c>
       <c r="AF133" s="12" t="n">
         <v>0</v>
@@ -45640,10 +45646,10 @@
     </row>
     <row r="134" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="8" t="n">
-        <v>312153</v>
+        <v>312154</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>320</v>
+        <v>228</v>
       </c>
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
@@ -45661,31 +45667,31 @@
         <v>303</v>
       </c>
       <c r="J134" s="9" t="s">
-        <v>460</v>
+        <v>166</v>
       </c>
       <c r="K134" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L134" s="12" t="n">
-        <v>16696.71</v>
+        <v>94424.92</v>
       </c>
       <c r="M134" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N134" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O134" s="12" t="n">
-        <v>15213.4</v>
+        <v>94424.92</v>
       </c>
       <c r="P134" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q134" s="13" t="n">
-        <v>0.00026</v>
+        <v>3.159442</v>
       </c>
       <c r="R134" s="12" t="n">
-        <v>6.1</v>
+        <v>3257.7</v>
       </c>
       <c r="S134" s="12" t="n">
         <v>0</v>
@@ -45697,19 +45703,19 @@
         <v>76</v>
       </c>
       <c r="V134" s="12" t="n">
-        <v>13253.91</v>
+        <v>80204.33</v>
       </c>
       <c r="W134" s="12" t="n">
-        <v>13.25</v>
+        <v>80.22</v>
       </c>
       <c r="X134" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y134" s="12" t="n">
-        <v>119.29</v>
+        <v>721.84</v>
       </c>
       <c r="Z134" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="AA134" s="9" t="s">
         <v>77</v>
@@ -45718,13 +45724,13 @@
         <v>303</v>
       </c>
       <c r="AC134" s="12" t="n">
-        <v>1483.31</v>
+        <v>0</v>
       </c>
       <c r="AD134" s="12" t="n">
-        <v>15213.4</v>
+        <v>94424.92</v>
       </c>
       <c r="AE134" s="12" t="n">
-        <v>608.54</v>
+        <v>6045.48</v>
       </c>
       <c r="AF134" s="12" t="n">
         <v>0</v>
@@ -45843,7 +45849,7 @@
     </row>
     <row r="135" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="8" t="n">
-        <v>312154</v>
+        <v>312155</v>
       </c>
       <c r="B135" s="9" t="s">
         <v>228</v>
@@ -45870,25 +45876,25 @@
         <v>74</v>
       </c>
       <c r="L135" s="12" t="n">
-        <v>94424.92</v>
+        <v>2072.88</v>
       </c>
       <c r="M135" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N135" s="12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O135" s="12" t="n">
-        <v>94424.92</v>
+        <v>2072.88</v>
       </c>
       <c r="P135" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q135" s="13" t="n">
-        <v>3.159442</v>
+        <v>0.051264</v>
       </c>
       <c r="R135" s="12" t="n">
-        <v>3257.7</v>
+        <v>29.6</v>
       </c>
       <c r="S135" s="12" t="n">
         <v>0</v>
@@ -45900,16 +45906,16 @@
         <v>76</v>
       </c>
       <c r="V135" s="12" t="n">
-        <v>80204.33</v>
+        <v>1805.89</v>
       </c>
       <c r="W135" s="12" t="n">
-        <v>80.22</v>
+        <v>1.81</v>
       </c>
       <c r="X135" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y135" s="12" t="n">
-        <v>721.84</v>
+        <v>16.25</v>
       </c>
       <c r="Z135" s="12" t="n">
         <v>28</v>
@@ -45924,10 +45930,10 @@
         <v>0</v>
       </c>
       <c r="AD135" s="12" t="n">
-        <v>94424.92</v>
+        <v>2072.88</v>
       </c>
       <c r="AE135" s="12" t="n">
-        <v>6045.48</v>
+        <v>82.92</v>
       </c>
       <c r="AF135" s="12" t="n">
         <v>0</v>
@@ -46046,7 +46052,7 @@
     </row>
     <row r="136" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="8" t="n">
-        <v>312155</v>
+        <v>312156</v>
       </c>
       <c r="B136" s="9" t="s">
         <v>228</v>
@@ -46067,13 +46073,13 @@
         <v>303</v>
       </c>
       <c r="J136" s="9" t="s">
-        <v>166</v>
+        <v>577</v>
       </c>
       <c r="K136" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L136" s="12" t="n">
-        <v>2072.88</v>
+        <v>1002.56</v>
       </c>
       <c r="M136" s="12" t="n">
         <v>0</v>
@@ -46082,16 +46088,16 @@
         <v>1</v>
       </c>
       <c r="O136" s="12" t="n">
-        <v>2072.88</v>
+        <v>1002.56</v>
       </c>
       <c r="P136" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q136" s="13" t="n">
-        <v>0.051264</v>
+        <v>0.034096</v>
       </c>
       <c r="R136" s="12" t="n">
-        <v>29.6</v>
+        <v>8</v>
       </c>
       <c r="S136" s="12" t="n">
         <v>0</v>
@@ -46103,19 +46109,19 @@
         <v>76</v>
       </c>
       <c r="V136" s="12" t="n">
-        <v>1805.89</v>
+        <v>846.14</v>
       </c>
       <c r="W136" s="12" t="n">
-        <v>1.81</v>
+        <v>0.85</v>
       </c>
       <c r="X136" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y136" s="12" t="n">
-        <v>16.25</v>
+        <v>7.62</v>
       </c>
       <c r="Z136" s="12" t="n">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="AA136" s="9" t="s">
         <v>77</v>
@@ -46127,10 +46133,10 @@
         <v>0</v>
       </c>
       <c r="AD136" s="12" t="n">
-        <v>2072.88</v>
+        <v>1002.56</v>
       </c>
       <c r="AE136" s="12" t="n">
-        <v>82.92</v>
+        <v>70.18</v>
       </c>
       <c r="AF136" s="12" t="n">
         <v>0</v>
@@ -46249,19 +46255,19 @@
     </row>
     <row r="137" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="8" t="n">
-        <v>312156</v>
+        <v>312157</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>228</v>
+        <v>604</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
       <c r="F137" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="H137" s="9" t="s">
         <v>291</v>
@@ -46270,55 +46276,55 @@
         <v>303</v>
       </c>
       <c r="J137" s="9" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="K137" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L137" s="12" t="n">
-        <v>1002.56</v>
+        <v>13370.46</v>
       </c>
       <c r="M137" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N137" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O137" s="12" t="n">
-        <v>1002.56</v>
+        <v>12633.6</v>
       </c>
       <c r="P137" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q137" s="13" t="n">
-        <v>0.034096</v>
+        <v>9.236704</v>
       </c>
       <c r="R137" s="12" t="n">
-        <v>8</v>
+        <v>195.74</v>
       </c>
       <c r="S137" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T137" s="14" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="U137" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V137" s="12" t="n">
-        <v>846.14</v>
+        <v>10089.19</v>
       </c>
       <c r="W137" s="12" t="n">
-        <v>0.85</v>
+        <v>10.09</v>
       </c>
       <c r="X137" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y137" s="12" t="n">
-        <v>7.62</v>
+        <v>90.8</v>
       </c>
       <c r="Z137" s="12" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="AA137" s="9" t="s">
         <v>77</v>
@@ -46327,13 +46333,13 @@
         <v>303</v>
       </c>
       <c r="AC137" s="12" t="n">
-        <v>0</v>
+        <v>736.86</v>
       </c>
       <c r="AD137" s="12" t="n">
-        <v>1002.56</v>
+        <v>12633.6</v>
       </c>
       <c r="AE137" s="12" t="n">
-        <v>70.18</v>
+        <v>1516.04</v>
       </c>
       <c r="AF137" s="12" t="n">
         <v>0</v>
@@ -46438,7 +46444,7 @@
         <v>73</v>
       </c>
       <c r="BN137" s="9" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="BO137" s="9" t="s">
         <v>79</v>
@@ -46452,19 +46458,19 @@
     </row>
     <row r="138" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="8" t="n">
-        <v>312157</v>
+        <v>312158</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>607</v>
+        <v>497</v>
       </c>
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
       <c r="F138" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H138" s="9" t="s">
         <v>291</v>
@@ -46473,31 +46479,31 @@
         <v>303</v>
       </c>
       <c r="J138" s="9" t="s">
-        <v>609</v>
+        <v>73</v>
       </c>
       <c r="K138" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L138" s="12" t="n">
-        <v>13370.46</v>
+        <v>10753.58</v>
       </c>
       <c r="M138" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N138" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O138" s="12" t="n">
-        <v>12633.6</v>
+        <v>10415.1</v>
       </c>
       <c r="P138" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q138" s="13" t="n">
-        <v>9.236704</v>
+        <v>2.38344</v>
       </c>
       <c r="R138" s="12" t="n">
-        <v>195.74</v>
+        <v>842.7</v>
       </c>
       <c r="S138" s="12" t="n">
         <v>0</v>
@@ -46509,19 +46515,19 @@
         <v>76</v>
       </c>
       <c r="V138" s="12" t="n">
-        <v>10089.19</v>
+        <v>9686.04</v>
       </c>
       <c r="W138" s="12" t="n">
-        <v>10.09</v>
+        <v>9.69</v>
       </c>
       <c r="X138" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y138" s="12" t="n">
-        <v>90.8</v>
+        <v>87.17</v>
       </c>
       <c r="Z138" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AA138" s="9" t="s">
         <v>77</v>
@@ -46530,13 +46536,13 @@
         <v>303</v>
       </c>
       <c r="AC138" s="12" t="n">
-        <v>736.86</v>
+        <v>338.48</v>
       </c>
       <c r="AD138" s="12" t="n">
-        <v>12633.6</v>
+        <v>10415.1</v>
       </c>
       <c r="AE138" s="12" t="n">
-        <v>1516.04</v>
+        <v>729.06</v>
       </c>
       <c r="AF138" s="12" t="n">
         <v>0</v>
@@ -46605,7 +46611,7 @@
         <v>78</v>
       </c>
       <c r="BB138" s="10" t="s">
-        <v>95</v>
+        <v>527</v>
       </c>
       <c r="BC138" s="14" t="s">
         <v>79</v>
@@ -46655,19 +46661,19 @@
     </row>
     <row r="139" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="8" t="n">
-        <v>312158</v>
+        <v>312159</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>500</v>
+        <v>612</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
       <c r="F139" s="9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="H139" s="9" t="s">
         <v>291</v>
@@ -46676,55 +46682,55 @@
         <v>303</v>
       </c>
       <c r="J139" s="9" t="s">
-        <v>73</v>
+        <v>570</v>
       </c>
       <c r="K139" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L139" s="12" t="n">
-        <v>10753.58</v>
+        <v>9200</v>
       </c>
       <c r="M139" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N139" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O139" s="12" t="n">
-        <v>10415.1</v>
+        <v>9200</v>
       </c>
       <c r="P139" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q139" s="13" t="n">
-        <v>2.38344</v>
+        <v>0.32908</v>
       </c>
       <c r="R139" s="12" t="n">
-        <v>842.7</v>
+        <v>13.4</v>
       </c>
       <c r="S139" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T139" s="14" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="U139" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V139" s="12" t="n">
-        <v>9686.04</v>
+        <v>0</v>
       </c>
       <c r="W139" s="12" t="n">
-        <v>9.69</v>
+        <v>0</v>
       </c>
       <c r="X139" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y139" s="12" t="n">
-        <v>87.17</v>
+        <v>0</v>
       </c>
       <c r="Z139" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA139" s="9" t="s">
         <v>77</v>
@@ -46733,13 +46739,13 @@
         <v>303</v>
       </c>
       <c r="AC139" s="12" t="n">
-        <v>338.48</v>
+        <v>0</v>
       </c>
       <c r="AD139" s="12" t="n">
-        <v>10415.1</v>
+        <v>9200</v>
       </c>
       <c r="AE139" s="12" t="n">
-        <v>729.06</v>
+        <v>644</v>
       </c>
       <c r="AF139" s="12" t="n">
         <v>0</v>
@@ -46808,7 +46814,7 @@
         <v>78</v>
       </c>
       <c r="BB139" s="10" t="s">
-        <v>530</v>
+        <v>95</v>
       </c>
       <c r="BC139" s="14" t="s">
         <v>79</v>
@@ -46844,7 +46850,7 @@
         <v>73</v>
       </c>
       <c r="BN139" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="BO139" s="9" t="s">
         <v>79</v>
@@ -46858,10 +46864,10 @@
     </row>
     <row r="140" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="8" t="n">
-        <v>312159</v>
+        <v>312160</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>615</v>
+        <v>360</v>
       </c>
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
@@ -46870,7 +46876,7 @@
         <v>616</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="H140" s="9" t="s">
         <v>291</v>
@@ -46879,31 +46885,31 @@
         <v>303</v>
       </c>
       <c r="J140" s="9" t="s">
-        <v>573</v>
+        <v>130</v>
       </c>
       <c r="K140" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L140" s="12" t="n">
-        <v>9200</v>
+        <v>44838.76</v>
       </c>
       <c r="M140" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N140" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O140" s="12" t="n">
-        <v>9200</v>
+        <v>43427.37</v>
       </c>
       <c r="P140" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q140" s="13" t="n">
-        <v>0.32908</v>
+        <v>6.447287</v>
       </c>
       <c r="R140" s="12" t="n">
-        <v>13.4</v>
+        <v>1195.02</v>
       </c>
       <c r="S140" s="12" t="n">
         <v>0</v>
@@ -46915,19 +46921,19 @@
         <v>76</v>
       </c>
       <c r="V140" s="12" t="n">
-        <v>0</v>
+        <v>36651.63</v>
       </c>
       <c r="W140" s="12" t="n">
-        <v>0</v>
+        <v>36.65</v>
       </c>
       <c r="X140" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y140" s="12" t="n">
-        <v>0</v>
+        <v>329.86</v>
       </c>
       <c r="Z140" s="12" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AA140" s="9" t="s">
         <v>77</v>
@@ -46936,13 +46942,13 @@
         <v>303</v>
       </c>
       <c r="AC140" s="12" t="n">
-        <v>0</v>
+        <v>1411.39</v>
       </c>
       <c r="AD140" s="12" t="n">
-        <v>9200</v>
+        <v>43427.37</v>
       </c>
       <c r="AE140" s="12" t="n">
-        <v>644</v>
+        <v>3039.91</v>
       </c>
       <c r="AF140" s="12" t="n">
         <v>0</v>
@@ -47061,10 +47067,10 @@
     </row>
     <row r="141" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="8" t="n">
-        <v>312160</v>
+        <v>312161</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
@@ -47073,64 +47079,64 @@
         <v>619</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>91</v>
+        <v>242</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>291</v>
+        <v>503</v>
       </c>
       <c r="I141" s="9" t="s">
         <v>303</v>
       </c>
       <c r="J141" s="9" t="s">
-        <v>130</v>
+        <v>620</v>
       </c>
       <c r="K141" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L141" s="12" t="n">
-        <v>44838.76</v>
+        <v>5328</v>
       </c>
       <c r="M141" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N141" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O141" s="12" t="n">
-        <v>43427.37</v>
+        <v>5328</v>
       </c>
       <c r="P141" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q141" s="13" t="n">
-        <v>6.447287</v>
+        <v>1.05336</v>
       </c>
       <c r="R141" s="12" t="n">
-        <v>1195.02</v>
+        <v>142.56</v>
       </c>
       <c r="S141" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T141" s="14" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="U141" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V141" s="12" t="n">
-        <v>36651.63</v>
+        <v>4496.7</v>
       </c>
       <c r="W141" s="12" t="n">
-        <v>36.65</v>
+        <v>4.5</v>
       </c>
       <c r="X141" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y141" s="12" t="n">
-        <v>329.86</v>
+        <v>40.47</v>
       </c>
       <c r="Z141" s="12" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AA141" s="9" t="s">
         <v>77</v>
@@ -47139,13 +47145,13 @@
         <v>303</v>
       </c>
       <c r="AC141" s="12" t="n">
-        <v>1411.39</v>
+        <v>0</v>
       </c>
       <c r="AD141" s="12" t="n">
-        <v>43427.37</v>
+        <v>5328</v>
       </c>
       <c r="AE141" s="12" t="n">
-        <v>3039.91</v>
+        <v>372.96</v>
       </c>
       <c r="AF141" s="12" t="n">
         <v>0</v>
@@ -47250,7 +47256,7 @@
         <v>73</v>
       </c>
       <c r="BN141" s="9" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="BO141" s="9" t="s">
         <v>79</v>
@@ -47264,34 +47270,34 @@
     </row>
     <row r="142" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="8" t="n">
-        <v>312161</v>
+        <v>312170</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>240</v>
+        <v>623</v>
       </c>
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
       <c r="F142" s="9" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>506</v>
+        <v>291</v>
       </c>
       <c r="I142" s="9" t="s">
-        <v>303</v>
+        <v>113</v>
       </c>
       <c r="J142" s="9" t="s">
-        <v>623</v>
+        <v>407</v>
       </c>
       <c r="K142" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L142" s="12" t="n">
-        <v>5328</v>
+        <v>108882</v>
       </c>
       <c r="M142" s="12" t="n">
         <v>0</v>
@@ -47300,55 +47306,55 @@
         <v>1</v>
       </c>
       <c r="O142" s="12" t="n">
-        <v>5328</v>
+        <v>108882</v>
       </c>
       <c r="P142" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q142" s="13" t="n">
-        <v>1.05336</v>
+        <v>6618.7836</v>
       </c>
       <c r="R142" s="12" t="n">
-        <v>142.56</v>
+        <v>5940</v>
       </c>
       <c r="S142" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T142" s="14" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="U142" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V142" s="12" t="n">
-        <v>4496.7</v>
+        <v>91893.69</v>
       </c>
       <c r="W142" s="12" t="n">
-        <v>4.5</v>
+        <v>91.89</v>
       </c>
       <c r="X142" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y142" s="12" t="n">
-        <v>40.47</v>
+        <v>827.04</v>
       </c>
       <c r="Z142" s="12" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="AA142" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AB142" s="9" t="s">
-        <v>303</v>
+        <v>113</v>
       </c>
       <c r="AC142" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AD142" s="12" t="n">
-        <v>5328</v>
+        <v>108882</v>
       </c>
       <c r="AE142" s="12" t="n">
-        <v>372.96</v>
+        <v>7621.74</v>
       </c>
       <c r="AF142" s="12" t="n">
         <v>0</v>
@@ -47453,7 +47459,7 @@
         <v>73</v>
       </c>
       <c r="BN142" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="BO142" s="9" t="s">
         <v>79</v>
@@ -47467,10 +47473,10 @@
     </row>
     <row r="143" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="8" t="n">
-        <v>312170</v>
+        <v>312187</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>626</v>
+        <v>220</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
@@ -47482,61 +47488,61 @@
         <v>91</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="I143" s="9" t="s">
         <v>113</v>
       </c>
       <c r="J143" s="9" t="s">
-        <v>412</v>
+        <v>628</v>
       </c>
       <c r="K143" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L143" s="12" t="n">
-        <v>108882</v>
+        <v>8164.82</v>
       </c>
       <c r="M143" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N143" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O143" s="12" t="n">
-        <v>108882</v>
+        <v>7943.1</v>
       </c>
       <c r="P143" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q143" s="13" t="n">
-        <v>6618.7836</v>
+        <v>18.600426</v>
       </c>
       <c r="R143" s="12" t="n">
-        <v>5940</v>
+        <v>737.14</v>
       </c>
       <c r="S143" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T143" s="14" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="U143" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V143" s="12" t="n">
-        <v>91893.69</v>
+        <v>6711.38</v>
       </c>
       <c r="W143" s="12" t="n">
-        <v>91.89</v>
+        <v>6.7</v>
       </c>
       <c r="X143" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y143" s="12" t="n">
-        <v>827.04</v>
+        <v>60.41</v>
       </c>
       <c r="Z143" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="AA143" s="9" t="s">
         <v>77</v>
@@ -47545,13 +47551,13 @@
         <v>113</v>
       </c>
       <c r="AC143" s="12" t="n">
-        <v>0</v>
+        <v>221.72</v>
       </c>
       <c r="AD143" s="12" t="n">
-        <v>108882</v>
+        <v>7823.74</v>
       </c>
       <c r="AE143" s="12" t="n">
-        <v>7621.74</v>
+        <v>547.65</v>
       </c>
       <c r="AF143" s="12" t="n">
         <v>0</v>
@@ -47656,7 +47662,7 @@
         <v>73</v>
       </c>
       <c r="BN143" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="BO143" s="9" t="s">
         <v>79</v>
@@ -47670,16 +47676,16 @@
     </row>
     <row r="144" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="8" t="n">
-        <v>312187</v>
+        <v>312190</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>220</v>
+        <v>360</v>
       </c>
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
       <c r="F144" s="9" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G144" s="10" t="s">
         <v>91</v>
@@ -47691,31 +47697,31 @@
         <v>113</v>
       </c>
       <c r="J144" s="9" t="s">
-        <v>631</v>
+        <v>161</v>
       </c>
       <c r="K144" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L144" s="12" t="n">
-        <v>8164.82</v>
+        <v>831.3</v>
       </c>
       <c r="M144" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N144" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O144" s="12" t="n">
-        <v>7943.1</v>
+        <v>790.21</v>
       </c>
       <c r="P144" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q144" s="13" t="n">
-        <v>18.600426</v>
+        <v>0.02376</v>
       </c>
       <c r="R144" s="12" t="n">
-        <v>737.14</v>
+        <v>12.9</v>
       </c>
       <c r="S144" s="12" t="n">
         <v>0</v>
@@ -47727,19 +47733,19 @@
         <v>76</v>
       </c>
       <c r="V144" s="12" t="n">
-        <v>6711.38</v>
+        <v>666.92</v>
       </c>
       <c r="W144" s="12" t="n">
-        <v>6.7</v>
+        <v>0.67</v>
       </c>
       <c r="X144" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y144" s="12" t="n">
-        <v>60.41</v>
+        <v>6</v>
       </c>
       <c r="Z144" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AA144" s="9" t="s">
         <v>77</v>
@@ -47748,13 +47754,13 @@
         <v>113</v>
       </c>
       <c r="AC144" s="12" t="n">
-        <v>221.72</v>
+        <v>41.09</v>
       </c>
       <c r="AD144" s="12" t="n">
-        <v>7823.74</v>
+        <v>790.21</v>
       </c>
       <c r="AE144" s="12" t="n">
-        <v>547.65</v>
+        <v>55.31</v>
       </c>
       <c r="AF144" s="12" t="n">
         <v>0</v>
@@ -47873,10 +47879,10 @@
     </row>
     <row r="145" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="8" t="n">
-        <v>312190</v>
+        <v>312191</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>360</v>
+        <v>245</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
@@ -47885,7 +47891,7 @@
         <v>634</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="H145" s="9" t="s">
         <v>303</v>
@@ -47894,13 +47900,13 @@
         <v>113</v>
       </c>
       <c r="J145" s="9" t="s">
-        <v>161</v>
+        <v>635</v>
       </c>
       <c r="K145" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L145" s="12" t="n">
-        <v>831.3</v>
+        <v>3294.09</v>
       </c>
       <c r="M145" s="12" t="n">
         <v>0</v>
@@ -47909,40 +47915,40 @@
         <v>1</v>
       </c>
       <c r="O145" s="12" t="n">
-        <v>790.21</v>
+        <v>3190.4</v>
       </c>
       <c r="P145" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q145" s="13" t="n">
-        <v>0.02376</v>
+        <v>0.03168</v>
       </c>
       <c r="R145" s="12" t="n">
-        <v>12.9</v>
+        <v>26.24</v>
       </c>
       <c r="S145" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T145" s="14" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="U145" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V145" s="12" t="n">
-        <v>666.92</v>
+        <v>2692.61</v>
       </c>
       <c r="W145" s="12" t="n">
-        <v>0.67</v>
+        <v>2.69</v>
       </c>
       <c r="X145" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y145" s="12" t="n">
-        <v>6</v>
+        <v>24.23</v>
       </c>
       <c r="Z145" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AA145" s="9" t="s">
         <v>77</v>
@@ -47951,13 +47957,13 @@
         <v>113</v>
       </c>
       <c r="AC145" s="12" t="n">
-        <v>41.09</v>
+        <v>103.69</v>
       </c>
       <c r="AD145" s="12" t="n">
-        <v>790.21</v>
+        <v>3190.4</v>
       </c>
       <c r="AE145" s="12" t="n">
-        <v>55.31</v>
+        <v>223.33</v>
       </c>
       <c r="AF145" s="12" t="n">
         <v>0</v>
@@ -48062,7 +48068,7 @@
         <v>73</v>
       </c>
       <c r="BN145" s="9" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="BO145" s="9" t="s">
         <v>79</v>
@@ -48076,7 +48082,7 @@
     </row>
     <row r="146" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="8" t="n">
-        <v>312191</v>
+        <v>312193</v>
       </c>
       <c r="B146" s="9" t="s">
         <v>245</v>
@@ -48085,7 +48091,7 @@
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
       <c r="F146" s="9" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G146" s="10" t="s">
         <v>135</v>
@@ -48097,13 +48103,13 @@
         <v>113</v>
       </c>
       <c r="J146" s="9" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="K146" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L146" s="12" t="n">
-        <v>3294.09</v>
+        <v>12054.44</v>
       </c>
       <c r="M146" s="12" t="n">
         <v>0</v>
@@ -48112,16 +48118,16 @@
         <v>1</v>
       </c>
       <c r="O146" s="12" t="n">
-        <v>3190.4</v>
+        <v>11675</v>
       </c>
       <c r="P146" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q146" s="13" t="n">
-        <v>0.03168</v>
+        <v>0.02</v>
       </c>
       <c r="R146" s="12" t="n">
-        <v>26.24</v>
+        <v>0.5</v>
       </c>
       <c r="S146" s="12" t="n">
         <v>0</v>
@@ -48133,16 +48139,16 @@
         <v>76</v>
       </c>
       <c r="V146" s="12" t="n">
-        <v>2692.61</v>
+        <v>9853.41</v>
       </c>
       <c r="W146" s="12" t="n">
-        <v>2.69</v>
+        <v>9.85</v>
       </c>
       <c r="X146" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y146" s="12" t="n">
-        <v>24.23</v>
+        <v>88.68</v>
       </c>
       <c r="Z146" s="12" t="n">
         <v>14</v>
@@ -48154,13 +48160,13 @@
         <v>113</v>
       </c>
       <c r="AC146" s="12" t="n">
-        <v>103.69</v>
+        <v>379.44</v>
       </c>
       <c r="AD146" s="12" t="n">
-        <v>3190.4</v>
+        <v>11675</v>
       </c>
       <c r="AE146" s="12" t="n">
-        <v>223.33</v>
+        <v>817.25</v>
       </c>
       <c r="AF146" s="12" t="n">
         <v>0</v>
@@ -48279,7 +48285,7 @@
     </row>
     <row r="147" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="8" t="n">
-        <v>312193</v>
+        <v>312194</v>
       </c>
       <c r="B147" s="9" t="s">
         <v>245</v>
@@ -48300,7 +48306,7 @@
         <v>113</v>
       </c>
       <c r="J147" s="9" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="K147" s="11" t="s">
         <v>74</v>
@@ -48330,7 +48336,7 @@
         <v>0</v>
       </c>
       <c r="T147" s="14" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="U147" s="15" t="s">
         <v>76</v>
@@ -48468,7 +48474,7 @@
         <v>73</v>
       </c>
       <c r="BN147" s="9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="BO147" s="9" t="s">
         <v>79</v>
@@ -48482,10 +48488,10 @@
     </row>
     <row r="148" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="8" t="n">
-        <v>312194</v>
+        <v>312195</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>245</v>
+        <v>643</v>
       </c>
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
@@ -48503,55 +48509,55 @@
         <v>113</v>
       </c>
       <c r="J148" s="9" t="s">
-        <v>638</v>
+        <v>130</v>
       </c>
       <c r="K148" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L148" s="12" t="n">
-        <v>12054.44</v>
+        <v>27845.42</v>
       </c>
       <c r="M148" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N148" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O148" s="12" t="n">
-        <v>11675</v>
+        <v>26691.6</v>
       </c>
       <c r="P148" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q148" s="13" t="n">
-        <v>0.02</v>
+        <v>3.20351</v>
       </c>
       <c r="R148" s="12" t="n">
-        <v>0.5</v>
+        <v>637.9</v>
       </c>
       <c r="S148" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T148" s="14" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="U148" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V148" s="12" t="n">
-        <v>9853.41</v>
+        <v>22685.3</v>
       </c>
       <c r="W148" s="12" t="n">
-        <v>9.85</v>
+        <v>22.67</v>
       </c>
       <c r="X148" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y148" s="12" t="n">
-        <v>88.68</v>
+        <v>204.16</v>
       </c>
       <c r="Z148" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA148" s="9" t="s">
         <v>77</v>
@@ -48560,13 +48566,13 @@
         <v>113</v>
       </c>
       <c r="AC148" s="12" t="n">
-        <v>379.44</v>
+        <v>1153.82</v>
       </c>
       <c r="AD148" s="12" t="n">
-        <v>11675</v>
+        <v>26691.6</v>
       </c>
       <c r="AE148" s="12" t="n">
-        <v>817.25</v>
+        <v>1694.03</v>
       </c>
       <c r="AF148" s="12" t="n">
         <v>0</v>
@@ -48671,7 +48677,7 @@
         <v>73</v>
       </c>
       <c r="BN148" s="9" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="BO148" s="9" t="s">
         <v>79</v>
@@ -48685,10 +48691,10 @@
     </row>
     <row r="149" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="8" t="n">
-        <v>312195</v>
+        <v>312196</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>646</v>
+        <v>133</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
@@ -48706,70 +48712,70 @@
         <v>113</v>
       </c>
       <c r="J149" s="9" t="s">
-        <v>130</v>
+        <v>628</v>
       </c>
       <c r="K149" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L149" s="12" t="n">
-        <v>27845.42</v>
+        <v>20255.11</v>
       </c>
       <c r="M149" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N149" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O149" s="12" t="n">
-        <v>26691.6</v>
+        <v>20124.3</v>
       </c>
       <c r="P149" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q149" s="13" t="n">
-        <v>3.20351</v>
+        <v>3.222219</v>
       </c>
       <c r="R149" s="12" t="n">
-        <v>637.9</v>
+        <v>14050</v>
       </c>
       <c r="S149" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T149" s="14" t="s">
-        <v>648</v>
+        <v>136</v>
       </c>
       <c r="U149" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V149" s="12" t="n">
-        <v>22685.3</v>
+        <v>16984.4</v>
       </c>
       <c r="W149" s="12" t="n">
-        <v>22.67</v>
+        <v>16.98</v>
       </c>
       <c r="X149" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y149" s="12" t="n">
-        <v>204.16</v>
+        <v>152.86</v>
       </c>
       <c r="Z149" s="12" t="n">
-        <v>17</v>
+        <v>97.55</v>
       </c>
       <c r="AA149" s="9" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AB149" s="9" t="s">
         <v>113</v>
       </c>
       <c r="AC149" s="12" t="n">
-        <v>1153.82</v>
+        <v>130.81</v>
       </c>
       <c r="AD149" s="12" t="n">
-        <v>26691.6</v>
+        <v>20124.3</v>
       </c>
       <c r="AE149" s="12" t="n">
-        <v>1694.03</v>
+        <v>1408.7</v>
       </c>
       <c r="AF149" s="12" t="n">
         <v>0</v>
@@ -48874,7 +48880,7 @@
         <v>73</v>
       </c>
       <c r="BN149" s="9" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="BO149" s="9" t="s">
         <v>79</v>
@@ -48888,16 +48894,16 @@
     </row>
     <row r="150" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="8" t="n">
-        <v>312196</v>
+        <v>312199</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>133</v>
+        <v>245</v>
       </c>
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
       <c r="F150" s="9" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G150" s="10" t="s">
         <v>135</v>
@@ -48909,13 +48915,13 @@
         <v>113</v>
       </c>
       <c r="J150" s="9" t="s">
-        <v>631</v>
+        <v>93</v>
       </c>
       <c r="K150" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L150" s="12" t="n">
-        <v>20255.11</v>
+        <v>2688.32</v>
       </c>
       <c r="M150" s="12" t="n">
         <v>0</v>
@@ -48924,55 +48930,55 @@
         <v>1</v>
       </c>
       <c r="O150" s="12" t="n">
-        <v>20124.3</v>
+        <v>2603.7</v>
       </c>
       <c r="P150" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q150" s="13" t="n">
-        <v>3.222219</v>
+        <v>0.0044</v>
       </c>
       <c r="R150" s="12" t="n">
-        <v>14050</v>
+        <v>0.11</v>
       </c>
       <c r="S150" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T150" s="14" t="s">
-        <v>136</v>
+        <v>650</v>
       </c>
       <c r="U150" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V150" s="12" t="n">
-        <v>16984.4</v>
+        <v>2197.46</v>
       </c>
       <c r="W150" s="12" t="n">
-        <v>16.98</v>
+        <v>2.2</v>
       </c>
       <c r="X150" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y150" s="12" t="n">
-        <v>152.86</v>
+        <v>19.78</v>
       </c>
       <c r="Z150" s="12" t="n">
-        <v>97.55</v>
+        <v>55.56</v>
       </c>
       <c r="AA150" s="9" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AB150" s="9" t="s">
         <v>113</v>
       </c>
       <c r="AC150" s="12" t="n">
-        <v>130.81</v>
+        <v>84.62</v>
       </c>
       <c r="AD150" s="12" t="n">
-        <v>20124.3</v>
+        <v>2603.7</v>
       </c>
       <c r="AE150" s="12" t="n">
-        <v>1408.7</v>
+        <v>182.26</v>
       </c>
       <c r="AF150" s="12" t="n">
         <v>0</v>
@@ -49091,34 +49097,34 @@
     </row>
     <row r="151" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="8" t="n">
-        <v>312199</v>
+        <v>312204</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>245</v>
+        <v>652</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
       <c r="F151" s="9" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>303</v>
+        <v>503</v>
       </c>
       <c r="I151" s="9" t="s">
         <v>113</v>
       </c>
       <c r="J151" s="9" t="s">
-        <v>93</v>
+        <v>635</v>
       </c>
       <c r="K151" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L151" s="12" t="n">
-        <v>2688.32</v>
+        <v>3454.8</v>
       </c>
       <c r="M151" s="12" t="n">
         <v>0</v>
@@ -49127,40 +49133,40 @@
         <v>1</v>
       </c>
       <c r="O151" s="12" t="n">
-        <v>2603.7</v>
+        <v>3454.8</v>
       </c>
       <c r="P151" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q151" s="13" t="n">
-        <v>0.0044</v>
+        <v>8.214</v>
       </c>
       <c r="R151" s="12" t="n">
-        <v>0.11</v>
+        <v>285</v>
       </c>
       <c r="S151" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T151" s="14" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="U151" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V151" s="12" t="n">
-        <v>2197.46</v>
+        <v>0</v>
       </c>
       <c r="W151" s="12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X151" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y151" s="12" t="n">
-        <v>19.78</v>
+        <v>0</v>
       </c>
       <c r="Z151" s="12" t="n">
-        <v>55.56</v>
+        <v>15</v>
       </c>
       <c r="AA151" s="9" t="s">
         <v>77</v>
@@ -49169,13 +49175,13 @@
         <v>113</v>
       </c>
       <c r="AC151" s="12" t="n">
-        <v>84.62</v>
+        <v>0</v>
       </c>
       <c r="AD151" s="12" t="n">
-        <v>2603.7</v>
+        <v>3454.8</v>
       </c>
       <c r="AE151" s="12" t="n">
-        <v>182.26</v>
+        <v>131.28</v>
       </c>
       <c r="AF151" s="12" t="n">
         <v>0</v>
@@ -49244,7 +49250,7 @@
         <v>78</v>
       </c>
       <c r="BB151" s="10" t="s">
-        <v>95</v>
+        <v>655</v>
       </c>
       <c r="BC151" s="14" t="s">
         <v>79</v>
@@ -49280,7 +49286,7 @@
         <v>73</v>
       </c>
       <c r="BN151" s="9" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="BO151" s="9" t="s">
         <v>79</v>
@@ -49294,34 +49300,34 @@
     </row>
     <row r="152" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="8" t="n">
-        <v>312204</v>
+        <v>312206</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
       <c r="F152" s="9" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="H152" s="9" t="s">
-        <v>506</v>
+        <v>303</v>
       </c>
       <c r="I152" s="9" t="s">
         <v>113</v>
       </c>
       <c r="J152" s="9" t="s">
-        <v>638</v>
+        <v>156</v>
       </c>
       <c r="K152" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L152" s="12" t="n">
-        <v>3454.8</v>
+        <v>21734.24</v>
       </c>
       <c r="M152" s="12" t="n">
         <v>0</v>
@@ -49330,55 +49336,55 @@
         <v>1</v>
       </c>
       <c r="O152" s="12" t="n">
-        <v>3454.8</v>
+        <v>21593.88</v>
       </c>
       <c r="P152" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q152" s="13" t="n">
-        <v>8.214</v>
+        <v>6.047595</v>
       </c>
       <c r="R152" s="12" t="n">
-        <v>285</v>
+        <v>21888</v>
       </c>
       <c r="S152" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T152" s="14" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="U152" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V152" s="12" t="n">
-        <v>0</v>
+        <v>18224.69</v>
       </c>
       <c r="W152" s="12" t="n">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="X152" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y152" s="12" t="n">
-        <v>0</v>
+        <v>164.02</v>
       </c>
       <c r="Z152" s="12" t="n">
-        <v>15</v>
+        <v>74.64</v>
       </c>
       <c r="AA152" s="9" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AB152" s="9" t="s">
         <v>113</v>
       </c>
       <c r="AC152" s="12" t="n">
-        <v>0</v>
+        <v>140.36</v>
       </c>
       <c r="AD152" s="12" t="n">
-        <v>3454.8</v>
+        <v>21593.88</v>
       </c>
       <c r="AE152" s="12" t="n">
-        <v>131.28</v>
+        <v>1511.57</v>
       </c>
       <c r="AF152" s="12" t="n">
         <v>0</v>
@@ -49447,7 +49453,7 @@
         <v>78</v>
       </c>
       <c r="BB152" s="10" t="s">
-        <v>658</v>
+        <v>95</v>
       </c>
       <c r="BC152" s="14" t="s">
         <v>79</v>
@@ -49483,7 +49489,7 @@
         <v>73</v>
       </c>
       <c r="BN152" s="9" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="BO152" s="9" t="s">
         <v>79</v>
@@ -49497,10 +49503,10 @@
     </row>
     <row r="153" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="8" t="n">
-        <v>312206</v>
+        <v>312208</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>660</v>
+        <v>240</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
@@ -49509,7 +49515,7 @@
         <v>661</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>135</v>
+        <v>242</v>
       </c>
       <c r="H153" s="9" t="s">
         <v>303</v>
@@ -49518,70 +49524,70 @@
         <v>113</v>
       </c>
       <c r="J153" s="9" t="s">
-        <v>156</v>
+        <v>662</v>
       </c>
       <c r="K153" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L153" s="12" t="n">
-        <v>21734.24</v>
+        <v>40079.51</v>
       </c>
       <c r="M153" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N153" s="12" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="O153" s="12" t="n">
-        <v>21593.88</v>
+        <v>39324.6</v>
       </c>
       <c r="P153" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q153" s="13" t="n">
-        <v>6.047595</v>
+        <v>8.453104</v>
       </c>
       <c r="R153" s="12" t="n">
-        <v>21888</v>
+        <v>854.51</v>
       </c>
       <c r="S153" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T153" s="14" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="U153" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V153" s="12" t="n">
-        <v>18224.69</v>
+        <v>33386.69</v>
       </c>
       <c r="W153" s="12" t="n">
-        <v>18.22</v>
+        <v>33.41</v>
       </c>
       <c r="X153" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y153" s="12" t="n">
-        <v>164.02</v>
+        <v>300.5</v>
       </c>
       <c r="Z153" s="12" t="n">
-        <v>74.64</v>
+        <v>60</v>
       </c>
       <c r="AA153" s="9" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AB153" s="9" t="s">
         <v>113</v>
       </c>
       <c r="AC153" s="12" t="n">
-        <v>140.36</v>
+        <v>754.91</v>
       </c>
       <c r="AD153" s="12" t="n">
-        <v>21593.88</v>
+        <v>39324.6</v>
       </c>
       <c r="AE153" s="12" t="n">
-        <v>1511.57</v>
+        <v>2534.85</v>
       </c>
       <c r="AF153" s="12" t="n">
         <v>0</v>
@@ -49686,7 +49692,7 @@
         <v>73</v>
       </c>
       <c r="BN153" s="9" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="BO153" s="9" t="s">
         <v>79</v>
@@ -49700,19 +49706,19 @@
     </row>
     <row r="154" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="8" t="n">
-        <v>312208</v>
+        <v>312209</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>240</v>
+        <v>665</v>
       </c>
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
       <c r="F154" s="9" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G154" s="10" t="s">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="H154" s="9" t="s">
         <v>303</v>
@@ -49721,55 +49727,55 @@
         <v>113</v>
       </c>
       <c r="J154" s="9" t="s">
-        <v>665</v>
+        <v>483</v>
       </c>
       <c r="K154" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L154" s="12" t="n">
-        <v>40079.51</v>
+        <v>180530.4</v>
       </c>
       <c r="M154" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N154" s="12" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="O154" s="12" t="n">
-        <v>39324.6</v>
+        <v>180530.4</v>
       </c>
       <c r="P154" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q154" s="13" t="n">
-        <v>8.453104</v>
+        <v>0.078677</v>
       </c>
       <c r="R154" s="12" t="n">
-        <v>854.51</v>
+        <v>40654.01</v>
       </c>
       <c r="S154" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T154" s="14" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="U154" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V154" s="12" t="n">
-        <v>33386.69</v>
+        <v>152363.14</v>
       </c>
       <c r="W154" s="12" t="n">
-        <v>33.41</v>
+        <v>152.36</v>
       </c>
       <c r="X154" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y154" s="12" t="n">
-        <v>300.5</v>
+        <v>1371.27</v>
       </c>
       <c r="Z154" s="12" t="n">
-        <v>60</v>
+        <v>52.5</v>
       </c>
       <c r="AA154" s="9" t="s">
         <v>77</v>
@@ -49778,13 +49784,13 @@
         <v>113</v>
       </c>
       <c r="AC154" s="12" t="n">
-        <v>754.91</v>
+        <v>0</v>
       </c>
       <c r="AD154" s="12" t="n">
-        <v>39324.6</v>
+        <v>180530.4</v>
       </c>
       <c r="AE154" s="12" t="n">
-        <v>2534.85</v>
+        <v>12637.13</v>
       </c>
       <c r="AF154" s="12" t="n">
         <v>0</v>
@@ -49889,7 +49895,7 @@
         <v>73</v>
       </c>
       <c r="BN154" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="BO154" s="9" t="s">
         <v>79</v>
@@ -49903,10 +49909,10 @@
     </row>
     <row r="155" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="8" t="n">
-        <v>312209</v>
+        <v>312214</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
@@ -49915,40 +49921,40 @@
         <v>669</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>200</v>
+        <v>91</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>303</v>
+        <v>503</v>
       </c>
       <c r="I155" s="9" t="s">
         <v>113</v>
       </c>
       <c r="J155" s="9" t="s">
-        <v>486</v>
+        <v>635</v>
       </c>
       <c r="K155" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L155" s="12" t="n">
-        <v>180530.4</v>
+        <v>15943.95</v>
       </c>
       <c r="M155" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N155" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O155" s="12" t="n">
-        <v>180530.4</v>
+        <v>15943.95</v>
       </c>
       <c r="P155" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q155" s="13" t="n">
-        <v>0.078677</v>
+        <v>36.86159</v>
       </c>
       <c r="R155" s="12" t="n">
-        <v>40654.01</v>
+        <v>1210</v>
       </c>
       <c r="S155" s="12" t="n">
         <v>0</v>
@@ -49960,19 +49966,19 @@
         <v>76</v>
       </c>
       <c r="V155" s="12" t="n">
-        <v>152363.14</v>
+        <v>0</v>
       </c>
       <c r="W155" s="12" t="n">
-        <v>152.36</v>
+        <v>0</v>
       </c>
       <c r="X155" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y155" s="12" t="n">
-        <v>1371.27</v>
+        <v>0</v>
       </c>
       <c r="Z155" s="12" t="n">
-        <v>52.5</v>
+        <v>15</v>
       </c>
       <c r="AA155" s="9" t="s">
         <v>77</v>
@@ -49984,10 +49990,10 @@
         <v>0</v>
       </c>
       <c r="AD155" s="12" t="n">
-        <v>180530.4</v>
+        <v>15943.95</v>
       </c>
       <c r="AE155" s="12" t="n">
-        <v>12637.13</v>
+        <v>605.87</v>
       </c>
       <c r="AF155" s="12" t="n">
         <v>0</v>
@@ -50056,7 +50062,7 @@
         <v>78</v>
       </c>
       <c r="BB155" s="10" t="s">
-        <v>95</v>
+        <v>655</v>
       </c>
       <c r="BC155" s="14" t="s">
         <v>79</v>
@@ -50106,76 +50112,76 @@
     </row>
     <row r="156" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="8" t="n">
-        <v>312214</v>
+        <v>312216</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
       <c r="F156" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G156" s="10" t="s">
-        <v>91</v>
+        <v>242</v>
       </c>
       <c r="H156" s="9" t="s">
-        <v>506</v>
+        <v>214</v>
       </c>
       <c r="I156" s="9" t="s">
         <v>113</v>
       </c>
       <c r="J156" s="9" t="s">
-        <v>638</v>
+        <v>166</v>
       </c>
       <c r="K156" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L156" s="12" t="n">
-        <v>15943.95</v>
+        <v>6281.48</v>
       </c>
       <c r="M156" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N156" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O156" s="12" t="n">
-        <v>15943.95</v>
+        <v>5772</v>
       </c>
       <c r="P156" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q156" s="13" t="n">
-        <v>36.86159</v>
+        <v>11.703</v>
       </c>
       <c r="R156" s="12" t="n">
-        <v>1210</v>
+        <v>347.3</v>
       </c>
       <c r="S156" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T156" s="14" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="U156" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V156" s="12" t="n">
-        <v>0</v>
+        <v>5338.87</v>
       </c>
       <c r="W156" s="12" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="X156" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y156" s="12" t="n">
-        <v>0</v>
+        <v>48.05</v>
       </c>
       <c r="Z156" s="12" t="n">
-        <v>15</v>
+        <v>56.57</v>
       </c>
       <c r="AA156" s="9" t="s">
         <v>77</v>
@@ -50184,13 +50190,13 @@
         <v>113</v>
       </c>
       <c r="AC156" s="12" t="n">
-        <v>0</v>
+        <v>509.48</v>
       </c>
       <c r="AD156" s="12" t="n">
-        <v>15943.95</v>
+        <v>5772</v>
       </c>
       <c r="AE156" s="12" t="n">
-        <v>605.87</v>
+        <v>230.88</v>
       </c>
       <c r="AF156" s="12" t="n">
         <v>0</v>
@@ -50259,7 +50265,7 @@
         <v>78</v>
       </c>
       <c r="BB156" s="10" t="s">
-        <v>658</v>
+        <v>95</v>
       </c>
       <c r="BC156" s="14" t="s">
         <v>79</v>
@@ -50295,7 +50301,7 @@
         <v>73</v>
       </c>
       <c r="BN156" s="9" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="BO156" s="9" t="s">
         <v>79</v>
@@ -50309,76 +50315,76 @@
     </row>
     <row r="157" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="8" t="n">
-        <v>312216</v>
+        <v>312222</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
       <c r="F157" s="9" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>214</v>
+        <v>503</v>
       </c>
       <c r="I157" s="9" t="s">
         <v>113</v>
       </c>
       <c r="J157" s="9" t="s">
-        <v>166</v>
+        <v>678</v>
       </c>
       <c r="K157" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L157" s="12" t="n">
-        <v>6281.48</v>
+        <v>3843</v>
       </c>
       <c r="M157" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N157" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O157" s="12" t="n">
-        <v>5772</v>
+        <v>3843</v>
       </c>
       <c r="P157" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q157" s="13" t="n">
-        <v>11.703</v>
+        <v>0.0006</v>
       </c>
       <c r="R157" s="12" t="n">
-        <v>347.3</v>
+        <v>33.4</v>
       </c>
       <c r="S157" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T157" s="14" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="U157" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V157" s="12" t="n">
-        <v>5338.87</v>
+        <v>3243.4</v>
       </c>
       <c r="W157" s="12" t="n">
-        <v>5.34</v>
+        <v>3.24</v>
       </c>
       <c r="X157" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y157" s="12" t="n">
-        <v>48.05</v>
+        <v>29.18</v>
       </c>
       <c r="Z157" s="12" t="n">
-        <v>56.57</v>
+        <v>46.67</v>
       </c>
       <c r="AA157" s="9" t="s">
         <v>77</v>
@@ -50387,13 +50393,13 @@
         <v>113</v>
       </c>
       <c r="AC157" s="12" t="n">
-        <v>509.48</v>
+        <v>0</v>
       </c>
       <c r="AD157" s="12" t="n">
-        <v>5772</v>
+        <v>3843</v>
       </c>
       <c r="AE157" s="12" t="n">
-        <v>230.88</v>
+        <v>269.01</v>
       </c>
       <c r="AF157" s="12" t="n">
         <v>0</v>
@@ -50498,7 +50504,7 @@
         <v>73</v>
       </c>
       <c r="BN157" s="9" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="BO157" s="9" t="s">
         <v>79</v>
@@ -50512,52 +50518,52 @@
     </row>
     <row r="158" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="8" t="n">
-        <v>312222</v>
+        <v>312224</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>679</v>
+        <v>228</v>
       </c>
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
       <c r="F158" s="9" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G158" s="10" t="s">
         <v>91</v>
       </c>
       <c r="H158" s="9" t="s">
-        <v>506</v>
+        <v>303</v>
       </c>
       <c r="I158" s="9" t="s">
         <v>113</v>
       </c>
       <c r="J158" s="9" t="s">
-        <v>681</v>
+        <v>628</v>
       </c>
       <c r="K158" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L158" s="12" t="n">
-        <v>3843</v>
+        <v>5424.61</v>
       </c>
       <c r="M158" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N158" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O158" s="12" t="n">
-        <v>3843</v>
+        <v>5424.61</v>
       </c>
       <c r="P158" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q158" s="13" t="n">
-        <v>0.0006</v>
+        <v>0.426736</v>
       </c>
       <c r="R158" s="12" t="n">
-        <v>33.4</v>
+        <v>118.51</v>
       </c>
       <c r="S158" s="12" t="n">
         <v>0</v>
@@ -50569,19 +50575,19 @@
         <v>76</v>
       </c>
       <c r="V158" s="12" t="n">
-        <v>3243.4</v>
+        <v>4578.23</v>
       </c>
       <c r="W158" s="12" t="n">
-        <v>3.24</v>
+        <v>4.58</v>
       </c>
       <c r="X158" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y158" s="12" t="n">
-        <v>29.18</v>
+        <v>41.2</v>
       </c>
       <c r="Z158" s="12" t="n">
-        <v>46.67</v>
+        <v>28</v>
       </c>
       <c r="AA158" s="9" t="s">
         <v>77</v>
@@ -50593,10 +50599,10 @@
         <v>0</v>
       </c>
       <c r="AD158" s="12" t="n">
-        <v>3843</v>
+        <v>5424.61</v>
       </c>
       <c r="AE158" s="12" t="n">
-        <v>269.01</v>
+        <v>379.72</v>
       </c>
       <c r="AF158" s="12" t="n">
         <v>0</v>
@@ -50715,73 +50721,73 @@
     </row>
     <row r="159" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="8" t="n">
-        <v>312224</v>
+        <v>312235</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>228</v>
+        <v>684</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
       <c r="F159" s="9" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>91</v>
+        <v>686</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>303</v>
+        <v>113</v>
       </c>
       <c r="I159" s="9" t="s">
-        <v>113</v>
+        <v>687</v>
       </c>
       <c r="J159" s="9" t="s">
-        <v>631</v>
+        <v>259</v>
       </c>
       <c r="K159" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L159" s="12" t="n">
-        <v>5424.61</v>
+        <v>20785</v>
       </c>
       <c r="M159" s="12" t="n">
-        <v>0</v>
+        <v>698.34</v>
       </c>
       <c r="N159" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O159" s="12" t="n">
-        <v>5424.61</v>
+        <v>21483.34</v>
       </c>
       <c r="P159" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q159" s="13" t="n">
-        <v>0.426736</v>
+        <v>35.0208</v>
       </c>
       <c r="R159" s="12" t="n">
-        <v>118.51</v>
+        <v>38200</v>
       </c>
       <c r="S159" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T159" s="14" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="U159" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V159" s="12" t="n">
-        <v>4578.23</v>
+        <v>15089.91</v>
       </c>
       <c r="W159" s="12" t="n">
-        <v>4.58</v>
+        <v>15.09</v>
       </c>
       <c r="X159" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y159" s="12" t="n">
-        <v>41.2</v>
+        <v>135.81</v>
       </c>
       <c r="Z159" s="12" t="n">
         <v>28</v>
@@ -50790,16 +50796,16 @@
         <v>77</v>
       </c>
       <c r="AB159" s="9" t="s">
-        <v>113</v>
+        <v>687</v>
       </c>
       <c r="AC159" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AD159" s="12" t="n">
-        <v>5424.61</v>
+        <v>20785</v>
       </c>
       <c r="AE159" s="12" t="n">
-        <v>379.72</v>
+        <v>4157</v>
       </c>
       <c r="AF159" s="12" t="n">
         <v>0</v>
@@ -50868,7 +50874,7 @@
         <v>78</v>
       </c>
       <c r="BB159" s="10" t="s">
-        <v>95</v>
+        <v>655</v>
       </c>
       <c r="BC159" s="14" t="s">
         <v>79</v>
@@ -50904,7 +50910,7 @@
         <v>73</v>
       </c>
       <c r="BN159" s="9" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="BO159" s="9" t="s">
         <v>79</v>
@@ -50918,25 +50924,25 @@
     </row>
     <row r="160" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="8" t="n">
-        <v>312235</v>
+        <v>312236</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
       <c r="F160" s="9" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="G160" s="10" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="H160" s="9" t="s">
         <v>113</v>
       </c>
       <c r="I160" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="J160" s="9" t="s">
         <v>259</v>
@@ -50945,46 +50951,46 @@
         <v>74</v>
       </c>
       <c r="L160" s="12" t="n">
-        <v>20785</v>
+        <v>10524.93</v>
       </c>
       <c r="M160" s="12" t="n">
-        <v>698.34</v>
+        <v>0</v>
       </c>
       <c r="N160" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O160" s="12" t="n">
-        <v>21483.34</v>
+        <v>10524.93</v>
       </c>
       <c r="P160" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q160" s="13" t="n">
-        <v>35.0208</v>
+        <v>0.019481</v>
       </c>
       <c r="R160" s="12" t="n">
-        <v>38200</v>
+        <v>11000</v>
       </c>
       <c r="S160" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T160" s="14" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="U160" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V160" s="12" t="n">
-        <v>15089.91</v>
+        <v>8405.21</v>
       </c>
       <c r="W160" s="12" t="n">
-        <v>15.09</v>
+        <v>8.41</v>
       </c>
       <c r="X160" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y160" s="12" t="n">
-        <v>135.81</v>
+        <v>75.65</v>
       </c>
       <c r="Z160" s="12" t="n">
         <v>28</v>
@@ -50993,16 +50999,16 @@
         <v>77</v>
       </c>
       <c r="AB160" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="AC160" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AD160" s="12" t="n">
-        <v>20785</v>
+        <v>10524.93</v>
       </c>
       <c r="AE160" s="12" t="n">
-        <v>4157</v>
+        <v>1262.99</v>
       </c>
       <c r="AF160" s="12" t="n">
         <v>0</v>
@@ -51071,7 +51077,7 @@
         <v>78</v>
       </c>
       <c r="BB160" s="10" t="s">
-        <v>658</v>
+        <v>95</v>
       </c>
       <c r="BC160" s="14" t="s">
         <v>79</v>
@@ -51107,7 +51113,7 @@
         <v>73</v>
       </c>
       <c r="BN160" s="9" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="BO160" s="9" t="s">
         <v>79</v>
@@ -51121,25 +51127,25 @@
     </row>
     <row r="161" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="8" t="n">
-        <v>312236</v>
+        <v>312239</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
       <c r="F161" s="9" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="H161" s="9" t="s">
         <v>113</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="J161" s="9" t="s">
         <v>259</v>
@@ -51148,7 +51154,7 @@
         <v>74</v>
       </c>
       <c r="L161" s="12" t="n">
-        <v>10524.93</v>
+        <v>24705.37</v>
       </c>
       <c r="M161" s="12" t="n">
         <v>0</v>
@@ -51157,16 +51163,16 @@
         <v>1</v>
       </c>
       <c r="O161" s="12" t="n">
-        <v>10524.93</v>
+        <v>24705.37</v>
       </c>
       <c r="P161" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q161" s="13" t="n">
-        <v>0.019481</v>
+        <v>0.019446</v>
       </c>
       <c r="R161" s="12" t="n">
-        <v>11000</v>
+        <v>21000</v>
       </c>
       <c r="S161" s="12" t="n">
         <v>0</v>
@@ -51178,16 +51184,16 @@
         <v>76</v>
       </c>
       <c r="V161" s="12" t="n">
-        <v>8405.21</v>
+        <v>19729.71</v>
       </c>
       <c r="W161" s="12" t="n">
-        <v>8.41</v>
+        <v>19.73</v>
       </c>
       <c r="X161" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y161" s="12" t="n">
-        <v>75.65</v>
+        <v>177.57</v>
       </c>
       <c r="Z161" s="12" t="n">
         <v>28</v>
@@ -51196,16 +51202,16 @@
         <v>77</v>
       </c>
       <c r="AB161" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="AC161" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AD161" s="12" t="n">
-        <v>10524.93</v>
+        <v>24705.37</v>
       </c>
       <c r="AE161" s="12" t="n">
-        <v>1262.99</v>
+        <v>2964.64</v>
       </c>
       <c r="AF161" s="12" t="n">
         <v>0</v>
@@ -51324,91 +51330,91 @@
     </row>
     <row r="162" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="8" t="n">
-        <v>312239</v>
+        <v>312244</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
       <c r="F162" s="9" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G162" s="10" t="s">
-        <v>695</v>
+        <v>135</v>
       </c>
       <c r="H162" s="9" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="I162" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="J162" s="9" t="s">
-        <v>259</v>
+        <v>101</v>
       </c>
       <c r="K162" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L162" s="12" t="n">
-        <v>24705.37</v>
+        <v>86836</v>
       </c>
       <c r="M162" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N162" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O162" s="12" t="n">
-        <v>24705.37</v>
+        <v>86836</v>
       </c>
       <c r="P162" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q162" s="13" t="n">
-        <v>0.019446</v>
+        <v>278.076</v>
       </c>
       <c r="R162" s="12" t="n">
-        <v>21000</v>
+        <v>15347.82</v>
       </c>
       <c r="S162" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T162" s="14" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="U162" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V162" s="12" t="n">
-        <v>19729.71</v>
+        <v>0</v>
       </c>
       <c r="W162" s="12" t="n">
-        <v>19.73</v>
+        <v>0</v>
       </c>
       <c r="X162" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y162" s="12" t="n">
-        <v>177.57</v>
+        <v>0</v>
       </c>
       <c r="Z162" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AA162" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AB162" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="AC162" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AD162" s="12" t="n">
-        <v>24705.37</v>
+        <v>86836</v>
       </c>
       <c r="AE162" s="12" t="n">
-        <v>2964.64</v>
+        <v>10420.32</v>
       </c>
       <c r="AF162" s="12" t="n">
         <v>0</v>
@@ -51513,7 +51519,7 @@
         <v>73</v>
       </c>
       <c r="BN162" s="9" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="BO162" s="9" t="s">
         <v>79</v>
@@ -51527,10 +51533,10 @@
     </row>
     <row r="163" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="8" t="n">
-        <v>312244</v>
+        <v>312253</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>701</v>
+        <v>652</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
@@ -51539,40 +51545,40 @@
         <v>702</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="I163" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="J163" s="9" t="s">
-        <v>101</v>
+        <v>362</v>
       </c>
       <c r="K163" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L163" s="12" t="n">
-        <v>86836</v>
+        <v>5000</v>
       </c>
       <c r="M163" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N163" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O163" s="12" t="n">
-        <v>86836</v>
+        <v>5000</v>
       </c>
       <c r="P163" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q163" s="13" t="n">
-        <v>278.076</v>
+        <v>23.14125</v>
       </c>
       <c r="R163" s="12" t="n">
-        <v>15347.82</v>
+        <v>360</v>
       </c>
       <c r="S163" s="12" t="n">
         <v>0</v>
@@ -51596,22 +51602,22 @@
         <v>0</v>
       </c>
       <c r="Z163" s="12" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="AA163" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AB163" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="AC163" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AD163" s="12" t="n">
-        <v>86836</v>
+        <v>5000</v>
       </c>
       <c r="AE163" s="12" t="n">
-        <v>10420.32</v>
+        <v>190</v>
       </c>
       <c r="AF163" s="12" t="n">
         <v>0</v>
@@ -51680,7 +51686,7 @@
         <v>78</v>
       </c>
       <c r="BB163" s="10" t="s">
-        <v>95</v>
+        <v>655</v>
       </c>
       <c r="BC163" s="14" t="s">
         <v>79</v>
@@ -51730,10 +51736,10 @@
     </row>
     <row r="164" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="8" t="n">
-        <v>312253</v>
+        <v>312254</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C164" s="9"/>
       <c r="D164" s="9"/>
@@ -51748,7 +51754,7 @@
         <v>113</v>
       </c>
       <c r="I164" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="J164" s="9" t="s">
         <v>362</v>
@@ -51757,7 +51763,7 @@
         <v>74</v>
       </c>
       <c r="L164" s="12" t="n">
-        <v>5000</v>
+        <v>5758</v>
       </c>
       <c r="M164" s="12" t="n">
         <v>0</v>
@@ -51766,16 +51772,16 @@
         <v>1</v>
       </c>
       <c r="O164" s="12" t="n">
-        <v>5000</v>
+        <v>5758</v>
       </c>
       <c r="P164" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q164" s="13" t="n">
-        <v>23.14125</v>
+        <v>13.69</v>
       </c>
       <c r="R164" s="12" t="n">
-        <v>360</v>
+        <v>475</v>
       </c>
       <c r="S164" s="12" t="n">
         <v>0</v>
@@ -51805,16 +51811,16 @@
         <v>77</v>
       </c>
       <c r="AB164" s="9" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="AC164" s="12" t="n">
         <v>0</v>
       </c>
       <c r="AD164" s="12" t="n">
-        <v>5000</v>
+        <v>5758</v>
       </c>
       <c r="AE164" s="12" t="n">
-        <v>190</v>
+        <v>219.38</v>
       </c>
       <c r="AF164" s="12" t="n">
         <v>0</v>
@@ -51883,7 +51889,7 @@
         <v>78</v>
       </c>
       <c r="BB164" s="10" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="BC164" s="14" t="s">
         <v>79</v>
@@ -51933,10 +51939,10 @@
     </row>
     <row r="165" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="8" t="n">
-        <v>312254</v>
+        <v>312261</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>655</v>
+        <v>245</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="9"/>
@@ -51945,22 +51951,22 @@
         <v>708</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="I165" s="9" t="s">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="J165" s="9" t="s">
-        <v>362</v>
+        <v>247</v>
       </c>
       <c r="K165" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L165" s="12" t="n">
-        <v>5758</v>
+        <v>639.27</v>
       </c>
       <c r="M165" s="12" t="n">
         <v>0</v>
@@ -51969,55 +51975,55 @@
         <v>1</v>
       </c>
       <c r="O165" s="12" t="n">
-        <v>5758</v>
+        <v>619.15</v>
       </c>
       <c r="P165" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q165" s="13" t="n">
-        <v>13.69</v>
+        <v>0.000735</v>
       </c>
       <c r="R165" s="12" t="n">
-        <v>475</v>
+        <v>1.12</v>
       </c>
       <c r="S165" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T165" s="14" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="U165" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V165" s="12" t="n">
-        <v>0</v>
+        <v>539.4</v>
       </c>
       <c r="W165" s="12" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="X165" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y165" s="12" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Z165" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA165" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AB165" s="9" t="s">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="AC165" s="12" t="n">
-        <v>0</v>
+        <v>20.12</v>
       </c>
       <c r="AD165" s="12" t="n">
-        <v>5758</v>
+        <v>619.15</v>
       </c>
       <c r="AE165" s="12" t="n">
-        <v>219.38</v>
+        <v>24.77</v>
       </c>
       <c r="AF165" s="12" t="n">
         <v>0</v>
@@ -52086,7 +52092,7 @@
         <v>78</v>
       </c>
       <c r="BB165" s="10" t="s">
-        <v>658</v>
+        <v>95</v>
       </c>
       <c r="BC165" s="14" t="s">
         <v>79</v>
@@ -52122,7 +52128,7 @@
         <v>73</v>
       </c>
       <c r="BN165" s="9" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="BO165" s="9" t="s">
         <v>79</v>
@@ -52136,91 +52142,91 @@
     </row>
     <row r="166" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="8" t="n">
-        <v>312261</v>
+        <v>312264</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>245</v>
+        <v>712</v>
       </c>
       <c r="C166" s="9"/>
       <c r="D166" s="9"/>
       <c r="E166" s="9"/>
       <c r="F166" s="9" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G166" s="10" t="s">
-        <v>135</v>
+        <v>714</v>
       </c>
       <c r="H166" s="9" t="s">
-        <v>179</v>
+        <v>291</v>
       </c>
       <c r="I166" s="9" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="J166" s="9" t="s">
-        <v>247</v>
+        <v>570</v>
       </c>
       <c r="K166" s="11" t="s">
         <v>74</v>
       </c>
       <c r="L166" s="12" t="n">
-        <v>639.27</v>
+        <v>182438.71</v>
       </c>
       <c r="M166" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N166" s="12" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="O166" s="12" t="n">
-        <v>619.15</v>
+        <v>180778.99</v>
       </c>
       <c r="P166" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q166" s="13" t="n">
-        <v>0.000735</v>
+        <v>176.614236</v>
       </c>
       <c r="R166" s="12" t="n">
-        <v>1.12</v>
+        <v>2984.31</v>
       </c>
       <c r="S166" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T166" s="14" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="U166" s="15" t="s">
         <v>76</v>
       </c>
       <c r="V166" s="12" t="n">
-        <v>539.4</v>
+        <v>157483.12</v>
       </c>
       <c r="W166" s="12" t="n">
-        <v>0.54</v>
+        <v>157.48</v>
       </c>
       <c r="X166" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Y166" s="12" t="n">
-        <v>4.85</v>
+        <v>1417.35</v>
       </c>
       <c r="Z166" s="12" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="AA166" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AB166" s="9" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AC166" s="12" t="n">
-        <v>20.12</v>
+        <v>1659.72</v>
       </c>
       <c r="AD166" s="12" t="n">
-        <v>619.15</v>
+        <v>180778.99</v>
       </c>
       <c r="AE166" s="12" t="n">
-        <v>24.77</v>
+        <v>7243.87</v>
       </c>
       <c r="AF166" s="12" t="n">
         <v>0</v>
@@ -52325,7 +52331,7 @@
         <v>73</v>
       </c>
       <c r="BN166" s="9" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="BO166" s="9" t="s">
         <v>79</v>
@@ -52342,7 +52348,7 @@
     </row>
     <row r="168" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="17" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B168" s="17"/>
       <c r="C168" s="17"/>
@@ -52372,7 +52378,7 @@
     </row>
     <row r="169" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="18" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B169" s="18" t="s">
         <v>12</v>
@@ -52381,7 +52387,7 @@
         <v>15</v>
       </c>
       <c r="D169" s="18" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E169" s="18" t="s">
         <v>28</v>
@@ -52396,7 +52402,7 @@
         <v>31</v>
       </c>
       <c r="I169" s="18" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="J169" s="18" t="s">
         <v>33</v>
@@ -52408,7 +52414,7 @@
         <v>34</v>
       </c>
       <c r="M169" s="18" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="N169" s="18" t="s">
         <v>36</v>
@@ -52426,10 +52432,10 @@
         <v>16</v>
       </c>
       <c r="S169" s="18" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="T169" s="18" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="U169" s="18" t="s">
         <v>40</v>
@@ -52441,13 +52447,13 @@
         <v>21</v>
       </c>
       <c r="X169" s="18" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="Y169" s="18" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="Z169" s="18" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -52464,13 +52470,13 @@
         <v>0</v>
       </c>
       <c r="E170" s="19" t="n">
-        <v>119437.67</v>
+        <v>121097.39</v>
       </c>
       <c r="F170" s="19" t="n">
-        <v>5650813.71</v>
+        <v>5770201.3</v>
       </c>
       <c r="G170" s="19" t="n">
-        <v>374619.71</v>
+        <v>377566.18</v>
       </c>
       <c r="H170" s="19" t="n">
         <v>0</v>
@@ -52482,7 +52488,7 @@
         <v>9646.28</v>
       </c>
       <c r="K170" s="19" t="n">
-        <v>5839691.36</v>
+        <v>5960738.67</v>
       </c>
       <c r="L170" s="19" t="n">
         <v>0</v>
@@ -52503,13 +52509,13 @@
         <v>0</v>
       </c>
       <c r="R170" s="20" t="n">
-        <v>11013.771478</v>
+        <v>11127.757414</v>
       </c>
       <c r="S170" s="19" t="n">
-        <v>5709946.98</v>
+        <v>5829334.57</v>
       </c>
       <c r="T170" s="19" t="n">
-        <v>5839691.36</v>
+        <v>5960738.67</v>
       </c>
       <c r="U170" s="19" t="n">
         <v>0</v>
@@ -52518,16 +52524,16 @@
         <v>0</v>
       </c>
       <c r="W170" s="19" t="n">
-        <v>4739590.13</v>
+        <v>4845260.45</v>
       </c>
       <c r="X170" s="19" t="n">
-        <v>4739.56</v>
+        <v>4845.23</v>
       </c>
       <c r="Y170" s="19" t="n">
         <v>0</v>
       </c>
       <c r="Z170" s="19" t="n">
-        <v>42656.42</v>
+        <v>43607.46</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -52562,18 +52568,18 @@
         <v>49</v>
       </c>
       <c r="K171" s="18" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="L171" s="18" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="M171" s="18" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="19" t="n">
-        <v>416592.91</v>
+        <v>414853.48</v>
       </c>
       <c r="B172" s="19" t="n">
         <v>0</v>
@@ -52582,7 +52588,7 @@
         <v>0</v>
       </c>
       <c r="D172" s="19" t="n">
-        <v>38.02</v>
+        <v>38.93</v>
       </c>
       <c r="E172" s="19" t="n">
         <v>0</v>
@@ -52617,7 +52623,7 @@
     </row>
     <row r="174" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="21" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B174" s="21"/>
       <c r="C174" s="21"/>
@@ -52763,7 +52769,7 @@
     </row>
     <row r="176" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -52836,7 +52842,7 @@
     </row>
     <row r="177" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -52909,7 +52915,7 @@
     </row>
     <row r="178" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -53055,7 +53061,7 @@
     </row>
     <row r="180" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -53128,7 +53134,7 @@
     </row>
     <row r="181" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -53201,7 +53207,7 @@
     </row>
     <row r="182" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -53274,7 +53280,7 @@
     </row>
     <row r="183" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -53347,7 +53353,7 @@
     </row>
     <row r="184" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>

--- a/tratando_tabelas/objetiva/entradas_objetiva.xlsx
+++ b/tratando_tabelas/objetiva/entradas_objetiva.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6760" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6800" uniqueCount="757">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.8 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 07/08/2026 09:17:21</t>
+    <t xml:space="preserve">Emitido em: 07/08/2026 09:23:34</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -2210,6 +2210,21 @@
   </si>
   <si>
     <t xml:space="preserve">43260788674080000101550010009356751586357000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">789 - TRAMONTINA GARIBALDI SA INDUSTRIA METALURGICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.347.987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.013,91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260790049792000181550010013479871371368339</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -19078,7 +19093,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BQ188"/>
+  <dimension ref="A1:BQ189"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="18.02"/>
@@ -53195,432 +53210,562 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="4"/>
+      <c r="A171" s="8" t="n">
+        <v>312287</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="C171" s="9"/>
+      <c r="D171" s="9"/>
+      <c r="E171" s="9"/>
+      <c r="F171" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="G171" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H171" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="I171" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="J171" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K171" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L171" s="12" t="n">
+        <v>4013.91</v>
+      </c>
+      <c r="M171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O171" s="12" t="n">
+        <v>4013.91</v>
+      </c>
+      <c r="P171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="13" t="n">
+        <v>0.181064</v>
+      </c>
+      <c r="R171" s="12" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="S171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" s="14" t="s">
+        <v>732</v>
+      </c>
+      <c r="U171" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="V171" s="12" t="n">
+        <v>3853.35</v>
+      </c>
+      <c r="W171" s="12" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="X171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y171" s="12" t="n">
+        <v>34.68</v>
+      </c>
+      <c r="Z171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA171" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB171" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="AC171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD171" s="12" t="n">
+        <v>4013.91</v>
+      </c>
+      <c r="AE171" s="12" t="n">
+        <v>160.56</v>
+      </c>
+      <c r="AF171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP171" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS171" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA171" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB171" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="BC171" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BD171" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BE171" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF171" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BG171" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH171" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BI171" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BJ171" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK171" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BL171" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM171" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BN171" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="BO171" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BP171" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BQ171" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="172" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="17" t="s">
-        <v>730</v>
-      </c>
-      <c r="B172" s="17"/>
-      <c r="C172" s="17"/>
-      <c r="D172" s="17"/>
-      <c r="E172" s="17"/>
-      <c r="F172" s="17"/>
-      <c r="G172" s="17"/>
-      <c r="H172" s="17"/>
-      <c r="I172" s="17"/>
-      <c r="J172" s="17"/>
-      <c r="K172" s="17"/>
-      <c r="L172" s="17"/>
-      <c r="M172" s="17"/>
-      <c r="N172" s="17"/>
-      <c r="O172" s="17"/>
-      <c r="P172" s="17"/>
-      <c r="Q172" s="17"/>
-      <c r="R172" s="17"/>
-      <c r="S172" s="17"/>
-      <c r="T172" s="17"/>
-      <c r="U172" s="17"/>
-      <c r="V172" s="17"/>
-      <c r="W172" s="17"/>
-      <c r="X172" s="17"/>
-      <c r="Y172" s="17"/>
-      <c r="Z172" s="17"/>
+    <row r="172" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="4"/>
     </row>
     <row r="173" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="18" t="s">
-        <v>731</v>
-      </c>
-      <c r="B173" s="18" t="s">
+      <c r="A173" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="B173" s="17"/>
+      <c r="C173" s="17"/>
+      <c r="D173" s="17"/>
+      <c r="E173" s="17"/>
+      <c r="F173" s="17"/>
+      <c r="G173" s="17"/>
+      <c r="H173" s="17"/>
+      <c r="I173" s="17"/>
+      <c r="J173" s="17"/>
+      <c r="K173" s="17"/>
+      <c r="L173" s="17"/>
+      <c r="M173" s="17"/>
+      <c r="N173" s="17"/>
+      <c r="O173" s="17"/>
+      <c r="P173" s="17"/>
+      <c r="Q173" s="17"/>
+      <c r="R173" s="17"/>
+      <c r="S173" s="17"/>
+      <c r="T173" s="17"/>
+      <c r="U173" s="17"/>
+      <c r="V173" s="17"/>
+      <c r="W173" s="17"/>
+      <c r="X173" s="17"/>
+      <c r="Y173" s="17"/>
+      <c r="Z173" s="17"/>
+    </row>
+    <row r="174" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="18" t="s">
+        <v>736</v>
+      </c>
+      <c r="B174" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C173" s="18" t="s">
+      <c r="C174" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D173" s="18" t="s">
-        <v>732</v>
-      </c>
-      <c r="E173" s="18" t="s">
+      <c r="D174" s="18" t="s">
+        <v>737</v>
+      </c>
+      <c r="E174" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F173" s="18" t="s">
+      <c r="F174" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G173" s="18" t="s">
+      <c r="G174" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H173" s="18" t="s">
+      <c r="H174" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="I173" s="18" t="s">
-        <v>733</v>
-      </c>
-      <c r="J173" s="18" t="s">
+      <c r="I174" s="18" t="s">
+        <v>738</v>
+      </c>
+      <c r="J174" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="K173" s="18" t="s">
+      <c r="K174" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="L173" s="18" t="s">
+      <c r="L174" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="M173" s="18" t="s">
-        <v>734</v>
-      </c>
-      <c r="N173" s="18" t="s">
+      <c r="M174" s="18" t="s">
+        <v>739</v>
+      </c>
+      <c r="N174" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="O173" s="18" t="s">
+      <c r="O174" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="P173" s="18" t="s">
+      <c r="P174" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="Q173" s="18" t="s">
+      <c r="Q174" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="R173" s="18" t="s">
+      <c r="R174" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="S173" s="18" t="s">
-        <v>735</v>
-      </c>
-      <c r="T173" s="18" t="s">
-        <v>736</v>
-      </c>
-      <c r="U173" s="18" t="s">
+      <c r="S174" s="18" t="s">
+        <v>740</v>
+      </c>
+      <c r="T174" s="18" t="s">
+        <v>741</v>
+      </c>
+      <c r="U174" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="V173" s="18" t="s">
+      <c r="V174" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="W173" s="18" t="s">
+      <c r="W174" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="X173" s="18" t="s">
-        <v>737</v>
-      </c>
-      <c r="Y173" s="18" t="s">
-        <v>738</v>
-      </c>
-      <c r="Z173" s="18" t="s">
-        <v>739</v>
+      <c r="X174" s="18" t="s">
+        <v>742</v>
+      </c>
+      <c r="Y174" s="18" t="s">
+        <v>743</v>
+      </c>
+      <c r="Z174" s="18" t="s">
+        <v>744</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="19" t="n">
-        <v>166</v>
-      </c>
-      <c r="B174" s="19" t="n">
+    <row r="175" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A175" s="19" t="n">
+        <v>167</v>
+      </c>
+      <c r="B175" s="19" t="n">
         <v>3043.14</v>
       </c>
-      <c r="C174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" s="19" t="n">
+      <c r="C175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" s="19" t="n">
         <v>124192.94</v>
       </c>
-      <c r="F174" s="19" t="n">
-        <v>6051032.68</v>
-      </c>
-      <c r="G174" s="19" t="n">
-        <v>402823.91</v>
-      </c>
-      <c r="H174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" s="19" t="n">
+      <c r="F175" s="19" t="n">
+        <v>6055046.59</v>
+      </c>
+      <c r="G175" s="19" t="n">
+        <v>402984.47</v>
+      </c>
+      <c r="H175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="19" t="n">
         <v>9646.28</v>
       </c>
-      <c r="K174" s="19" t="n">
-        <v>6239719.63</v>
-      </c>
-      <c r="L174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M174" s="19" t="n">
+      <c r="K175" s="19" t="n">
+        <v>6243733.54</v>
+      </c>
+      <c r="L175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="19" t="n">
         <v>52664.85</v>
       </c>
-      <c r="N174" s="19" t="n">
+      <c r="N175" s="19" t="n">
         <v>8093.66</v>
       </c>
-      <c r="O174" s="19" t="n">
+      <c r="O175" s="19" t="n">
         <v>373.06</v>
       </c>
-      <c r="P174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R174" s="20" t="n">
-        <v>10953.439397</v>
-      </c>
-      <c r="S174" s="19" t="n">
-        <v>6110476.17</v>
-      </c>
-      <c r="T174" s="19" t="n">
-        <v>6239719.63</v>
-      </c>
-      <c r="U174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W174" s="19" t="n">
-        <v>5077475.1</v>
-      </c>
-      <c r="X174" s="19" t="n">
-        <v>5077.46</v>
-      </c>
-      <c r="Y174" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z174" s="19" t="n">
-        <v>45697.44</v>
+      <c r="P175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" s="20" t="n">
+        <v>10953.620461</v>
+      </c>
+      <c r="S175" s="19" t="n">
+        <v>6114490.08</v>
+      </c>
+      <c r="T175" s="19" t="n">
+        <v>6243733.54</v>
+      </c>
+      <c r="U175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" s="19" t="n">
+        <v>5081328.45</v>
+      </c>
+      <c r="X175" s="19" t="n">
+        <v>5081.32</v>
+      </c>
+      <c r="Y175" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="19" t="n">
+        <v>45732.12</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="18" t="s">
+    <row r="176" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A176" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B175" s="18" t="s">
+      <c r="B176" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C175" s="18" t="s">
+      <c r="C176" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D175" s="18" t="s">
+      <c r="D176" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E175" s="18" t="s">
+      <c r="E176" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F175" s="18" t="s">
+      <c r="F176" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G175" s="18" t="s">
+      <c r="G176" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="H175" s="18" t="s">
+      <c r="H176" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I175" s="18" t="s">
+      <c r="I176" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="J175" s="18" t="s">
+      <c r="J176" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="K175" s="18" t="s">
-        <v>740</v>
-      </c>
-      <c r="L175" s="18" t="s">
-        <v>741</v>
-      </c>
-      <c r="M175" s="18" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="19" t="n">
-        <v>409138.69</v>
-      </c>
-      <c r="B176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D176" s="19" t="n">
-        <v>39.56</v>
-      </c>
-      <c r="E176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L176" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M176" s="19" t="n">
-        <v>0</v>
+      <c r="K176" s="18" t="s">
+        <v>745</v>
+      </c>
+      <c r="L176" s="18" t="s">
+        <v>746</v>
+      </c>
+      <c r="M176" s="18" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="4"/>
+      <c r="A177" s="19" t="n">
+        <v>409179.51</v>
+      </c>
+      <c r="B177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" s="19" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="E177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="178" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="21" t="s">
-        <v>743</v>
-      </c>
-      <c r="B178" s="21"/>
-      <c r="C178" s="21"/>
-      <c r="D178" s="21"/>
-      <c r="E178" s="21"/>
-      <c r="F178" s="21"/>
-      <c r="G178" s="21"/>
-      <c r="H178" s="21"/>
-      <c r="I178" s="21"/>
-      <c r="J178" s="21"/>
-      <c r="K178" s="21"/>
-      <c r="L178" s="21"/>
-      <c r="M178" s="21"/>
-      <c r="N178" s="21"/>
-      <c r="O178" s="21"/>
-      <c r="P178" s="21"/>
-      <c r="Q178" s="21"/>
-      <c r="R178" s="21"/>
-      <c r="S178" s="21"/>
-      <c r="T178" s="21"/>
-      <c r="U178" s="21"/>
-      <c r="V178" s="21"/>
-      <c r="W178" s="21"/>
-      <c r="X178" s="21"/>
-      <c r="Y178" s="21"/>
-      <c r="Z178" s="21"/>
-      <c r="AA178" s="21"/>
-      <c r="AB178" s="21"/>
-      <c r="AC178" s="21"/>
-      <c r="AD178" s="21"/>
-      <c r="AE178" s="21"/>
-      <c r="AF178" s="21"/>
-      <c r="AG178" s="21"/>
-      <c r="AH178" s="21"/>
-      <c r="AI178" s="21"/>
-      <c r="AJ178" s="21"/>
-      <c r="AK178" s="21"/>
-      <c r="AL178" s="21"/>
-      <c r="AM178" s="21"/>
-      <c r="AN178" s="21"/>
-      <c r="AO178" s="21"/>
-      <c r="AP178" s="21"/>
-      <c r="AQ178" s="21"/>
-      <c r="AR178" s="21"/>
-      <c r="AS178" s="21"/>
-      <c r="AT178" s="21"/>
-      <c r="AU178" s="21"/>
-      <c r="AV178" s="21"/>
-      <c r="AW178" s="21"/>
-      <c r="AX178" s="21"/>
-      <c r="AY178" s="21"/>
-      <c r="AZ178" s="21"/>
-      <c r="BA178" s="21"/>
-      <c r="BB178" s="21"/>
-      <c r="BC178" s="21"/>
-      <c r="BD178" s="21"/>
-      <c r="BE178" s="21"/>
-      <c r="BF178" s="21"/>
-      <c r="BG178" s="21"/>
-      <c r="BH178" s="21"/>
-      <c r="BI178" s="21"/>
-      <c r="BJ178" s="21"/>
-      <c r="BK178" s="21"/>
-      <c r="BL178" s="21"/>
-      <c r="BM178" s="21"/>
-      <c r="BN178" s="21"/>
-      <c r="BO178" s="21"/>
-      <c r="BP178" s="21"/>
-      <c r="BQ178" s="21"/>
+    <row r="178" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A178" s="4"/>
     </row>
-    <row r="179" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B179" s="4"/>
-      <c r="C179" s="4"/>
-      <c r="D179" s="4"/>
-      <c r="E179" s="4"/>
-      <c r="F179" s="4"/>
-      <c r="G179" s="4"/>
-      <c r="H179" s="4"/>
-      <c r="I179" s="4"/>
-      <c r="J179" s="4"/>
-      <c r="K179" s="4"/>
-      <c r="L179" s="4"/>
-      <c r="M179" s="4"/>
-      <c r="N179" s="4"/>
-      <c r="O179" s="4"/>
-      <c r="P179" s="4"/>
-      <c r="Q179" s="4"/>
-      <c r="R179" s="4"/>
-      <c r="S179" s="4"/>
-      <c r="T179" s="4"/>
-      <c r="U179" s="4"/>
-      <c r="V179" s="4"/>
-      <c r="W179" s="4"/>
-      <c r="X179" s="4"/>
-      <c r="Y179" s="4"/>
-      <c r="Z179" s="4"/>
-      <c r="AA179" s="4"/>
-      <c r="AB179" s="4"/>
-      <c r="AC179" s="4"/>
-      <c r="AD179" s="4"/>
-      <c r="AE179" s="4"/>
-      <c r="AF179" s="4"/>
-      <c r="AG179" s="4"/>
-      <c r="AH179" s="4"/>
-      <c r="AI179" s="4"/>
-      <c r="AJ179" s="4"/>
-      <c r="AK179" s="4"/>
-      <c r="AL179" s="4"/>
-      <c r="AM179" s="4"/>
-      <c r="AN179" s="4"/>
-      <c r="AO179" s="4"/>
-      <c r="AP179" s="4"/>
-      <c r="AQ179" s="4"/>
-      <c r="AR179" s="4"/>
-      <c r="AS179" s="4"/>
-      <c r="AT179" s="4"/>
-      <c r="AU179" s="4"/>
-      <c r="AV179" s="4"/>
-      <c r="AW179" s="4"/>
-      <c r="AX179" s="4"/>
-      <c r="AY179" s="4"/>
-      <c r="AZ179" s="4"/>
-      <c r="BA179" s="4"/>
-      <c r="BB179" s="4"/>
-      <c r="BC179" s="4"/>
-      <c r="BD179" s="4"/>
-      <c r="BE179" s="4"/>
-      <c r="BF179" s="4"/>
-      <c r="BG179" s="4"/>
-      <c r="BH179" s="4"/>
-      <c r="BI179" s="4"/>
-      <c r="BJ179" s="4"/>
-      <c r="BK179" s="4"/>
-      <c r="BL179" s="4"/>
-      <c r="BM179" s="4"/>
-      <c r="BN179" s="4"/>
-      <c r="BO179" s="4"/>
-      <c r="BP179" s="4"/>
-      <c r="BQ179" s="4"/>
+    <row r="179" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="21" t="s">
+        <v>748</v>
+      </c>
+      <c r="B179" s="21"/>
+      <c r="C179" s="21"/>
+      <c r="D179" s="21"/>
+      <c r="E179" s="21"/>
+      <c r="F179" s="21"/>
+      <c r="G179" s="21"/>
+      <c r="H179" s="21"/>
+      <c r="I179" s="21"/>
+      <c r="J179" s="21"/>
+      <c r="K179" s="21"/>
+      <c r="L179" s="21"/>
+      <c r="M179" s="21"/>
+      <c r="N179" s="21"/>
+      <c r="O179" s="21"/>
+      <c r="P179" s="21"/>
+      <c r="Q179" s="21"/>
+      <c r="R179" s="21"/>
+      <c r="S179" s="21"/>
+      <c r="T179" s="21"/>
+      <c r="U179" s="21"/>
+      <c r="V179" s="21"/>
+      <c r="W179" s="21"/>
+      <c r="X179" s="21"/>
+      <c r="Y179" s="21"/>
+      <c r="Z179" s="21"/>
+      <c r="AA179" s="21"/>
+      <c r="AB179" s="21"/>
+      <c r="AC179" s="21"/>
+      <c r="AD179" s="21"/>
+      <c r="AE179" s="21"/>
+      <c r="AF179" s="21"/>
+      <c r="AG179" s="21"/>
+      <c r="AH179" s="21"/>
+      <c r="AI179" s="21"/>
+      <c r="AJ179" s="21"/>
+      <c r="AK179" s="21"/>
+      <c r="AL179" s="21"/>
+      <c r="AM179" s="21"/>
+      <c r="AN179" s="21"/>
+      <c r="AO179" s="21"/>
+      <c r="AP179" s="21"/>
+      <c r="AQ179" s="21"/>
+      <c r="AR179" s="21"/>
+      <c r="AS179" s="21"/>
+      <c r="AT179" s="21"/>
+      <c r="AU179" s="21"/>
+      <c r="AV179" s="21"/>
+      <c r="AW179" s="21"/>
+      <c r="AX179" s="21"/>
+      <c r="AY179" s="21"/>
+      <c r="AZ179" s="21"/>
+      <c r="BA179" s="21"/>
+      <c r="BB179" s="21"/>
+      <c r="BC179" s="21"/>
+      <c r="BD179" s="21"/>
+      <c r="BE179" s="21"/>
+      <c r="BF179" s="21"/>
+      <c r="BG179" s="21"/>
+      <c r="BH179" s="21"/>
+      <c r="BI179" s="21"/>
+      <c r="BJ179" s="21"/>
+      <c r="BK179" s="21"/>
+      <c r="BL179" s="21"/>
+      <c r="BM179" s="21"/>
+      <c r="BN179" s="21"/>
+      <c r="BO179" s="21"/>
+      <c r="BP179" s="21"/>
+      <c r="BQ179" s="21"/>
     </row>
     <row r="180" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="s">
-        <v>744</v>
+        <v>79</v>
       </c>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -53693,7 +53838,7 @@
     </row>
     <row r="181" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -53766,7 +53911,7 @@
     </row>
     <row r="182" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -53839,7 +53984,7 @@
     </row>
     <row r="183" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="s">
-        <v>26</v>
+        <v>751</v>
       </c>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -53912,7 +54057,7 @@
     </row>
     <row r="184" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="s">
-        <v>747</v>
+        <v>26</v>
       </c>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -53985,7 +54130,7 @@
     </row>
     <row r="185" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -54058,7 +54203,7 @@
     </row>
     <row r="186" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="4" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -54131,7 +54276,7 @@
     </row>
     <row r="187" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="4" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -54204,7 +54349,7 @@
     </row>
     <row r="188" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="4" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -54275,8 +54420,81 @@
       <c r="BP188" s="4"/>
       <c r="BQ188" s="4"/>
     </row>
+    <row r="189" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A189" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="B189" s="4"/>
+      <c r="C189" s="4"/>
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
+      <c r="I189" s="4"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
+      <c r="L189" s="4"/>
+      <c r="M189" s="4"/>
+      <c r="N189" s="4"/>
+      <c r="O189" s="4"/>
+      <c r="P189" s="4"/>
+      <c r="Q189" s="4"/>
+      <c r="R189" s="4"/>
+      <c r="S189" s="4"/>
+      <c r="T189" s="4"/>
+      <c r="U189" s="4"/>
+      <c r="V189" s="4"/>
+      <c r="W189" s="4"/>
+      <c r="X189" s="4"/>
+      <c r="Y189" s="4"/>
+      <c r="Z189" s="4"/>
+      <c r="AA189" s="4"/>
+      <c r="AB189" s="4"/>
+      <c r="AC189" s="4"/>
+      <c r="AD189" s="4"/>
+      <c r="AE189" s="4"/>
+      <c r="AF189" s="4"/>
+      <c r="AG189" s="4"/>
+      <c r="AH189" s="4"/>
+      <c r="AI189" s="4"/>
+      <c r="AJ189" s="4"/>
+      <c r="AK189" s="4"/>
+      <c r="AL189" s="4"/>
+      <c r="AM189" s="4"/>
+      <c r="AN189" s="4"/>
+      <c r="AO189" s="4"/>
+      <c r="AP189" s="4"/>
+      <c r="AQ189" s="4"/>
+      <c r="AR189" s="4"/>
+      <c r="AS189" s="4"/>
+      <c r="AT189" s="4"/>
+      <c r="AU189" s="4"/>
+      <c r="AV189" s="4"/>
+      <c r="AW189" s="4"/>
+      <c r="AX189" s="4"/>
+      <c r="AY189" s="4"/>
+      <c r="AZ189" s="4"/>
+      <c r="BA189" s="4"/>
+      <c r="BB189" s="4"/>
+      <c r="BC189" s="4"/>
+      <c r="BD189" s="4"/>
+      <c r="BE189" s="4"/>
+      <c r="BF189" s="4"/>
+      <c r="BG189" s="4"/>
+      <c r="BH189" s="4"/>
+      <c r="BI189" s="4"/>
+      <c r="BJ189" s="4"/>
+      <c r="BK189" s="4"/>
+      <c r="BL189" s="4"/>
+      <c r="BM189" s="4"/>
+      <c r="BN189" s="4"/>
+      <c r="BO189" s="4"/>
+      <c r="BP189" s="4"/>
+      <c r="BQ189" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="182">
+  <mergeCells count="183">
     <mergeCell ref="A1:BM1"/>
     <mergeCell ref="BN1:BQ1"/>
     <mergeCell ref="A2:BQ2"/>
@@ -54447,8 +54665,8 @@
     <mergeCell ref="B168:E168"/>
     <mergeCell ref="B169:E169"/>
     <mergeCell ref="B170:E170"/>
-    <mergeCell ref="A172:Z172"/>
-    <mergeCell ref="A178:BQ178"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="A173:Z173"/>
     <mergeCell ref="A179:BQ179"/>
     <mergeCell ref="A180:BQ180"/>
     <mergeCell ref="A181:BQ181"/>
@@ -54459,6 +54677,7 @@
     <mergeCell ref="A186:BQ186"/>
     <mergeCell ref="A187:BQ187"/>
     <mergeCell ref="A188:BQ188"/>
+    <mergeCell ref="A189:BQ189"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/objetiva/entradas_objetiva.xlsx
+++ b/tratando_tabelas/objetiva/entradas_objetiva.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Santri ADM 1.1.5.8 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 10/08/2026 10:54:46</t>
+    <t xml:space="preserve">Emitido em: 10/08/2026 11:02:43</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>

--- a/tratando_tabelas/objetiva/entradas_objetiva.xlsx
+++ b/tratando_tabelas/objetiva/entradas_objetiva.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Santri ADM 1.1.5.8 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 10/08/2026 11:02:43</t>
+    <t xml:space="preserve">Emitido em: 10/08/2026 11:33:09</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>

--- a/tratando_tabelas/objetiva/entradas_objetiva.xlsx
+++ b/tratando_tabelas/objetiva/entradas_objetiva.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Santri ADM 1.1.5.8 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 10/08/2026 11:33:09</t>
+    <t xml:space="preserve">Emitido em: 10/08/2026 11:47:08</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>

--- a/tratando_tabelas/objetiva/entradas_objetiva.xlsx
+++ b/tratando_tabelas/objetiva/entradas_objetiva.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5800" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5840" uniqueCount="652">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.8 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 11/08/2026 07:50:13</t>
+    <t xml:space="preserve">Emitido em: 11/08/2026 08:47:55</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -1898,6 +1898,18 @@
   </si>
   <si>
     <t xml:space="preserve">52260833081704002210550180000868141038448487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.615 - TENASTEEL INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.349,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260814048772000108550040000097641363099952</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -18766,7 +18778,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BQ164"/>
+  <dimension ref="A1:BQ165"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="18.02"/>
@@ -48011,432 +48023,562 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="4"/>
+      <c r="A147" s="8" t="n">
+        <v>312428</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="C147" s="9"/>
+      <c r="D147" s="9"/>
+      <c r="E147" s="9"/>
+      <c r="F147" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="I147" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="J147" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="K147" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L147" s="12" t="n">
+        <v>19349.6</v>
+      </c>
+      <c r="M147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="O147" s="12" t="n">
+        <v>18759.55</v>
+      </c>
+      <c r="P147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="13" t="n">
+        <v>0.339544</v>
+      </c>
+      <c r="R147" s="12" t="n">
+        <v>941.01</v>
+      </c>
+      <c r="S147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="U147" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="V147" s="12" t="n">
+        <v>15832.59</v>
+      </c>
+      <c r="W147" s="12" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="X147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="12" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="Z147" s="12" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="AA147" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB147" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="AC147" s="12" t="n">
+        <v>590.05</v>
+      </c>
+      <c r="AD147" s="12" t="n">
+        <v>18759.55</v>
+      </c>
+      <c r="AE147" s="12" t="n">
+        <v>1313.17</v>
+      </c>
+      <c r="AF147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS147" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA147" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB147" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="BC147" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BD147" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BE147" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF147" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BG147" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH147" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BI147" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BJ147" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK147" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BL147" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM147" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BN147" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="BO147" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BP147" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BQ147" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="148" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="17" t="s">
-        <v>626</v>
-      </c>
-      <c r="B148" s="17"/>
-      <c r="C148" s="17"/>
-      <c r="D148" s="17"/>
-      <c r="E148" s="17"/>
-      <c r="F148" s="17"/>
-      <c r="G148" s="17"/>
-      <c r="H148" s="17"/>
-      <c r="I148" s="17"/>
-      <c r="J148" s="17"/>
-      <c r="K148" s="17"/>
-      <c r="L148" s="17"/>
-      <c r="M148" s="17"/>
-      <c r="N148" s="17"/>
-      <c r="O148" s="17"/>
-      <c r="P148" s="17"/>
-      <c r="Q148" s="17"/>
-      <c r="R148" s="17"/>
-      <c r="S148" s="17"/>
-      <c r="T148" s="17"/>
-      <c r="U148" s="17"/>
-      <c r="V148" s="17"/>
-      <c r="W148" s="17"/>
-      <c r="X148" s="17"/>
-      <c r="Y148" s="17"/>
-      <c r="Z148" s="17"/>
+    <row r="148" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="4"/>
     </row>
     <row r="149" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="18" t="s">
-        <v>627</v>
-      </c>
-      <c r="B149" s="18" t="s">
+      <c r="A149" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="B149" s="17"/>
+      <c r="C149" s="17"/>
+      <c r="D149" s="17"/>
+      <c r="E149" s="17"/>
+      <c r="F149" s="17"/>
+      <c r="G149" s="17"/>
+      <c r="H149" s="17"/>
+      <c r="I149" s="17"/>
+      <c r="J149" s="17"/>
+      <c r="K149" s="17"/>
+      <c r="L149" s="17"/>
+      <c r="M149" s="17"/>
+      <c r="N149" s="17"/>
+      <c r="O149" s="17"/>
+      <c r="P149" s="17"/>
+      <c r="Q149" s="17"/>
+      <c r="R149" s="17"/>
+      <c r="S149" s="17"/>
+      <c r="T149" s="17"/>
+      <c r="U149" s="17"/>
+      <c r="V149" s="17"/>
+      <c r="W149" s="17"/>
+      <c r="X149" s="17"/>
+      <c r="Y149" s="17"/>
+      <c r="Z149" s="17"/>
+    </row>
+    <row r="150" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="B150" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C149" s="18" t="s">
+      <c r="C150" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D149" s="18" t="s">
-        <v>628</v>
-      </c>
-      <c r="E149" s="18" t="s">
+      <c r="D150" s="18" t="s">
+        <v>632</v>
+      </c>
+      <c r="E150" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F149" s="18" t="s">
+      <c r="F150" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G149" s="18" t="s">
+      <c r="G150" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H149" s="18" t="s">
+      <c r="H150" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="I149" s="18" t="s">
-        <v>629</v>
-      </c>
-      <c r="J149" s="18" t="s">
+      <c r="I150" s="18" t="s">
+        <v>633</v>
+      </c>
+      <c r="J150" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="K149" s="18" t="s">
+      <c r="K150" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="L149" s="18" t="s">
+      <c r="L150" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="M149" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="N149" s="18" t="s">
+      <c r="M150" s="18" t="s">
+        <v>634</v>
+      </c>
+      <c r="N150" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="O149" s="18" t="s">
+      <c r="O150" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="P149" s="18" t="s">
+      <c r="P150" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="Q149" s="18" t="s">
+      <c r="Q150" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="R149" s="18" t="s">
+      <c r="R150" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="S149" s="18" t="s">
-        <v>631</v>
-      </c>
-      <c r="T149" s="18" t="s">
-        <v>632</v>
-      </c>
-      <c r="U149" s="18" t="s">
+      <c r="S150" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="T150" s="18" t="s">
+        <v>636</v>
+      </c>
+      <c r="U150" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="V149" s="18" t="s">
+      <c r="V150" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="W149" s="18" t="s">
+      <c r="W150" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="X149" s="18" t="s">
-        <v>633</v>
-      </c>
-      <c r="Y149" s="18" t="s">
-        <v>634</v>
-      </c>
-      <c r="Z149" s="18" t="s">
-        <v>635</v>
+      <c r="X150" s="18" t="s">
+        <v>637</v>
+      </c>
+      <c r="Y150" s="18" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z150" s="18" t="s">
+        <v>639</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="19" t="n">
-        <v>142</v>
-      </c>
-      <c r="B150" s="19" t="n">
+    <row r="151" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="19" t="n">
+        <v>143</v>
+      </c>
+      <c r="B151" s="19" t="n">
         <v>885.91</v>
       </c>
-      <c r="C150" s="19" t="n">
+      <c r="C151" s="19" t="n">
         <v>1325.33</v>
       </c>
-      <c r="D150" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" s="19" t="n">
-        <v>106708.44</v>
-      </c>
-      <c r="F150" s="19" t="n">
-        <v>4687977.43</v>
-      </c>
-      <c r="G150" s="19" t="n">
-        <v>297663.27</v>
-      </c>
-      <c r="H150" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" s="19" t="n">
+      <c r="D151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="19" t="n">
+        <v>107298.49</v>
+      </c>
+      <c r="F151" s="19" t="n">
+        <v>4706736.98</v>
+      </c>
+      <c r="G151" s="19" t="n">
+        <v>298976.44</v>
+      </c>
+      <c r="H151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="19" t="n">
         <v>1376.65</v>
       </c>
-      <c r="K150" s="19" t="n">
-        <v>4839007.01</v>
-      </c>
-      <c r="L150" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" s="19" t="n">
+      <c r="K151" s="19" t="n">
+        <v>4858356.61</v>
+      </c>
+      <c r="L151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="19" t="n">
         <v>44100.05</v>
       </c>
-      <c r="N150" s="19" t="n">
+      <c r="N151" s="19" t="n">
         <v>6802.25</v>
       </c>
-      <c r="O150" s="19" t="n">
+      <c r="O151" s="19" t="n">
         <v>373.06</v>
       </c>
-      <c r="P150" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" s="20" t="n">
-        <v>4048.277646</v>
-      </c>
-      <c r="S150" s="19" t="n">
-        <v>4725056.9</v>
-      </c>
-      <c r="T150" s="19" t="n">
-        <v>4839007.01</v>
-      </c>
-      <c r="U150" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W150" s="19" t="n">
-        <v>4020097.76</v>
-      </c>
-      <c r="X150" s="19" t="n">
-        <v>4020.08</v>
-      </c>
-      <c r="Y150" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z150" s="19" t="n">
-        <v>36181.05</v>
+      <c r="P151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" s="20" t="n">
+        <v>4048.61719</v>
+      </c>
+      <c r="S151" s="19" t="n">
+        <v>4743816.45</v>
+      </c>
+      <c r="T151" s="19" t="n">
+        <v>4858356.61</v>
+      </c>
+      <c r="U151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" s="19" t="n">
+        <v>4035930.35</v>
+      </c>
+      <c r="X151" s="19" t="n">
+        <v>4035.92</v>
+      </c>
+      <c r="Y151" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="19" t="n">
+        <v>36323.55</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="18" t="s">
+    <row r="152" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B151" s="18" t="s">
+      <c r="B152" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C151" s="18" t="s">
+      <c r="C152" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D151" s="18" t="s">
+      <c r="D152" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E151" s="18" t="s">
+      <c r="E152" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F151" s="18" t="s">
+      <c r="F152" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G151" s="18" t="s">
+      <c r="G152" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="H151" s="18" t="s">
+      <c r="H152" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I151" s="18" t="s">
+      <c r="I152" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="J151" s="18" t="s">
+      <c r="J152" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="K151" s="18" t="s">
-        <v>636</v>
-      </c>
-      <c r="L151" s="18" t="s">
-        <v>637</v>
-      </c>
-      <c r="M151" s="18" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="19" t="n">
-        <v>215125.73</v>
-      </c>
-      <c r="B152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="19" t="n">
-        <v>37</v>
-      </c>
-      <c r="E152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" s="19" t="n">
-        <v>0</v>
+      <c r="K152" s="18" t="s">
+        <v>640</v>
+      </c>
+      <c r="L152" s="18" t="s">
+        <v>641</v>
+      </c>
+      <c r="M152" s="18" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="4"/>
+      <c r="A153" s="19" t="n">
+        <v>216066.74</v>
+      </c>
+      <c r="B153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" s="19" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="E153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="154" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="21" t="s">
-        <v>639</v>
-      </c>
-      <c r="B154" s="21"/>
-      <c r="C154" s="21"/>
-      <c r="D154" s="21"/>
-      <c r="E154" s="21"/>
-      <c r="F154" s="21"/>
-      <c r="G154" s="21"/>
-      <c r="H154" s="21"/>
-      <c r="I154" s="21"/>
-      <c r="J154" s="21"/>
-      <c r="K154" s="21"/>
-      <c r="L154" s="21"/>
-      <c r="M154" s="21"/>
-      <c r="N154" s="21"/>
-      <c r="O154" s="21"/>
-      <c r="P154" s="21"/>
-      <c r="Q154" s="21"/>
-      <c r="R154" s="21"/>
-      <c r="S154" s="21"/>
-      <c r="T154" s="21"/>
-      <c r="U154" s="21"/>
-      <c r="V154" s="21"/>
-      <c r="W154" s="21"/>
-      <c r="X154" s="21"/>
-      <c r="Y154" s="21"/>
-      <c r="Z154" s="21"/>
-      <c r="AA154" s="21"/>
-      <c r="AB154" s="21"/>
-      <c r="AC154" s="21"/>
-      <c r="AD154" s="21"/>
-      <c r="AE154" s="21"/>
-      <c r="AF154" s="21"/>
-      <c r="AG154" s="21"/>
-      <c r="AH154" s="21"/>
-      <c r="AI154" s="21"/>
-      <c r="AJ154" s="21"/>
-      <c r="AK154" s="21"/>
-      <c r="AL154" s="21"/>
-      <c r="AM154" s="21"/>
-      <c r="AN154" s="21"/>
-      <c r="AO154" s="21"/>
-      <c r="AP154" s="21"/>
-      <c r="AQ154" s="21"/>
-      <c r="AR154" s="21"/>
-      <c r="AS154" s="21"/>
-      <c r="AT154" s="21"/>
-      <c r="AU154" s="21"/>
-      <c r="AV154" s="21"/>
-      <c r="AW154" s="21"/>
-      <c r="AX154" s="21"/>
-      <c r="AY154" s="21"/>
-      <c r="AZ154" s="21"/>
-      <c r="BA154" s="21"/>
-      <c r="BB154" s="21"/>
-      <c r="BC154" s="21"/>
-      <c r="BD154" s="21"/>
-      <c r="BE154" s="21"/>
-      <c r="BF154" s="21"/>
-      <c r="BG154" s="21"/>
-      <c r="BH154" s="21"/>
-      <c r="BI154" s="21"/>
-      <c r="BJ154" s="21"/>
-      <c r="BK154" s="21"/>
-      <c r="BL154" s="21"/>
-      <c r="BM154" s="21"/>
-      <c r="BN154" s="21"/>
-      <c r="BO154" s="21"/>
-      <c r="BP154" s="21"/>
-      <c r="BQ154" s="21"/>
+    <row r="154" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4"/>
     </row>
-    <row r="155" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
-      <c r="F155" s="4"/>
-      <c r="G155" s="4"/>
-      <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
-      <c r="K155" s="4"/>
-      <c r="L155" s="4"/>
-      <c r="M155" s="4"/>
-      <c r="N155" s="4"/>
-      <c r="O155" s="4"/>
-      <c r="P155" s="4"/>
-      <c r="Q155" s="4"/>
-      <c r="R155" s="4"/>
-      <c r="S155" s="4"/>
-      <c r="T155" s="4"/>
-      <c r="U155" s="4"/>
-      <c r="V155" s="4"/>
-      <c r="W155" s="4"/>
-      <c r="X155" s="4"/>
-      <c r="Y155" s="4"/>
-      <c r="Z155" s="4"/>
-      <c r="AA155" s="4"/>
-      <c r="AB155" s="4"/>
-      <c r="AC155" s="4"/>
-      <c r="AD155" s="4"/>
-      <c r="AE155" s="4"/>
-      <c r="AF155" s="4"/>
-      <c r="AG155" s="4"/>
-      <c r="AH155" s="4"/>
-      <c r="AI155" s="4"/>
-      <c r="AJ155" s="4"/>
-      <c r="AK155" s="4"/>
-      <c r="AL155" s="4"/>
-      <c r="AM155" s="4"/>
-      <c r="AN155" s="4"/>
-      <c r="AO155" s="4"/>
-      <c r="AP155" s="4"/>
-      <c r="AQ155" s="4"/>
-      <c r="AR155" s="4"/>
-      <c r="AS155" s="4"/>
-      <c r="AT155" s="4"/>
-      <c r="AU155" s="4"/>
-      <c r="AV155" s="4"/>
-      <c r="AW155" s="4"/>
-      <c r="AX155" s="4"/>
-      <c r="AY155" s="4"/>
-      <c r="AZ155" s="4"/>
-      <c r="BA155" s="4"/>
-      <c r="BB155" s="4"/>
-      <c r="BC155" s="4"/>
-      <c r="BD155" s="4"/>
-      <c r="BE155" s="4"/>
-      <c r="BF155" s="4"/>
-      <c r="BG155" s="4"/>
-      <c r="BH155" s="4"/>
-      <c r="BI155" s="4"/>
-      <c r="BJ155" s="4"/>
-      <c r="BK155" s="4"/>
-      <c r="BL155" s="4"/>
-      <c r="BM155" s="4"/>
-      <c r="BN155" s="4"/>
-      <c r="BO155" s="4"/>
-      <c r="BP155" s="4"/>
-      <c r="BQ155" s="4"/>
+    <row r="155" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="21" t="s">
+        <v>643</v>
+      </c>
+      <c r="B155" s="21"/>
+      <c r="C155" s="21"/>
+      <c r="D155" s="21"/>
+      <c r="E155" s="21"/>
+      <c r="F155" s="21"/>
+      <c r="G155" s="21"/>
+      <c r="H155" s="21"/>
+      <c r="I155" s="21"/>
+      <c r="J155" s="21"/>
+      <c r="K155" s="21"/>
+      <c r="L155" s="21"/>
+      <c r="M155" s="21"/>
+      <c r="N155" s="21"/>
+      <c r="O155" s="21"/>
+      <c r="P155" s="21"/>
+      <c r="Q155" s="21"/>
+      <c r="R155" s="21"/>
+      <c r="S155" s="21"/>
+      <c r="T155" s="21"/>
+      <c r="U155" s="21"/>
+      <c r="V155" s="21"/>
+      <c r="W155" s="21"/>
+      <c r="X155" s="21"/>
+      <c r="Y155" s="21"/>
+      <c r="Z155" s="21"/>
+      <c r="AA155" s="21"/>
+      <c r="AB155" s="21"/>
+      <c r="AC155" s="21"/>
+      <c r="AD155" s="21"/>
+      <c r="AE155" s="21"/>
+      <c r="AF155" s="21"/>
+      <c r="AG155" s="21"/>
+      <c r="AH155" s="21"/>
+      <c r="AI155" s="21"/>
+      <c r="AJ155" s="21"/>
+      <c r="AK155" s="21"/>
+      <c r="AL155" s="21"/>
+      <c r="AM155" s="21"/>
+      <c r="AN155" s="21"/>
+      <c r="AO155" s="21"/>
+      <c r="AP155" s="21"/>
+      <c r="AQ155" s="21"/>
+      <c r="AR155" s="21"/>
+      <c r="AS155" s="21"/>
+      <c r="AT155" s="21"/>
+      <c r="AU155" s="21"/>
+      <c r="AV155" s="21"/>
+      <c r="AW155" s="21"/>
+      <c r="AX155" s="21"/>
+      <c r="AY155" s="21"/>
+      <c r="AZ155" s="21"/>
+      <c r="BA155" s="21"/>
+      <c r="BB155" s="21"/>
+      <c r="BC155" s="21"/>
+      <c r="BD155" s="21"/>
+      <c r="BE155" s="21"/>
+      <c r="BF155" s="21"/>
+      <c r="BG155" s="21"/>
+      <c r="BH155" s="21"/>
+      <c r="BI155" s="21"/>
+      <c r="BJ155" s="21"/>
+      <c r="BK155" s="21"/>
+      <c r="BL155" s="21"/>
+      <c r="BM155" s="21"/>
+      <c r="BN155" s="21"/>
+      <c r="BO155" s="21"/>
+      <c r="BP155" s="21"/>
+      <c r="BQ155" s="21"/>
     </row>
     <row r="156" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="4" t="s">
-        <v>640</v>
+        <v>79</v>
       </c>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -48509,7 +48651,7 @@
     </row>
     <row r="157" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -48582,7 +48724,7 @@
     </row>
     <row r="158" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="4" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -48655,7 +48797,7 @@
     </row>
     <row r="159" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="s">
-        <v>26</v>
+        <v>646</v>
       </c>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -48728,7 +48870,7 @@
     </row>
     <row r="160" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="4" t="s">
-        <v>643</v>
+        <v>26</v>
       </c>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -48801,7 +48943,7 @@
     </row>
     <row r="161" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -48874,7 +49016,7 @@
     </row>
     <row r="162" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="4" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -48947,7 +49089,7 @@
     </row>
     <row r="163" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -49020,7 +49162,7 @@
     </row>
     <row r="164" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="4" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -49091,8 +49233,81 @@
       <c r="BP164" s="4"/>
       <c r="BQ164" s="4"/>
     </row>
+    <row r="165" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="B165" s="4"/>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4"/>
+      <c r="G165" s="4"/>
+      <c r="H165" s="4"/>
+      <c r="I165" s="4"/>
+      <c r="J165" s="4"/>
+      <c r="K165" s="4"/>
+      <c r="L165" s="4"/>
+      <c r="M165" s="4"/>
+      <c r="N165" s="4"/>
+      <c r="O165" s="4"/>
+      <c r="P165" s="4"/>
+      <c r="Q165" s="4"/>
+      <c r="R165" s="4"/>
+      <c r="S165" s="4"/>
+      <c r="T165" s="4"/>
+      <c r="U165" s="4"/>
+      <c r="V165" s="4"/>
+      <c r="W165" s="4"/>
+      <c r="X165" s="4"/>
+      <c r="Y165" s="4"/>
+      <c r="Z165" s="4"/>
+      <c r="AA165" s="4"/>
+      <c r="AB165" s="4"/>
+      <c r="AC165" s="4"/>
+      <c r="AD165" s="4"/>
+      <c r="AE165" s="4"/>
+      <c r="AF165" s="4"/>
+      <c r="AG165" s="4"/>
+      <c r="AH165" s="4"/>
+      <c r="AI165" s="4"/>
+      <c r="AJ165" s="4"/>
+      <c r="AK165" s="4"/>
+      <c r="AL165" s="4"/>
+      <c r="AM165" s="4"/>
+      <c r="AN165" s="4"/>
+      <c r="AO165" s="4"/>
+      <c r="AP165" s="4"/>
+      <c r="AQ165" s="4"/>
+      <c r="AR165" s="4"/>
+      <c r="AS165" s="4"/>
+      <c r="AT165" s="4"/>
+      <c r="AU165" s="4"/>
+      <c r="AV165" s="4"/>
+      <c r="AW165" s="4"/>
+      <c r="AX165" s="4"/>
+      <c r="AY165" s="4"/>
+      <c r="AZ165" s="4"/>
+      <c r="BA165" s="4"/>
+      <c r="BB165" s="4"/>
+      <c r="BC165" s="4"/>
+      <c r="BD165" s="4"/>
+      <c r="BE165" s="4"/>
+      <c r="BF165" s="4"/>
+      <c r="BG165" s="4"/>
+      <c r="BH165" s="4"/>
+      <c r="BI165" s="4"/>
+      <c r="BJ165" s="4"/>
+      <c r="BK165" s="4"/>
+      <c r="BL165" s="4"/>
+      <c r="BM165" s="4"/>
+      <c r="BN165" s="4"/>
+      <c r="BO165" s="4"/>
+      <c r="BP165" s="4"/>
+      <c r="BQ165" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="158">
+  <mergeCells count="159">
     <mergeCell ref="A1:BM1"/>
     <mergeCell ref="BN1:BQ1"/>
     <mergeCell ref="A2:BQ2"/>
@@ -49239,8 +49454,8 @@
     <mergeCell ref="B144:E144"/>
     <mergeCell ref="B145:E145"/>
     <mergeCell ref="B146:E146"/>
-    <mergeCell ref="A148:Z148"/>
-    <mergeCell ref="A154:BQ154"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="A149:Z149"/>
     <mergeCell ref="A155:BQ155"/>
     <mergeCell ref="A156:BQ156"/>
     <mergeCell ref="A157:BQ157"/>
@@ -49251,6 +49466,7 @@
     <mergeCell ref="A162:BQ162"/>
     <mergeCell ref="A163:BQ163"/>
     <mergeCell ref="A164:BQ164"/>
+    <mergeCell ref="A165:BQ165"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/objetiva/entradas_objetiva.xlsx
+++ b/tratando_tabelas/objetiva/entradas_objetiva.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">Santri ADM 1.1.5.8 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 17/08/2026 07:07:00</t>
+    <t xml:space="preserve">Emitido em: 17/08/2026 07:15:13</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>

--- a/tratando_tabelas/objetiva/entradas_objetiva.xlsx
+++ b/tratando_tabelas/objetiva/entradas_objetiva.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3040" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3200" uniqueCount="436">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.8 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 17/08/2026 07:15:13</t>
+    <t xml:space="preserve">Emitido em: 17/08/2026 07:46:51</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -1211,6 +1211,57 @@
   </si>
   <si>
     <t xml:space="preserve">53260801637895007498550060014717301628625065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.472.050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.338,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53260801637895007498550060014720501593003631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.472.051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53260801637895007498550060014720511531746247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.665 - SIDERURGICA NORTE BRASIL S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">883.323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.992,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15260807933914000154550010008833231474851771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.471.777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.881,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53260801637895007498550060014717771044302211</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -18079,7 +18130,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BQ95"/>
+  <dimension ref="A1:BQ99"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="18.02"/>
@@ -33317,651 +33368,1171 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4"/>
+      <c r="A78" s="8" t="n">
+        <v>312621</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L78" s="12" t="n">
+        <v>27338</v>
+      </c>
+      <c r="M78" s="12" t="n">
+        <v>918.28</v>
+      </c>
+      <c r="N78" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O78" s="12" t="n">
+        <v>28256.28</v>
+      </c>
+      <c r="P78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="13" t="n">
+        <v>28.608</v>
+      </c>
+      <c r="R78" s="12" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="U78" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="V78" s="12" t="n">
+        <v>19847.39</v>
+      </c>
+      <c r="W78" s="12" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="X78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="12" t="n">
+        <v>178.63</v>
+      </c>
+      <c r="Z78" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA78" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB78" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="12" t="n">
+        <v>27338</v>
+      </c>
+      <c r="AE78" s="12" t="n">
+        <v>5467.6</v>
+      </c>
+      <c r="AF78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA78" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB78" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="BC78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BD78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BE78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BG78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BI78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BJ78" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK78" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BL78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM78" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BN78" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="BO78" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BP78" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BQ78" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="79" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="17" t="s">
-        <v>397</v>
-      </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="K79" s="17"/>
-      <c r="L79" s="17"/>
-      <c r="M79" s="17"/>
-      <c r="N79" s="17"/>
-      <c r="O79" s="17"/>
-      <c r="P79" s="17"/>
-      <c r="Q79" s="17"/>
-      <c r="R79" s="17"/>
-      <c r="S79" s="17"/>
-      <c r="T79" s="17"/>
-      <c r="U79" s="17"/>
-      <c r="V79" s="17"/>
-      <c r="W79" s="17"/>
-      <c r="X79" s="17"/>
-      <c r="Y79" s="17"/>
-      <c r="Z79" s="17"/>
+    <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8" t="n">
+        <v>312622</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <v>1315.2</v>
+      </c>
+      <c r="M79" s="12" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="N79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="12" t="n">
+        <v>1308.8</v>
+      </c>
+      <c r="P79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="13" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="R79" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="U79" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="V79" s="12" t="n">
+        <v>918.12</v>
+      </c>
+      <c r="W79" s="12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="X79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="12" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="Z79" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA79" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB79" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="12" t="n">
+        <v>1264.62</v>
+      </c>
+      <c r="AE79" s="12" t="n">
+        <v>252.92</v>
+      </c>
+      <c r="AF79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="12" t="n">
+        <v>1517.54</v>
+      </c>
+      <c r="AK79" s="12" t="n">
+        <v>50.58</v>
+      </c>
+      <c r="AL79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB79" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="BC79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BD79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BE79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BG79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BI79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BJ79" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK79" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BL79" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM79" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BN79" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="BO79" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BP79" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BQ79" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="80" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="18" t="s">
-        <v>398</v>
-      </c>
-      <c r="B80" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="18" t="s">
+    <row r="80" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="n">
+        <v>312623</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I80" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="E80" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F80" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G80" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="H80" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="I80" s="18" t="s">
-        <v>400</v>
-      </c>
-      <c r="J80" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="K80" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L80" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="M80" s="18" t="s">
-        <v>401</v>
-      </c>
-      <c r="N80" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="O80" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="P80" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q80" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="R80" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S80" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="T80" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="U80" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="V80" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="W80" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="X80" s="18" t="s">
-        <v>404</v>
-      </c>
-      <c r="Y80" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="Z80" s="18" t="s">
-        <v>406</v>
+      <c r="J80" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L80" s="12" t="n">
+        <v>16992</v>
+      </c>
+      <c r="M80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" s="12" t="n">
+        <v>16992</v>
+      </c>
+      <c r="P80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="13" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="R80" s="12" t="n">
+        <v>3234</v>
+      </c>
+      <c r="S80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="U80" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="V80" s="12" t="n">
+        <v>13569.82</v>
+      </c>
+      <c r="W80" s="12" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="X80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="12" t="n">
+        <v>122.13</v>
+      </c>
+      <c r="Z80" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA80" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB80" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="12" t="n">
+        <v>16992</v>
+      </c>
+      <c r="AE80" s="12" t="n">
+        <v>2039.04</v>
+      </c>
+      <c r="AF80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS80" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB80" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="BC80" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BD80" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BE80" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF80" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BG80" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH80" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BI80" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BJ80" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK80" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BL80" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM80" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BN80" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="BO80" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BP80" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BQ80" s="16" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="19" t="n">
+      <c r="A81" s="8" t="n">
+        <v>312624</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="J81" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B81" s="19" t="n">
-        <v>2526.21</v>
-      </c>
-      <c r="C81" s="19" t="n">
+      <c r="K81" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L81" s="12" t="n">
+        <v>39881</v>
+      </c>
+      <c r="M81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" s="12" t="n">
+        <v>39881</v>
+      </c>
+      <c r="P81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="13" t="n">
+        <v>30.6432</v>
+      </c>
+      <c r="R81" s="12" t="n">
+        <v>38000</v>
+      </c>
+      <c r="S81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="U81" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="V81" s="12" t="n">
+        <v>31904.8</v>
+      </c>
+      <c r="W81" s="12" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="X81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="12" t="n">
+        <v>287.14</v>
+      </c>
+      <c r="Z81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB81" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="AC81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="12" t="n">
+        <v>39881</v>
+      </c>
+      <c r="AE81" s="12" t="n">
+        <v>7976.2</v>
+      </c>
+      <c r="AF81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA81" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB81" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="BC81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BD81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BE81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BG81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BI81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BJ81" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK81" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BL81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM81" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="BN81" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="BO81" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BP81" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="BQ81" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4"/>
+    </row>
+    <row r="83" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="17"/>
+      <c r="H83" s="17"/>
+      <c r="I83" s="17"/>
+      <c r="J83" s="17"/>
+      <c r="K83" s="17"/>
+      <c r="L83" s="17"/>
+      <c r="M83" s="17"/>
+      <c r="N83" s="17"/>
+      <c r="O83" s="17"/>
+      <c r="P83" s="17"/>
+      <c r="Q83" s="17"/>
+      <c r="R83" s="17"/>
+      <c r="S83" s="17"/>
+      <c r="T83" s="17"/>
+      <c r="U83" s="17"/>
+      <c r="V83" s="17"/>
+      <c r="W83" s="17"/>
+      <c r="X83" s="17"/>
+      <c r="Y83" s="17"/>
+      <c r="Z83" s="17"/>
+    </row>
+    <row r="84" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G84" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H84" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I84" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="J84" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K84" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L84" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="M84" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="N84" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="O84" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="P84" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q84" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="R84" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S84" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="T84" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="U84" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="V84" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="W84" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="X84" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="Y84" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="Z84" s="18" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="19" t="n">
+        <v>77</v>
+      </c>
+      <c r="B85" s="19" t="n">
+        <v>3488.67</v>
+      </c>
+      <c r="C85" s="19" t="n">
         <v>1325.33</v>
       </c>
-      <c r="D81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="19" t="n">
+      <c r="D85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="19" t="n">
         <v>38034.26</v>
       </c>
-      <c r="F81" s="19" t="n">
-        <v>1911994.68</v>
-      </c>
-      <c r="G81" s="19" t="n">
-        <v>123731.56</v>
-      </c>
-      <c r="H81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="19" t="n">
-        <v>1961065.12</v>
-      </c>
-      <c r="L81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="19" t="n">
-        <v>3042.7</v>
-      </c>
-      <c r="N81" s="19" t="n">
-        <v>101.16</v>
-      </c>
-      <c r="O81" s="19" t="n">
+      <c r="F85" s="19" t="n">
+        <v>1997470.3</v>
+      </c>
+      <c r="G85" s="19" t="n">
+        <v>139467.32</v>
+      </c>
+      <c r="H85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="19" t="n">
+        <v>2046591.32</v>
+      </c>
+      <c r="L85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="19" t="n">
+        <v>4560.24</v>
+      </c>
+      <c r="N85" s="19" t="n">
+        <v>151.74</v>
+      </c>
+      <c r="O85" s="19" t="n">
         <v>373.06</v>
       </c>
-      <c r="P81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" s="20" t="n">
-        <v>1715.154864</v>
-      </c>
-      <c r="S81" s="19" t="n">
-        <v>1924130.58</v>
-      </c>
-      <c r="T81" s="19" t="n">
-        <v>1961065.12</v>
-      </c>
-      <c r="U81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" s="19" t="n">
-        <v>1614378.64</v>
-      </c>
-      <c r="X81" s="19" t="n">
-        <v>1614.45</v>
-      </c>
-      <c r="Y81" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="19" t="n">
-        <v>14529.45</v>
+      <c r="P85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="20" t="n">
+        <v>1809.990064</v>
+      </c>
+      <c r="S85" s="19" t="n">
+        <v>2010568.66</v>
+      </c>
+      <c r="T85" s="19" t="n">
+        <v>2046591.32</v>
+      </c>
+      <c r="U85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="19" t="n">
+        <v>1680618.77</v>
+      </c>
+      <c r="X85" s="19" t="n">
+        <v>1680.69</v>
+      </c>
+      <c r="Y85" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="19" t="n">
+        <v>15125.61</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="18" t="s">
+    <row r="86" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B82" s="18" t="s">
+      <c r="B86" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C82" s="18" t="s">
+      <c r="C86" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D82" s="18" t="s">
+      <c r="D86" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E82" s="18" t="s">
+      <c r="E86" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="18" t="s">
+      <c r="F86" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G82" s="18" t="s">
+      <c r="G86" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="H82" s="18" t="s">
+      <c r="H86" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I82" s="18" t="s">
+      <c r="I86" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="J82" s="18" t="s">
+      <c r="J86" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="K82" s="18" t="s">
-        <v>407</v>
-      </c>
-      <c r="L82" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="M82" s="18" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="19" t="n">
-        <v>247460.16</v>
-      </c>
-      <c r="B83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="19" t="n">
-        <v>41.98</v>
-      </c>
-      <c r="E83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4"/>
-    </row>
-    <row r="85" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="B85" s="21"/>
-      <c r="C85" s="21"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="21"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="21"/>
-      <c r="I85" s="21"/>
-      <c r="J85" s="21"/>
-      <c r="K85" s="21"/>
-      <c r="L85" s="21"/>
-      <c r="M85" s="21"/>
-      <c r="N85" s="21"/>
-      <c r="O85" s="21"/>
-      <c r="P85" s="21"/>
-      <c r="Q85" s="21"/>
-      <c r="R85" s="21"/>
-      <c r="S85" s="21"/>
-      <c r="T85" s="21"/>
-      <c r="U85" s="21"/>
-      <c r="V85" s="21"/>
-      <c r="W85" s="21"/>
-      <c r="X85" s="21"/>
-      <c r="Y85" s="21"/>
-      <c r="Z85" s="21"/>
-      <c r="AA85" s="21"/>
-      <c r="AB85" s="21"/>
-      <c r="AC85" s="21"/>
-      <c r="AD85" s="21"/>
-      <c r="AE85" s="21"/>
-      <c r="AF85" s="21"/>
-      <c r="AG85" s="21"/>
-      <c r="AH85" s="21"/>
-      <c r="AI85" s="21"/>
-      <c r="AJ85" s="21"/>
-      <c r="AK85" s="21"/>
-      <c r="AL85" s="21"/>
-      <c r="AM85" s="21"/>
-      <c r="AN85" s="21"/>
-      <c r="AO85" s="21"/>
-      <c r="AP85" s="21"/>
-      <c r="AQ85" s="21"/>
-      <c r="AR85" s="21"/>
-      <c r="AS85" s="21"/>
-      <c r="AT85" s="21"/>
-      <c r="AU85" s="21"/>
-      <c r="AV85" s="21"/>
-      <c r="AW85" s="21"/>
-      <c r="AX85" s="21"/>
-      <c r="AY85" s="21"/>
-      <c r="AZ85" s="21"/>
-      <c r="BA85" s="21"/>
-      <c r="BB85" s="21"/>
-      <c r="BC85" s="21"/>
-      <c r="BD85" s="21"/>
-      <c r="BE85" s="21"/>
-      <c r="BF85" s="21"/>
-      <c r="BG85" s="21"/>
-      <c r="BH85" s="21"/>
-      <c r="BI85" s="21"/>
-      <c r="BJ85" s="21"/>
-      <c r="BK85" s="21"/>
-      <c r="BL85" s="21"/>
-      <c r="BM85" s="21"/>
-      <c r="BN85" s="21"/>
-      <c r="BO85" s="21"/>
-      <c r="BP85" s="21"/>
-      <c r="BQ85" s="21"/>
-    </row>
-    <row r="86" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="4"/>
-      <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
-      <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
-      <c r="Q86" s="4"/>
-      <c r="R86" s="4"/>
-      <c r="S86" s="4"/>
-      <c r="T86" s="4"/>
-      <c r="U86" s="4"/>
-      <c r="V86" s="4"/>
-      <c r="W86" s="4"/>
-      <c r="X86" s="4"/>
-      <c r="Y86" s="4"/>
-      <c r="Z86" s="4"/>
-      <c r="AA86" s="4"/>
-      <c r="AB86" s="4"/>
-      <c r="AC86" s="4"/>
-      <c r="AD86" s="4"/>
-      <c r="AE86" s="4"/>
-      <c r="AF86" s="4"/>
-      <c r="AG86" s="4"/>
-      <c r="AH86" s="4"/>
-      <c r="AI86" s="4"/>
-      <c r="AJ86" s="4"/>
-      <c r="AK86" s="4"/>
-      <c r="AL86" s="4"/>
-      <c r="AM86" s="4"/>
-      <c r="AN86" s="4"/>
-      <c r="AO86" s="4"/>
-      <c r="AP86" s="4"/>
-      <c r="AQ86" s="4"/>
-      <c r="AR86" s="4"/>
-      <c r="AS86" s="4"/>
-      <c r="AT86" s="4"/>
-      <c r="AU86" s="4"/>
-      <c r="AV86" s="4"/>
-      <c r="AW86" s="4"/>
-      <c r="AX86" s="4"/>
-      <c r="AY86" s="4"/>
-      <c r="AZ86" s="4"/>
-      <c r="BA86" s="4"/>
-      <c r="BB86" s="4"/>
-      <c r="BC86" s="4"/>
-      <c r="BD86" s="4"/>
-      <c r="BE86" s="4"/>
-      <c r="BF86" s="4"/>
-      <c r="BG86" s="4"/>
-      <c r="BH86" s="4"/>
-      <c r="BI86" s="4"/>
-      <c r="BJ86" s="4"/>
-      <c r="BK86" s="4"/>
-      <c r="BL86" s="4"/>
-      <c r="BM86" s="4"/>
-      <c r="BN86" s="4"/>
-      <c r="BO86" s="4"/>
-      <c r="BP86" s="4"/>
-      <c r="BQ86" s="4"/>
+      <c r="K86" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="L86" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="M86" s="18" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-      <c r="Q87" s="4"/>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
-      <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
-      <c r="V87" s="4"/>
-      <c r="W87" s="4"/>
-      <c r="X87" s="4"/>
-      <c r="Y87" s="4"/>
-      <c r="Z87" s="4"/>
-      <c r="AA87" s="4"/>
-      <c r="AB87" s="4"/>
-      <c r="AC87" s="4"/>
-      <c r="AD87" s="4"/>
-      <c r="AE87" s="4"/>
-      <c r="AF87" s="4"/>
-      <c r="AG87" s="4"/>
-      <c r="AH87" s="4"/>
-      <c r="AI87" s="4"/>
-      <c r="AJ87" s="4"/>
-      <c r="AK87" s="4"/>
-      <c r="AL87" s="4"/>
-      <c r="AM87" s="4"/>
-      <c r="AN87" s="4"/>
-      <c r="AO87" s="4"/>
-      <c r="AP87" s="4"/>
-      <c r="AQ87" s="4"/>
-      <c r="AR87" s="4"/>
-      <c r="AS87" s="4"/>
-      <c r="AT87" s="4"/>
-      <c r="AU87" s="4"/>
-      <c r="AV87" s="4"/>
-      <c r="AW87" s="4"/>
-      <c r="AX87" s="4"/>
-      <c r="AY87" s="4"/>
-      <c r="AZ87" s="4"/>
-      <c r="BA87" s="4"/>
-      <c r="BB87" s="4"/>
-      <c r="BC87" s="4"/>
-      <c r="BD87" s="4"/>
-      <c r="BE87" s="4"/>
-      <c r="BF87" s="4"/>
-      <c r="BG87" s="4"/>
-      <c r="BH87" s="4"/>
-      <c r="BI87" s="4"/>
-      <c r="BJ87" s="4"/>
-      <c r="BK87" s="4"/>
-      <c r="BL87" s="4"/>
-      <c r="BM87" s="4"/>
-      <c r="BN87" s="4"/>
-      <c r="BO87" s="4"/>
-      <c r="BP87" s="4"/>
-      <c r="BQ87" s="4"/>
+      <c r="A87" s="19" t="n">
+        <v>326694.16</v>
+      </c>
+      <c r="B87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="19" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="E87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
-      <c r="V88" s="4"/>
-      <c r="W88" s="4"/>
-      <c r="X88" s="4"/>
-      <c r="Y88" s="4"/>
-      <c r="Z88" s="4"/>
-      <c r="AA88" s="4"/>
-      <c r="AB88" s="4"/>
-      <c r="AC88" s="4"/>
-      <c r="AD88" s="4"/>
-      <c r="AE88" s="4"/>
-      <c r="AF88" s="4"/>
-      <c r="AG88" s="4"/>
-      <c r="AH88" s="4"/>
-      <c r="AI88" s="4"/>
-      <c r="AJ88" s="4"/>
-      <c r="AK88" s="4"/>
-      <c r="AL88" s="4"/>
-      <c r="AM88" s="4"/>
-      <c r="AN88" s="4"/>
-      <c r="AO88" s="4"/>
-      <c r="AP88" s="4"/>
-      <c r="AQ88" s="4"/>
-      <c r="AR88" s="4"/>
-      <c r="AS88" s="4"/>
-      <c r="AT88" s="4"/>
-      <c r="AU88" s="4"/>
-      <c r="AV88" s="4"/>
-      <c r="AW88" s="4"/>
-      <c r="AX88" s="4"/>
-      <c r="AY88" s="4"/>
-      <c r="AZ88" s="4"/>
-      <c r="BA88" s="4"/>
-      <c r="BB88" s="4"/>
-      <c r="BC88" s="4"/>
-      <c r="BD88" s="4"/>
-      <c r="BE88" s="4"/>
-      <c r="BF88" s="4"/>
-      <c r="BG88" s="4"/>
-      <c r="BH88" s="4"/>
-      <c r="BI88" s="4"/>
-      <c r="BJ88" s="4"/>
-      <c r="BK88" s="4"/>
-      <c r="BL88" s="4"/>
-      <c r="BM88" s="4"/>
-      <c r="BN88" s="4"/>
-      <c r="BO88" s="4"/>
-      <c r="BP88" s="4"/>
-      <c r="BQ88" s="4"/>
+      <c r="A88" s="4"/>
     </row>
-    <row r="89" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
-      <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="4"/>
-      <c r="X89" s="4"/>
-      <c r="Y89" s="4"/>
-      <c r="Z89" s="4"/>
-      <c r="AA89" s="4"/>
-      <c r="AB89" s="4"/>
-      <c r="AC89" s="4"/>
-      <c r="AD89" s="4"/>
-      <c r="AE89" s="4"/>
-      <c r="AF89" s="4"/>
-      <c r="AG89" s="4"/>
-      <c r="AH89" s="4"/>
-      <c r="AI89" s="4"/>
-      <c r="AJ89" s="4"/>
-      <c r="AK89" s="4"/>
-      <c r="AL89" s="4"/>
-      <c r="AM89" s="4"/>
-      <c r="AN89" s="4"/>
-      <c r="AO89" s="4"/>
-      <c r="AP89" s="4"/>
-      <c r="AQ89" s="4"/>
-      <c r="AR89" s="4"/>
-      <c r="AS89" s="4"/>
-      <c r="AT89" s="4"/>
-      <c r="AU89" s="4"/>
-      <c r="AV89" s="4"/>
-      <c r="AW89" s="4"/>
-      <c r="AX89" s="4"/>
-      <c r="AY89" s="4"/>
-      <c r="AZ89" s="4"/>
-      <c r="BA89" s="4"/>
-      <c r="BB89" s="4"/>
-      <c r="BC89" s="4"/>
-      <c r="BD89" s="4"/>
-      <c r="BE89" s="4"/>
-      <c r="BF89" s="4"/>
-      <c r="BG89" s="4"/>
-      <c r="BH89" s="4"/>
-      <c r="BI89" s="4"/>
-      <c r="BJ89" s="4"/>
-      <c r="BK89" s="4"/>
-      <c r="BL89" s="4"/>
-      <c r="BM89" s="4"/>
-      <c r="BN89" s="4"/>
-      <c r="BO89" s="4"/>
-      <c r="BP89" s="4"/>
-      <c r="BQ89" s="4"/>
+    <row r="89" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="21" t="s">
+        <v>427</v>
+      </c>
+      <c r="B89" s="21"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="21"/>
+      <c r="F89" s="21"/>
+      <c r="G89" s="21"/>
+      <c r="H89" s="21"/>
+      <c r="I89" s="21"/>
+      <c r="J89" s="21"/>
+      <c r="K89" s="21"/>
+      <c r="L89" s="21"/>
+      <c r="M89" s="21"/>
+      <c r="N89" s="21"/>
+      <c r="O89" s="21"/>
+      <c r="P89" s="21"/>
+      <c r="Q89" s="21"/>
+      <c r="R89" s="21"/>
+      <c r="S89" s="21"/>
+      <c r="T89" s="21"/>
+      <c r="U89" s="21"/>
+      <c r="V89" s="21"/>
+      <c r="W89" s="21"/>
+      <c r="X89" s="21"/>
+      <c r="Y89" s="21"/>
+      <c r="Z89" s="21"/>
+      <c r="AA89" s="21"/>
+      <c r="AB89" s="21"/>
+      <c r="AC89" s="21"/>
+      <c r="AD89" s="21"/>
+      <c r="AE89" s="21"/>
+      <c r="AF89" s="21"/>
+      <c r="AG89" s="21"/>
+      <c r="AH89" s="21"/>
+      <c r="AI89" s="21"/>
+      <c r="AJ89" s="21"/>
+      <c r="AK89" s="21"/>
+      <c r="AL89" s="21"/>
+      <c r="AM89" s="21"/>
+      <c r="AN89" s="21"/>
+      <c r="AO89" s="21"/>
+      <c r="AP89" s="21"/>
+      <c r="AQ89" s="21"/>
+      <c r="AR89" s="21"/>
+      <c r="AS89" s="21"/>
+      <c r="AT89" s="21"/>
+      <c r="AU89" s="21"/>
+      <c r="AV89" s="21"/>
+      <c r="AW89" s="21"/>
+      <c r="AX89" s="21"/>
+      <c r="AY89" s="21"/>
+      <c r="AZ89" s="21"/>
+      <c r="BA89" s="21"/>
+      <c r="BB89" s="21"/>
+      <c r="BC89" s="21"/>
+      <c r="BD89" s="21"/>
+      <c r="BE89" s="21"/>
+      <c r="BF89" s="21"/>
+      <c r="BG89" s="21"/>
+      <c r="BH89" s="21"/>
+      <c r="BI89" s="21"/>
+      <c r="BJ89" s="21"/>
+      <c r="BK89" s="21"/>
+      <c r="BL89" s="21"/>
+      <c r="BM89" s="21"/>
+      <c r="BN89" s="21"/>
+      <c r="BO89" s="21"/>
+      <c r="BP89" s="21"/>
+      <c r="BQ89" s="21"/>
     </row>
     <row r="90" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -34034,7 +34605,7 @@
     </row>
     <row r="91" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -34107,7 +34678,7 @@
     </row>
     <row r="92" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -34180,7 +34751,7 @@
     </row>
     <row r="93" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -34253,7 +34824,7 @@
     </row>
     <row r="94" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>417</v>
+        <v>26</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -34326,7 +34897,7 @@
     </row>
     <row r="95" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -34397,8 +34968,300 @@
       <c r="BP95" s="4"/>
       <c r="BQ95" s="4"/>
     </row>
+    <row r="96" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="4"/>
+      <c r="R96" s="4"/>
+      <c r="S96" s="4"/>
+      <c r="T96" s="4"/>
+      <c r="U96" s="4"/>
+      <c r="V96" s="4"/>
+      <c r="W96" s="4"/>
+      <c r="X96" s="4"/>
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="4"/>
+      <c r="AA96" s="4"/>
+      <c r="AB96" s="4"/>
+      <c r="AC96" s="4"/>
+      <c r="AD96" s="4"/>
+      <c r="AE96" s="4"/>
+      <c r="AF96" s="4"/>
+      <c r="AG96" s="4"/>
+      <c r="AH96" s="4"/>
+      <c r="AI96" s="4"/>
+      <c r="AJ96" s="4"/>
+      <c r="AK96" s="4"/>
+      <c r="AL96" s="4"/>
+      <c r="AM96" s="4"/>
+      <c r="AN96" s="4"/>
+      <c r="AO96" s="4"/>
+      <c r="AP96" s="4"/>
+      <c r="AQ96" s="4"/>
+      <c r="AR96" s="4"/>
+      <c r="AS96" s="4"/>
+      <c r="AT96" s="4"/>
+      <c r="AU96" s="4"/>
+      <c r="AV96" s="4"/>
+      <c r="AW96" s="4"/>
+      <c r="AX96" s="4"/>
+      <c r="AY96" s="4"/>
+      <c r="AZ96" s="4"/>
+      <c r="BA96" s="4"/>
+      <c r="BB96" s="4"/>
+      <c r="BC96" s="4"/>
+      <c r="BD96" s="4"/>
+      <c r="BE96" s="4"/>
+      <c r="BF96" s="4"/>
+      <c r="BG96" s="4"/>
+      <c r="BH96" s="4"/>
+      <c r="BI96" s="4"/>
+      <c r="BJ96" s="4"/>
+      <c r="BK96" s="4"/>
+      <c r="BL96" s="4"/>
+      <c r="BM96" s="4"/>
+      <c r="BN96" s="4"/>
+      <c r="BO96" s="4"/>
+      <c r="BP96" s="4"/>
+      <c r="BQ96" s="4"/>
+    </row>
+    <row r="97" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="4"/>
+      <c r="Q97" s="4"/>
+      <c r="R97" s="4"/>
+      <c r="S97" s="4"/>
+      <c r="T97" s="4"/>
+      <c r="U97" s="4"/>
+      <c r="V97" s="4"/>
+      <c r="W97" s="4"/>
+      <c r="X97" s="4"/>
+      <c r="Y97" s="4"/>
+      <c r="Z97" s="4"/>
+      <c r="AA97" s="4"/>
+      <c r="AB97" s="4"/>
+      <c r="AC97" s="4"/>
+      <c r="AD97" s="4"/>
+      <c r="AE97" s="4"/>
+      <c r="AF97" s="4"/>
+      <c r="AG97" s="4"/>
+      <c r="AH97" s="4"/>
+      <c r="AI97" s="4"/>
+      <c r="AJ97" s="4"/>
+      <c r="AK97" s="4"/>
+      <c r="AL97" s="4"/>
+      <c r="AM97" s="4"/>
+      <c r="AN97" s="4"/>
+      <c r="AO97" s="4"/>
+      <c r="AP97" s="4"/>
+      <c r="AQ97" s="4"/>
+      <c r="AR97" s="4"/>
+      <c r="AS97" s="4"/>
+      <c r="AT97" s="4"/>
+      <c r="AU97" s="4"/>
+      <c r="AV97" s="4"/>
+      <c r="AW97" s="4"/>
+      <c r="AX97" s="4"/>
+      <c r="AY97" s="4"/>
+      <c r="AZ97" s="4"/>
+      <c r="BA97" s="4"/>
+      <c r="BB97" s="4"/>
+      <c r="BC97" s="4"/>
+      <c r="BD97" s="4"/>
+      <c r="BE97" s="4"/>
+      <c r="BF97" s="4"/>
+      <c r="BG97" s="4"/>
+      <c r="BH97" s="4"/>
+      <c r="BI97" s="4"/>
+      <c r="BJ97" s="4"/>
+      <c r="BK97" s="4"/>
+      <c r="BL97" s="4"/>
+      <c r="BM97" s="4"/>
+      <c r="BN97" s="4"/>
+      <c r="BO97" s="4"/>
+      <c r="BP97" s="4"/>
+      <c r="BQ97" s="4"/>
+    </row>
+    <row r="98" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="4"/>
+      <c r="Q98" s="4"/>
+      <c r="R98" s="4"/>
+      <c r="S98" s="4"/>
+      <c r="T98" s="4"/>
+      <c r="U98" s="4"/>
+      <c r="V98" s="4"/>
+      <c r="W98" s="4"/>
+      <c r="X98" s="4"/>
+      <c r="Y98" s="4"/>
+      <c r="Z98" s="4"/>
+      <c r="AA98" s="4"/>
+      <c r="AB98" s="4"/>
+      <c r="AC98" s="4"/>
+      <c r="AD98" s="4"/>
+      <c r="AE98" s="4"/>
+      <c r="AF98" s="4"/>
+      <c r="AG98" s="4"/>
+      <c r="AH98" s="4"/>
+      <c r="AI98" s="4"/>
+      <c r="AJ98" s="4"/>
+      <c r="AK98" s="4"/>
+      <c r="AL98" s="4"/>
+      <c r="AM98" s="4"/>
+      <c r="AN98" s="4"/>
+      <c r="AO98" s="4"/>
+      <c r="AP98" s="4"/>
+      <c r="AQ98" s="4"/>
+      <c r="AR98" s="4"/>
+      <c r="AS98" s="4"/>
+      <c r="AT98" s="4"/>
+      <c r="AU98" s="4"/>
+      <c r="AV98" s="4"/>
+      <c r="AW98" s="4"/>
+      <c r="AX98" s="4"/>
+      <c r="AY98" s="4"/>
+      <c r="AZ98" s="4"/>
+      <c r="BA98" s="4"/>
+      <c r="BB98" s="4"/>
+      <c r="BC98" s="4"/>
+      <c r="BD98" s="4"/>
+      <c r="BE98" s="4"/>
+      <c r="BF98" s="4"/>
+      <c r="BG98" s="4"/>
+      <c r="BH98" s="4"/>
+      <c r="BI98" s="4"/>
+      <c r="BJ98" s="4"/>
+      <c r="BK98" s="4"/>
+      <c r="BL98" s="4"/>
+      <c r="BM98" s="4"/>
+      <c r="BN98" s="4"/>
+      <c r="BO98" s="4"/>
+      <c r="BP98" s="4"/>
+      <c r="BQ98" s="4"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="4"/>
+      <c r="Q99" s="4"/>
+      <c r="R99" s="4"/>
+      <c r="S99" s="4"/>
+      <c r="T99" s="4"/>
+      <c r="U99" s="4"/>
+      <c r="V99" s="4"/>
+      <c r="W99" s="4"/>
+      <c r="X99" s="4"/>
+      <c r="Y99" s="4"/>
+      <c r="Z99" s="4"/>
+      <c r="AA99" s="4"/>
+      <c r="AB99" s="4"/>
+      <c r="AC99" s="4"/>
+      <c r="AD99" s="4"/>
+      <c r="AE99" s="4"/>
+      <c r="AF99" s="4"/>
+      <c r="AG99" s="4"/>
+      <c r="AH99" s="4"/>
+      <c r="AI99" s="4"/>
+      <c r="AJ99" s="4"/>
+      <c r="AK99" s="4"/>
+      <c r="AL99" s="4"/>
+      <c r="AM99" s="4"/>
+      <c r="AN99" s="4"/>
+      <c r="AO99" s="4"/>
+      <c r="AP99" s="4"/>
+      <c r="AQ99" s="4"/>
+      <c r="AR99" s="4"/>
+      <c r="AS99" s="4"/>
+      <c r="AT99" s="4"/>
+      <c r="AU99" s="4"/>
+      <c r="AV99" s="4"/>
+      <c r="AW99" s="4"/>
+      <c r="AX99" s="4"/>
+      <c r="AY99" s="4"/>
+      <c r="AZ99" s="4"/>
+      <c r="BA99" s="4"/>
+      <c r="BB99" s="4"/>
+      <c r="BC99" s="4"/>
+      <c r="BD99" s="4"/>
+      <c r="BE99" s="4"/>
+      <c r="BF99" s="4"/>
+      <c r="BG99" s="4"/>
+      <c r="BH99" s="4"/>
+      <c r="BI99" s="4"/>
+      <c r="BJ99" s="4"/>
+      <c r="BK99" s="4"/>
+      <c r="BL99" s="4"/>
+      <c r="BM99" s="4"/>
+      <c r="BN99" s="4"/>
+      <c r="BO99" s="4"/>
+      <c r="BP99" s="4"/>
+      <c r="BQ99" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="89">
+  <mergeCells count="93">
     <mergeCell ref="A1:BM1"/>
     <mergeCell ref="BN1:BQ1"/>
     <mergeCell ref="A2:BQ2"/>
@@ -34476,11 +35339,11 @@
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="B76:E76"/>
     <mergeCell ref="B77:E77"/>
-    <mergeCell ref="A79:Z79"/>
-    <mergeCell ref="A85:BQ85"/>
-    <mergeCell ref="A86:BQ86"/>
-    <mergeCell ref="A87:BQ87"/>
-    <mergeCell ref="A88:BQ88"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="A83:Z83"/>
     <mergeCell ref="A89:BQ89"/>
     <mergeCell ref="A90:BQ90"/>
     <mergeCell ref="A91:BQ91"/>
@@ -34488,6 +35351,10 @@
     <mergeCell ref="A93:BQ93"/>
     <mergeCell ref="A94:BQ94"/>
     <mergeCell ref="A95:BQ95"/>
+    <mergeCell ref="A96:BQ96"/>
+    <mergeCell ref="A97:BQ97"/>
+    <mergeCell ref="A98:BQ98"/>
+    <mergeCell ref="A99:BQ99"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
